--- a/input_processing/clean_excel_files_PL/reg_partnership.xlsx
+++ b/input_processing/clean_excel_files_PL/reg_partnership.xlsx
@@ -165,13 +165,13 @@
     <t>Les_c4_Retired_L1</t>
   </si>
   <si>
-    <t>Les_c4_Student_Dgn</t>
-  </si>
-  <si>
-    <t>Les_c4_NotEmployed_Dgn</t>
-  </si>
-  <si>
-    <t>Les_c4_Retired_Dgn</t>
+    <t>Dgn_Les_c4_Student_L1</t>
+  </si>
+  <si>
+    <t>Dgn_Les_c4_NotEmployed_L1</t>
+  </si>
+  <si>
+    <t>Dgn_Les_c4_Retired_L1</t>
   </si>
   <si>
     <t>Dhe_Fair</t>
@@ -493,7 +493,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>0.09653466446907033</v>
+        <v>0.096534689033953569</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -501,7 +501,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="1">
-        <v>692.78913889781575</v>
+        <v>692.78993388975459</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="1">
-        <v>-4787295.8291362207</v>
+        <v>-4787295.6989714447</v>
       </c>
     </row>
     <row r="9">
@@ -573,7 +573,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="1">
-        <v>0.089005650034680861</v>
+        <v>0.089002203411627567</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -581,7 +581,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="1">
-        <v>176.37139558765489</v>
+        <v>176.36544561882715</v>
       </c>
     </row>
     <row r="14">
@@ -597,7 +597,7 @@
         <v>25</v>
       </c>
       <c r="F14" s="1">
-        <v>-861676.48916399968</v>
+        <v>-861679.74919964327</v>
       </c>
     </row>
   </sheetData>
@@ -724,109 +724,109 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>0.032308885668369314</v>
+        <v>0.032308826668187407</v>
       </c>
       <c r="C2" s="1">
-        <v>5.7077035556071165e-05</v>
+        <v>5.7076781277196299e-05</v>
       </c>
       <c r="D2" s="1">
-        <v>-6.8628298072365284e-07</v>
+        <v>-6.8627979130762189e-07</v>
       </c>
       <c r="E2" s="1">
-        <v>2.575049148910468e-06</v>
+        <v>2.5749553786135208e-06</v>
       </c>
       <c r="F2" s="1">
-        <v>6.0905622363669485e-05</v>
+        <v>6.0904622232392644e-05</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.00013998483852906016</v>
+        <v>-0.00013998340774125335</v>
       </c>
       <c r="H2" s="1">
-        <v>5.2243716594150766e-05</v>
+        <v>5.2244595095198227e-05</v>
       </c>
       <c r="I2" s="1">
-        <v>3.9976930654169856e-05</v>
+        <v>3.9978535171493793e-05</v>
       </c>
       <c r="J2" s="1">
-        <v>-2.8204369602493836e-05</v>
+        <v>-2.8202526391531179e-05</v>
       </c>
       <c r="K2" s="1">
-        <v>-2.5335394036607678e-05</v>
+        <v>-2.5333575131431787e-05</v>
       </c>
       <c r="L2" s="1">
-        <v>-6.3598494578199495e-07</v>
+        <v>-6.3598245064984389e-07</v>
       </c>
       <c r="M2" s="1">
-        <v>-4.4523709050523245e-05</v>
+        <v>-4.4527168894267647e-05</v>
       </c>
       <c r="N2" s="1">
-        <v>-5.7228304060927195e-05</v>
+        <v>-5.7227342843701318e-05</v>
       </c>
       <c r="O2" s="1">
-        <v>0.00015399678834331212</v>
+        <v>0.00015399549930996125</v>
       </c>
       <c r="P2" s="1">
-        <v>-6.3297231391195728e-05</v>
+        <v>-6.32983525634668e-05</v>
       </c>
       <c r="Q2" s="1">
-        <v>-3.9426247011551877e-05</v>
+        <v>-3.9427885353519204e-05</v>
       </c>
       <c r="R2" s="1">
-        <v>0.00030701867894046022</v>
+        <v>0.00030701817545530734</v>
       </c>
       <c r="S2" s="1">
-        <v>-1.2760387812585058e-05</v>
+        <v>-1.2760220792588659e-05</v>
       </c>
       <c r="T2" s="1">
-        <v>5.5182437204160897e-05</v>
+        <v>5.5183975946626509e-05</v>
       </c>
       <c r="U2" s="1">
-        <v>0.00014753959923505825</v>
+        <v>0.00014753996167914842</v>
       </c>
       <c r="V2" s="1">
-        <v>9.8860343215931979e-05</v>
+        <v>9.8860495273206113e-05</v>
       </c>
       <c r="W2" s="1">
-        <v>0.00048960940691704098</v>
+        <v>0.00048960431695527348</v>
       </c>
       <c r="X2" s="1">
-        <v>4.2528895620748256e-05</v>
+        <v>4.2532632568744637e-05</v>
       </c>
       <c r="Y2" s="1">
-        <v>-3.3743639117629024e-05</v>
+        <v>-3.3743635558729646e-05</v>
       </c>
       <c r="Z2" s="1">
-        <v>-1.7099215246567118e-05</v>
+        <v>-1.709594055688136e-05</v>
       </c>
       <c r="AA2" s="1">
-        <v>7.0188735972137942e-06</v>
+        <v>7.0181798006870542e-06</v>
       </c>
       <c r="AB2" s="1">
-        <v>0.00018567670333693382</v>
+        <v>0.0001856761243294749</v>
       </c>
       <c r="AC2" s="1">
-        <v>0.00027216433663260849</v>
+        <v>0.0002721631116205628</v>
       </c>
       <c r="AD2" s="1">
-        <v>0.00030867299995009328</v>
+        <v>0.00030867171528705664</v>
       </c>
       <c r="AE2" s="1">
-        <v>2.8306155158717983e-05</v>
+        <v>2.830682841456066e-05</v>
       </c>
       <c r="AF2" s="1">
-        <v>1.4010557329755002e-05</v>
+        <v>1.4011033407124152e-05</v>
       </c>
       <c r="AG2" s="1">
-        <v>1.2980007629815834e-05</v>
+        <v>1.2980567515141761e-05</v>
       </c>
       <c r="AH2" s="1">
-        <v>-1.4684746289809949e-05</v>
+        <v>-1.4683798727084237e-05</v>
       </c>
       <c r="AI2" s="1">
-        <v>1.3508909798347709e-06</v>
+        <v>1.3508352144051095e-06</v>
       </c>
       <c r="AJ2" s="1">
-        <v>-0.0013737123397219745</v>
+        <v>-0.0013737078679931687</v>
       </c>
     </row>
     <row r="3">
@@ -834,109 +834,109 @@
         <v>29</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.00052207539473376119</v>
+        <v>-0.00052207472032267388</v>
       </c>
       <c r="C3" s="1">
-        <v>-6.8628298072365284e-07</v>
+        <v>-6.8627979130762189e-07</v>
       </c>
       <c r="D3" s="1">
-        <v>8.7854702255960485e-09</v>
+        <v>8.7854305696847327e-09</v>
       </c>
       <c r="E3" s="1">
-        <v>2.7172088924296669e-07</v>
+        <v>2.7172096468647076e-07</v>
       </c>
       <c r="F3" s="1">
-        <v>-7.8451859164472258e-07</v>
+        <v>-7.8451461404377946e-07</v>
       </c>
       <c r="G3" s="1">
-        <v>1.9364975840381348e-06</v>
+        <v>1.9364905753540041e-06</v>
       </c>
       <c r="H3" s="1">
-        <v>-7.1257876187118704e-07</v>
+        <v>-7.1260216589030011e-07</v>
       </c>
       <c r="I3" s="1">
-        <v>-3.9660355741430841e-07</v>
+        <v>-3.9662686978448665e-07</v>
       </c>
       <c r="J3" s="1">
-        <v>4.9287103980716147e-07</v>
+        <v>4.9284394345285094e-07</v>
       </c>
       <c r="K3" s="1">
-        <v>1.0275124607310917e-07</v>
+        <v>1.0272433494008275e-07</v>
       </c>
       <c r="L3" s="1">
-        <v>7.0085726881803537e-09</v>
+        <v>7.0085409282790471e-09</v>
       </c>
       <c r="M3" s="1">
-        <v>4.2679394562569333e-07</v>
+        <v>4.2684847013249517e-07</v>
       </c>
       <c r="N3" s="1">
-        <v>7.2068448689796629e-07</v>
+        <v>7.2068097618752903e-07</v>
       </c>
       <c r="O3" s="1">
-        <v>-1.9844840922676206e-06</v>
+        <v>-1.9844786512222254e-06</v>
       </c>
       <c r="P3" s="1">
-        <v>8.3256089161760051e-07</v>
+        <v>8.3258717768035957e-07</v>
       </c>
       <c r="Q3" s="1">
-        <v>4.33176523057774e-07</v>
+        <v>4.3320016634359458e-07</v>
       </c>
       <c r="R3" s="1">
-        <v>-3.549840756224113e-06</v>
+        <v>-3.5498434032382622e-06</v>
       </c>
       <c r="S3" s="1">
-        <v>8.2479551165736072e-08</v>
+        <v>8.2476986461290973e-08</v>
       </c>
       <c r="T3" s="1">
-        <v>-8.4219991143292612e-07</v>
+        <v>-8.4221861976990896e-07</v>
       </c>
       <c r="U3" s="1">
-        <v>-1.1442561150505924e-06</v>
+        <v>-1.1442567367710943e-06</v>
       </c>
       <c r="V3" s="1">
-        <v>-1.0598411567220541e-06</v>
+        <v>-1.0598407018523324e-06</v>
       </c>
       <c r="W3" s="1">
-        <v>-7.4529894906173297e-06</v>
+        <v>-7.4529299137327028e-06</v>
       </c>
       <c r="X3" s="1">
-        <v>-7.2579344679136176e-07</v>
+        <v>-7.2585024226574455e-07</v>
       </c>
       <c r="Y3" s="1">
-        <v>1.769903967788333e-07</v>
+        <v>1.7698986989963004e-07</v>
       </c>
       <c r="Z3" s="1">
-        <v>-1.6554399894002201e-07</v>
+        <v>-1.6558045543957419e-07</v>
       </c>
       <c r="AA3" s="1">
-        <v>5.8699640237404798e-07</v>
+        <v>5.8700408775871764e-07</v>
       </c>
       <c r="AB3" s="1">
-        <v>-2.4238604987083328e-06</v>
+        <v>-2.4238540831881245e-06</v>
       </c>
       <c r="AC3" s="1">
-        <v>-3.2995521669964297e-06</v>
+        <v>-3.2995384669150509e-06</v>
       </c>
       <c r="AD3" s="1">
-        <v>-3.4769203898458093e-06</v>
+        <v>-3.4769053911115863e-06</v>
       </c>
       <c r="AE3" s="1">
-        <v>-4.6530067114586417e-07</v>
+        <v>-4.6530828621832126e-07</v>
       </c>
       <c r="AF3" s="1">
-        <v>-4.2677078782167945e-07</v>
+        <v>-4.2677608011418802e-07</v>
       </c>
       <c r="AG3" s="1">
-        <v>-3.3515804808041737e-07</v>
+        <v>-3.3516418809115164e-07</v>
       </c>
       <c r="AH3" s="1">
-        <v>-3.3140509847197309e-08</v>
+        <v>-3.3151959867674149e-08</v>
       </c>
       <c r="AI3" s="1">
-        <v>-1.4179325650530169e-08</v>
+        <v>-1.4178591810838709e-08</v>
       </c>
       <c r="AJ3" s="1">
-        <v>1.5790998508530073e-05</v>
+        <v>1.5790947878286583e-05</v>
       </c>
     </row>
     <row r="4">
@@ -944,109 +944,109 @@
         <v>30</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.12981455512101175</v>
+        <v>-0.12981427060430298</v>
       </c>
       <c r="C4" s="1">
-        <v>2.575049148910468e-06</v>
+        <v>2.5749553786135208e-06</v>
       </c>
       <c r="D4" s="1">
-        <v>2.7172088924296669e-07</v>
+        <v>2.7172096468647076e-07</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0020298859060753145</v>
+        <v>0.0020298918986188658</v>
       </c>
       <c r="F4" s="1">
-        <v>0.0006020000052034645</v>
+        <v>0.00060203777221878212</v>
       </c>
       <c r="G4" s="1">
-        <v>-0.00027867839756572386</v>
+        <v>-0.00027872907144583771</v>
       </c>
       <c r="H4" s="1">
-        <v>0.00019035893291415853</v>
+        <v>0.00019042298174276178</v>
       </c>
       <c r="I4" s="1">
-        <v>-5.9647707198464631e-05</v>
+        <v>-5.962778710002958e-05</v>
       </c>
       <c r="J4" s="1">
-        <v>0.00018601438507195167</v>
+        <v>0.00018603838465634326</v>
       </c>
       <c r="K4" s="1">
-        <v>-2.4517015897646856e-05</v>
+        <v>-2.4492310394911253e-05</v>
       </c>
       <c r="L4" s="1">
-        <v>-2.1188177960275384e-07</v>
+        <v>-2.1187905009502996e-07</v>
       </c>
       <c r="M4" s="1">
-        <v>9.3921477680512615e-06</v>
+        <v>9.3424874144738736e-06</v>
       </c>
       <c r="N4" s="1">
-        <v>-0.00059293813692799042</v>
+        <v>-0.00059297580610242324</v>
       </c>
       <c r="O4" s="1">
-        <v>0.00022455807826074657</v>
+        <v>0.00022460739237397919</v>
       </c>
       <c r="P4" s="1">
-        <v>-0.00015186954876649926</v>
+        <v>-0.00015193298706182309</v>
       </c>
       <c r="Q4" s="1">
-        <v>6.9379171881549196e-05</v>
+        <v>6.9359621375737686e-05</v>
       </c>
       <c r="R4" s="1">
-        <v>0.00027725399536987331</v>
+        <v>0.00027729744631712738</v>
       </c>
       <c r="S4" s="1">
-        <v>0.00021974233489613452</v>
+        <v>0.00021974369811781971</v>
       </c>
       <c r="T4" s="1">
-        <v>-0.00047827977513975351</v>
+        <v>-0.00047827996598539938</v>
       </c>
       <c r="U4" s="1">
-        <v>0.0013256211304872368</v>
+        <v>0.0013256067323528416</v>
       </c>
       <c r="V4" s="1">
-        <v>0.00085724104851977003</v>
+        <v>0.00085723225974047141</v>
       </c>
       <c r="W4" s="1">
-        <v>0.00029796563639309059</v>
+        <v>0.00029797915818645214</v>
       </c>
       <c r="X4" s="1">
-        <v>-0.0020644882461998372</v>
+        <v>-0.0020644448798767985</v>
       </c>
       <c r="Y4" s="1">
-        <v>-0.0017276316854921642</v>
+        <v>-0.001727630255680367</v>
       </c>
       <c r="Z4" s="1">
-        <v>-0.0024108920295859947</v>
+        <v>-0.0024109103060657956</v>
       </c>
       <c r="AA4" s="1">
-        <v>0.0010016955794332359</v>
+        <v>0.0010016998948100487</v>
       </c>
       <c r="AB4" s="1">
-        <v>-7.3158754373563379e-05</v>
+        <v>-7.3155372977507183e-05</v>
       </c>
       <c r="AC4" s="1">
-        <v>-1.1438041462563317e-05</v>
+        <v>-1.1431143622900444e-05</v>
       </c>
       <c r="AD4" s="1">
-        <v>-0.00018837488119969307</v>
+        <v>-0.00018837144918692252</v>
       </c>
       <c r="AE4" s="1">
-        <v>-0.00012273045915808225</v>
+        <v>-0.00012273342236003787</v>
       </c>
       <c r="AF4" s="1">
-        <v>-0.00031380160237652751</v>
+        <v>-0.00031380434301005389</v>
       </c>
       <c r="AG4" s="1">
-        <v>-0.00021590371231865863</v>
+        <v>-0.00021590707885969199</v>
       </c>
       <c r="AH4" s="1">
-        <v>-0.00013733134413083611</v>
+        <v>-0.00013733253135790249</v>
       </c>
       <c r="AI4" s="1">
-        <v>1.255474364764266e-05</v>
+        <v>1.2554507273252845e-05</v>
       </c>
       <c r="AJ4" s="1">
-        <v>-0.0016426316723233468</v>
+        <v>-0.0016426595337495859</v>
       </c>
     </row>
     <row r="5">
@@ -1054,109 +1054,109 @@
         <v>31</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.032891880859458815</v>
+        <v>-0.032889699474098408</v>
       </c>
       <c r="C5" s="1">
-        <v>6.0905622363669485e-05</v>
+        <v>6.0904622232392644e-05</v>
       </c>
       <c r="D5" s="1">
-        <v>-7.8451859164472258e-07</v>
+        <v>-7.8451461404377946e-07</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0006020000052034645</v>
+        <v>0.00060203777221878212</v>
       </c>
       <c r="F5" s="1">
-        <v>0.0038748458684268604</v>
+        <v>0.0038750814941185445</v>
       </c>
       <c r="G5" s="1">
-        <v>-0.0046383244308215964</v>
+        <v>-0.0046386407676822375</v>
       </c>
       <c r="H5" s="1">
-        <v>0.00095977893735323236</v>
+        <v>0.0009602271792811313</v>
       </c>
       <c r="I5" s="1">
-        <v>-0.0009992884764051409</v>
+        <v>-0.00099914765577706994</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.00055843227725555986</v>
+        <v>-0.00055826282276097568</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.00047086266590333698</v>
+        <v>-0.00047068848261181149</v>
       </c>
       <c r="L5" s="1">
-        <v>-6.0658240081193661e-07</v>
+        <v>-6.0655848357436849e-07</v>
       </c>
       <c r="M5" s="1">
-        <v>0.00064215242728752112</v>
+        <v>0.00064181005055088036</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.003879296986032709</v>
+        <v>-0.0038795319336844751</v>
       </c>
       <c r="O5" s="1">
-        <v>0.0046884330391518082</v>
+        <v>0.0046887397131640321</v>
       </c>
       <c r="P5" s="1">
-        <v>-0.00089875314838740118</v>
+        <v>-0.00089919654613862055</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.0010894805349598213</v>
+        <v>0.0010893419761174314</v>
       </c>
       <c r="R5" s="1">
-        <v>0.0015035074056068561</v>
+        <v>0.0015038049337555018</v>
       </c>
       <c r="S5" s="1">
-        <v>-0.00016794487191463704</v>
+        <v>-0.00016793347453158682</v>
       </c>
       <c r="T5" s="1">
-        <v>-0.00095333762545360694</v>
+        <v>-0.00095334010158321721</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.0011014759215987552</v>
+        <v>-0.0011015763435854142</v>
       </c>
       <c r="V5" s="1">
-        <v>-0.00079792068133940951</v>
+        <v>-0.00079798034000817862</v>
       </c>
       <c r="W5" s="1">
-        <v>0.0035743485821720391</v>
+        <v>0.0035744384730242119</v>
       </c>
       <c r="X5" s="1">
-        <v>-0.0012986065817310053</v>
+        <v>-0.0012983044917876446</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.00013911978450791064</v>
+        <v>0.00013912948682769026</v>
       </c>
       <c r="Z5" s="1">
-        <v>-0.0033526085689021276</v>
+        <v>-0.0033527300149531736</v>
       </c>
       <c r="AA5" s="1">
-        <v>-0.00027200605825754016</v>
+        <v>-0.00027197552282913137</v>
       </c>
       <c r="AB5" s="1">
-        <v>-0.00054904823955806577</v>
+        <v>-0.00054902349042574813</v>
       </c>
       <c r="AC5" s="1">
-        <v>0.00021462164673800727</v>
+        <v>0.00021466888148837968</v>
       </c>
       <c r="AD5" s="1">
-        <v>8.8997508597785471e-05</v>
+        <v>8.9021670287227347e-05</v>
       </c>
       <c r="AE5" s="1">
-        <v>-0.00068920773046776869</v>
+        <v>-0.00068922790808510315</v>
       </c>
       <c r="AF5" s="1">
-        <v>-0.00074261486021463287</v>
+        <v>-0.00074263182783332999</v>
       </c>
       <c r="AG5" s="1">
-        <v>-0.00052810991246496233</v>
+        <v>-0.00052813191026200123</v>
       </c>
       <c r="AH5" s="1">
-        <v>-0.00061377970312598783</v>
+        <v>-0.00061378660768325577</v>
       </c>
       <c r="AI5" s="1">
-        <v>2.8263956674194945e-05</v>
+        <v>2.8262430894677129e-05</v>
       </c>
       <c r="AJ5" s="1">
-        <v>-0.0011750187512226927</v>
+        <v>-0.001175206529903489</v>
       </c>
     </row>
     <row r="6">
@@ -1164,109 +1164,109 @@
         <v>32</v>
       </c>
       <c r="B6" s="1">
-        <v>0.68312657235564589</v>
+        <v>0.68312374145496291</v>
       </c>
       <c r="C6" s="1">
-        <v>-0.00013998483852906016</v>
+        <v>-0.00013998340774125335</v>
       </c>
       <c r="D6" s="1">
-        <v>1.9364975840381348e-06</v>
+        <v>1.9364905753540041e-06</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.00027867839756572386</v>
+        <v>-0.00027872907144583771</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.0046383244308215964</v>
+        <v>-0.0046386407676822375</v>
       </c>
       <c r="G6" s="1">
-        <v>0.012538534263899342</v>
+        <v>0.012538952077718921</v>
       </c>
       <c r="H6" s="1">
-        <v>-0.0015697974420815731</v>
+        <v>-0.00157035248335186</v>
       </c>
       <c r="I6" s="1">
-        <v>0.0002757508966080652</v>
+        <v>0.00027558450261466934</v>
       </c>
       <c r="J6" s="1">
-        <v>0.00012460137746396198</v>
+        <v>0.0001243964602294189</v>
       </c>
       <c r="K6" s="1">
-        <v>-8.5261824084378776e-05</v>
+        <v>-8.5472991433263284e-05</v>
       </c>
       <c r="L6" s="1">
-        <v>1.037315374907832e-06</v>
+        <v>1.0372835343913102e-06</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.00073382807309752148</v>
+        <v>-0.00073337930801301834</v>
       </c>
       <c r="N6" s="1">
-        <v>0.0046048708927714684</v>
+        <v>0.0046051864513547841</v>
       </c>
       <c r="O6" s="1">
-        <v>-0.012489113640893394</v>
+        <v>-0.012489518855753492</v>
       </c>
       <c r="P6" s="1">
-        <v>0.0014711210825547759</v>
+        <v>0.001471669729060606</v>
       </c>
       <c r="Q6" s="1">
-        <v>-0.0003705346102551885</v>
+        <v>-0.00037037125058585045</v>
       </c>
       <c r="R6" s="1">
-        <v>-0.0018700280226454046</v>
+        <v>-0.0018704012042237183</v>
       </c>
       <c r="S6" s="1">
-        <v>0.00033323964561803526</v>
+        <v>0.00033322504043537806</v>
       </c>
       <c r="T6" s="1">
-        <v>0.00081592853956486647</v>
+        <v>0.00081593268786342194</v>
       </c>
       <c r="U6" s="1">
-        <v>0.00097945032815097903</v>
+        <v>0.00097958186311035943</v>
       </c>
       <c r="V6" s="1">
-        <v>-0.00030736797364871744</v>
+        <v>-0.00030728834569701031</v>
       </c>
       <c r="W6" s="1">
-        <v>-0.0057129249932653826</v>
+        <v>-0.0057130437672272905</v>
       </c>
       <c r="X6" s="1">
-        <v>0.0010797367122114506</v>
+        <v>0.0010793420177027115</v>
       </c>
       <c r="Y6" s="1">
-        <v>0.00060282801309254378</v>
+        <v>0.00060281469113584714</v>
       </c>
       <c r="Z6" s="1">
-        <v>0.003662310011416813</v>
+        <v>0.0036624717139218232</v>
       </c>
       <c r="AA6" s="1">
-        <v>0.00060357386612478435</v>
+        <v>0.00060353660414547692</v>
       </c>
       <c r="AB6" s="1">
-        <v>5.079873288942513e-05</v>
+        <v>5.0769764369736425e-05</v>
       </c>
       <c r="AC6" s="1">
-        <v>-0.0011106461019369637</v>
+        <v>-0.0011107055319055823</v>
       </c>
       <c r="AD6" s="1">
-        <v>-0.00092497854492216503</v>
+        <v>-0.00092500781081141588</v>
       </c>
       <c r="AE6" s="1">
-        <v>0.00036246944289637818</v>
+        <v>0.00036249608349150068</v>
       </c>
       <c r="AF6" s="1">
-        <v>0.0006706085670580399</v>
+        <v>0.00067063065013258814</v>
       </c>
       <c r="AG6" s="1">
-        <v>0.00054409039338993727</v>
+        <v>0.00054411851541867748</v>
       </c>
       <c r="AH6" s="1">
-        <v>0.00059340243601426975</v>
+        <v>0.00059341155444972221</v>
       </c>
       <c r="AI6" s="1">
-        <v>-4.9085173872531317e-06</v>
+        <v>-4.9064600933876577e-06</v>
       </c>
       <c r="AJ6" s="1">
-        <v>0.003153343902905724</v>
+        <v>0.0031535685407946853</v>
       </c>
     </row>
     <row r="7">
@@ -1274,109 +1274,109 @@
         <v>33</v>
       </c>
       <c r="B7" s="1">
-        <v>0.066454864691687071</v>
+        <v>0.066459830786060825</v>
       </c>
       <c r="C7" s="1">
-        <v>5.2243716594150766e-05</v>
+        <v>5.2244595095198227e-05</v>
       </c>
       <c r="D7" s="1">
-        <v>-7.1257876187118704e-07</v>
+        <v>-7.1260216589030011e-07</v>
       </c>
       <c r="E7" s="1">
-        <v>0.00019035893291415853</v>
+        <v>0.00019042298174276178</v>
       </c>
       <c r="F7" s="1">
-        <v>0.00095977893735323236</v>
+        <v>0.0009602271792811313</v>
       </c>
       <c r="G7" s="1">
-        <v>-0.0015697974420815731</v>
+        <v>-0.00157035248335186</v>
       </c>
       <c r="H7" s="1">
-        <v>0.003979412769398739</v>
+        <v>0.0039795174861654032</v>
       </c>
       <c r="I7" s="1">
-        <v>0.0017114001336788764</v>
+        <v>0.0017112837399241923</v>
       </c>
       <c r="J7" s="1">
-        <v>0.0017379407856503134</v>
+        <v>0.0017378741838945772</v>
       </c>
       <c r="K7" s="1">
-        <v>0.0017067595179708283</v>
+        <v>0.0017067071661352252</v>
       </c>
       <c r="L7" s="1">
-        <v>-5.2458188137569918e-07</v>
+        <v>-5.2456375684694851e-07</v>
       </c>
       <c r="M7" s="1">
-        <v>0.00068082457015849053</v>
+        <v>0.00068029755409085074</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.00093205832065126036</v>
+        <v>-0.00093250681573324576</v>
       </c>
       <c r="O7" s="1">
-        <v>0.001569319215318997</v>
+        <v>0.001569853633891137</v>
       </c>
       <c r="P7" s="1">
-        <v>-0.0039501903968308955</v>
+        <v>-0.0039502804562873504</v>
       </c>
       <c r="Q7" s="1">
-        <v>-0.0016904558285760181</v>
+        <v>-0.0016903346272723638</v>
       </c>
       <c r="R7" s="1">
-        <v>0.0026320020380557665</v>
+        <v>0.0026321582842970181</v>
       </c>
       <c r="S7" s="1">
-        <v>0.00014501086282175127</v>
+        <v>0.00014501015666834371</v>
       </c>
       <c r="T7" s="1">
-        <v>-0.00021078114369537835</v>
+        <v>-0.0002108222183750388</v>
       </c>
       <c r="U7" s="1">
-        <v>-0.00034733730726302695</v>
+        <v>-0.0003474965757822785</v>
       </c>
       <c r="V7" s="1">
-        <v>-7.0361546271750287e-06</v>
+        <v>-7.1482463312627946e-06</v>
       </c>
       <c r="W7" s="1">
-        <v>0.0014792156226646909</v>
+        <v>0.0014794582710462799</v>
       </c>
       <c r="X7" s="1">
-        <v>-0.00088580594736052231</v>
+        <v>-0.00088535264409792046</v>
       </c>
       <c r="Y7" s="1">
-        <v>4.5675007195362049e-05</v>
+        <v>4.5692534344414048e-05</v>
       </c>
       <c r="Z7" s="1">
-        <v>-0.0011496162036902613</v>
+        <v>-0.0011498798556034979</v>
       </c>
       <c r="AA7" s="1">
-        <v>0.001488159077545758</v>
+        <v>0.0014881206838272838</v>
       </c>
       <c r="AB7" s="1">
-        <v>0.0012909200246827952</v>
+        <v>0.0012908781300790455</v>
       </c>
       <c r="AC7" s="1">
-        <v>0.001280286357059708</v>
+        <v>0.0012803152604903157</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.0013333477758047602</v>
+        <v>0.0013333321402453685</v>
       </c>
       <c r="AE7" s="1">
-        <v>-0.00022764615778182317</v>
+        <v>-0.0002276934939397725</v>
       </c>
       <c r="AF7" s="1">
-        <v>-0.00015800481647704591</v>
+        <v>-0.00015804634116542741</v>
       </c>
       <c r="AG7" s="1">
-        <v>-0.00052665838886137338</v>
+        <v>-0.00052667882768670632</v>
       </c>
       <c r="AH7" s="1">
-        <v>-0.00032616092452972516</v>
+        <v>-0.00032618408341076569</v>
       </c>
       <c r="AI7" s="1">
-        <v>1.741585922386649e-05</v>
+        <v>1.741361451819347e-05</v>
       </c>
       <c r="AJ7" s="1">
-        <v>-0.0041704967322112648</v>
+        <v>-0.0041704531396316007</v>
       </c>
     </row>
     <row r="8">
@@ -1384,109 +1384,109 @@
         <v>34</v>
       </c>
       <c r="B8" s="1">
-        <v>0.13707753156077457</v>
+        <v>0.13707958391939079</v>
       </c>
       <c r="C8" s="1">
-        <v>3.9976930654169856e-05</v>
+        <v>3.9978535171493793e-05</v>
       </c>
       <c r="D8" s="1">
-        <v>-3.9660355741430841e-07</v>
+        <v>-3.9662686978448665e-07</v>
       </c>
       <c r="E8" s="1">
-        <v>-5.9647707198464631e-05</v>
+        <v>-5.962778710002958e-05</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.0009992884764051409</v>
+        <v>-0.00099914765577706994</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0002757508966080652</v>
+        <v>0.00027558450261466934</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0017114001336788764</v>
+        <v>0.0017112837399241923</v>
       </c>
       <c r="I8" s="1">
-        <v>0.004711389618193236</v>
+        <v>0.0047112705432928986</v>
       </c>
       <c r="J8" s="1">
-        <v>0.0034819370519951097</v>
+        <v>0.0034818312025404422</v>
       </c>
       <c r="K8" s="1">
-        <v>0.0034869025873250038</v>
+        <v>0.0034868019627523278</v>
       </c>
       <c r="L8" s="1">
-        <v>-7.2385757696322111e-07</v>
+        <v>-7.2386437956098698e-07</v>
       </c>
       <c r="M8" s="1">
-        <v>0.0014270840841693628</v>
+        <v>0.0014269388288880706</v>
       </c>
       <c r="N8" s="1">
-        <v>0.0010031426474713082</v>
+        <v>0.0010030016475293566</v>
       </c>
       <c r="O8" s="1">
-        <v>-0.00026833107522518688</v>
+        <v>-0.00026817277955142288</v>
       </c>
       <c r="P8" s="1">
-        <v>-0.0017073359197908428</v>
+        <v>-0.0017072126881385308</v>
       </c>
       <c r="Q8" s="1">
-        <v>-0.0047094338044225753</v>
+        <v>-0.0047093130948772759</v>
       </c>
       <c r="R8" s="1">
-        <v>0.0019346355101348611</v>
+        <v>0.0019346073941537891</v>
       </c>
       <c r="S8" s="1">
-        <v>-6.6709193365269951e-05</v>
+        <v>-6.6713293915070053e-05</v>
       </c>
       <c r="T8" s="1">
-        <v>0.00056370459443238347</v>
+        <v>0.00056367811840290344</v>
       </c>
       <c r="U8" s="1">
-        <v>0.0020007433476945972</v>
+        <v>0.0020006945575810403</v>
       </c>
       <c r="V8" s="1">
-        <v>0.0018998803956907944</v>
+        <v>0.0018998436807964958</v>
       </c>
       <c r="W8" s="1">
-        <v>0.0013922391631048595</v>
+        <v>0.0013923454247804839</v>
       </c>
       <c r="X8" s="1">
-        <v>-0.0013621364771101221</v>
+        <v>-0.001362015941516595</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.00055085573727041144</v>
+        <v>0.0005508609500596384</v>
       </c>
       <c r="Z8" s="1">
-        <v>0.00099958091079303921</v>
+        <v>0.00099947932137634714</v>
       </c>
       <c r="AA8" s="1">
-        <v>0.0013055376981238617</v>
+        <v>0.001305511867321525</v>
       </c>
       <c r="AB8" s="1">
-        <v>0.00095366583503762067</v>
+        <v>0.00095363937490805777</v>
       </c>
       <c r="AC8" s="1">
-        <v>0.00089052257459676658</v>
+        <v>0.00089052550820354454</v>
       </c>
       <c r="AD8" s="1">
-        <v>0.0011087375670186116</v>
+        <v>0.0011087260215954862</v>
       </c>
       <c r="AE8" s="1">
-        <v>0.00018515964929681863</v>
+        <v>0.0001851409498239585</v>
       </c>
       <c r="AF8" s="1">
-        <v>0.00014858417056414852</v>
+        <v>0.00014856841844449538</v>
       </c>
       <c r="AG8" s="1">
-        <v>-0.00020112699055516723</v>
+        <v>-0.00020113127159360937</v>
       </c>
       <c r="AH8" s="1">
-        <v>-8.2837029022211385e-05</v>
+        <v>-8.2849051703585063e-05</v>
       </c>
       <c r="AI8" s="1">
-        <v>-1.1382031392512905e-05</v>
+        <v>-1.1382495404554734e-05</v>
       </c>
       <c r="AJ8" s="1">
-        <v>-0.0050700104057033457</v>
+        <v>-0.0050699305737094292</v>
       </c>
     </row>
     <row r="9">
@@ -1494,109 +1494,109 @@
         <v>35</v>
       </c>
       <c r="B9" s="1">
-        <v>0.19324789380895607</v>
+        <v>0.19325023522355098</v>
       </c>
       <c r="C9" s="1">
-        <v>-2.8204369602493836e-05</v>
+        <v>-2.8202526391531179e-05</v>
       </c>
       <c r="D9" s="1">
-        <v>4.9287103980716147e-07</v>
+        <v>4.9284394345285094e-07</v>
       </c>
       <c r="E9" s="1">
-        <v>0.00018601438507195167</v>
+        <v>0.00018603838465634326</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.00055843227725555986</v>
+        <v>-0.00055826282276097568</v>
       </c>
       <c r="G9" s="1">
-        <v>0.00012460137746396198</v>
+        <v>0.0001243964602294189</v>
       </c>
       <c r="H9" s="1">
-        <v>0.0017379407856503134</v>
+        <v>0.0017378741838945772</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0034819370519951097</v>
+        <v>0.0034818312025404422</v>
       </c>
       <c r="J9" s="1">
-        <v>0.0047023236639651134</v>
+        <v>0.0047022338334022805</v>
       </c>
       <c r="K9" s="1">
-        <v>0.0037600150946747596</v>
+        <v>0.0037599310129370223</v>
       </c>
       <c r="L9" s="1">
-        <v>1.0435732992641255e-08</v>
+        <v>1.042787316448928e-08</v>
       </c>
       <c r="M9" s="1">
-        <v>0.0014075010316592165</v>
+        <v>0.0014073233157437931</v>
       </c>
       <c r="N9" s="1">
-        <v>0.00056550894896002942</v>
+        <v>0.00056533943955032842</v>
       </c>
       <c r="O9" s="1">
-        <v>-7.4767172308181501e-05</v>
+        <v>-7.4571543077473997e-05</v>
       </c>
       <c r="P9" s="1">
-        <v>-0.0016398251582653608</v>
+        <v>-0.0016397509598989361</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.0034658311367286926</v>
+        <v>-0.0034657233561023533</v>
       </c>
       <c r="R9" s="1">
-        <v>0.0016890260551520411</v>
+        <v>0.0016890333024401642</v>
       </c>
       <c r="S9" s="1">
-        <v>-0.00022504971246903679</v>
+        <v>-0.00022505293278313421</v>
       </c>
       <c r="T9" s="1">
-        <v>0.00018699308905809569</v>
+        <v>0.00018696433573911085</v>
       </c>
       <c r="U9" s="1">
-        <v>0.0020852839105369382</v>
+        <v>0.0020852217183651473</v>
       </c>
       <c r="V9" s="1">
-        <v>0.0022039971738406923</v>
+        <v>0.0022039524436357296</v>
       </c>
       <c r="W9" s="1">
-        <v>0.0013101882111798879</v>
+        <v>0.0013103094283483539</v>
       </c>
       <c r="X9" s="1">
-        <v>-0.0016580897846829911</v>
+        <v>-0.0016579413131395302</v>
       </c>
       <c r="Y9" s="1">
-        <v>0.00026266422473716</v>
+        <v>0.00026267072954944918</v>
       </c>
       <c r="Z9" s="1">
-        <v>0.00022785974371266867</v>
+        <v>0.00022774070461687801</v>
       </c>
       <c r="AA9" s="1">
-        <v>0.0017355079428353437</v>
+        <v>0.0017354861416748555</v>
       </c>
       <c r="AB9" s="1">
-        <v>0.00080027025396507494</v>
+        <v>0.00080024710286813417</v>
       </c>
       <c r="AC9" s="1">
-        <v>0.00051708052606190395</v>
+        <v>0.00051709016351411013</v>
       </c>
       <c r="AD9" s="1">
-        <v>0.00094024159745541747</v>
+        <v>0.00094023421966154923</v>
       </c>
       <c r="AE9" s="1">
-        <v>-0.00015824604240486598</v>
+        <v>-0.0001582678783063271</v>
       </c>
       <c r="AF9" s="1">
-        <v>-6.9300398554017484e-05</v>
+        <v>-6.9318641952183756e-05</v>
       </c>
       <c r="AG9" s="1">
-        <v>-0.00054973084875415529</v>
+        <v>-0.00054973821265992106</v>
       </c>
       <c r="AH9" s="1">
-        <v>-0.00023504201985235867</v>
+        <v>-0.00023505605931662017</v>
       </c>
       <c r="AI9" s="1">
-        <v>1.6892235833482138e-05</v>
+        <v>1.6891683437225403e-05</v>
       </c>
       <c r="AJ9" s="1">
-        <v>-0.0042334005449576658</v>
+        <v>-0.0042333473785687919</v>
       </c>
     </row>
     <row r="10">
@@ -1604,109 +1604,109 @@
         <v>36</v>
       </c>
       <c r="B10" s="1">
-        <v>0.24865065737709868</v>
+        <v>0.24865303548464432</v>
       </c>
       <c r="C10" s="1">
-        <v>-2.5335394036607678e-05</v>
+        <v>-2.5333575131431787e-05</v>
       </c>
       <c r="D10" s="1">
-        <v>1.0275124607310917e-07</v>
+        <v>1.0272433494008275e-07</v>
       </c>
       <c r="E10" s="1">
-        <v>-2.4517015897646856e-05</v>
+        <v>-2.4492310394911253e-05</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.00047086266590333698</v>
+        <v>-0.00047068848261181149</v>
       </c>
       <c r="G10" s="1">
-        <v>-8.5261824084378776e-05</v>
+        <v>-8.5472991433263284e-05</v>
       </c>
       <c r="H10" s="1">
-        <v>0.0017067595179708283</v>
+        <v>0.0017067071661352252</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0034869025873250038</v>
+        <v>0.0034868019627523278</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0037600150946747596</v>
+        <v>0.0037599310129370223</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0055684634704204535</v>
+        <v>0.005568385051673664</v>
       </c>
       <c r="L10" s="1">
-        <v>3.9619992555178538e-07</v>
+        <v>3.9619265814578576e-07</v>
       </c>
       <c r="M10" s="1">
-        <v>0.0014422194831362057</v>
+        <v>0.0014420334946889934</v>
       </c>
       <c r="N10" s="1">
-        <v>0.00048397931343819813</v>
+        <v>0.00048380508951871348</v>
       </c>
       <c r="O10" s="1">
-        <v>8.8794896298132831e-05</v>
+        <v>8.8996571445917861e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>-0.0016377252149076184</v>
+        <v>-0.0016376651709522267</v>
       </c>
       <c r="Q10" s="1">
-        <v>-0.0034788730617994409</v>
+        <v>-0.0034787704794699168</v>
       </c>
       <c r="R10" s="1">
-        <v>0.0015682641419355312</v>
+        <v>0.0015682808384390227</v>
       </c>
       <c r="S10" s="1">
-        <v>-0.00075745607570977297</v>
+        <v>-0.00075745883223086248</v>
       </c>
       <c r="T10" s="1">
-        <v>0.0002478261232163374</v>
+        <v>0.00024779723191825284</v>
       </c>
       <c r="U10" s="1">
-        <v>0.0016535279141053228</v>
+        <v>0.0016534625969280695</v>
       </c>
       <c r="V10" s="1">
-        <v>0.0022486683515078368</v>
+        <v>0.0022486218894221823</v>
       </c>
       <c r="W10" s="1">
-        <v>0.0026544300983962496</v>
+        <v>0.0026545528042873669</v>
       </c>
       <c r="X10" s="1">
-        <v>-0.001451262510249515</v>
+        <v>-0.001451106528047876</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.00044895249355682103</v>
+        <v>0.00044895927714875416</v>
       </c>
       <c r="Z10" s="1">
-        <v>0.00041184559005387586</v>
+        <v>0.00041172417690653492</v>
       </c>
       <c r="AA10" s="1">
-        <v>0.00083647023838219091</v>
+        <v>0.00083644848811074415</v>
       </c>
       <c r="AB10" s="1">
-        <v>0.00075503785750727294</v>
+        <v>0.00075501471886707202</v>
       </c>
       <c r="AC10" s="1">
-        <v>0.00047936991272410907</v>
+        <v>0.00047938011654964505</v>
       </c>
       <c r="AD10" s="1">
-        <v>0.00070862514206416615</v>
+        <v>0.00070861775940705344</v>
       </c>
       <c r="AE10" s="1">
-        <v>-0.00011139281263663537</v>
+        <v>-0.00011141497727708239</v>
       </c>
       <c r="AF10" s="1">
-        <v>5.1587903793503978e-05</v>
+        <v>5.1569399446359352e-05</v>
       </c>
       <c r="AG10" s="1">
-        <v>-0.00036123603703072356</v>
+        <v>-0.00036124367583604243</v>
       </c>
       <c r="AH10" s="1">
-        <v>-0.00010943466550209239</v>
+        <v>-0.00010944867271054238</v>
       </c>
       <c r="AI10" s="1">
-        <v>6.92294932858807e-06</v>
+        <v>6.9223646815861164e-06</v>
       </c>
       <c r="AJ10" s="1">
-        <v>-0.0035354693203620263</v>
+        <v>-0.003535421964164176</v>
       </c>
     </row>
     <row r="11">
@@ -1714,109 +1714,109 @@
         <v>37</v>
       </c>
       <c r="B11" s="1">
-        <v>0.0014579031941996223</v>
+        <v>0.0014579038799378025</v>
       </c>
       <c r="C11" s="1">
-        <v>-6.3598494578199495e-07</v>
+        <v>-6.3598245064984389e-07</v>
       </c>
       <c r="D11" s="1">
-        <v>7.0085726881803537e-09</v>
+        <v>7.0085409282790471e-09</v>
       </c>
       <c r="E11" s="1">
-        <v>-2.1188177960275384e-07</v>
+        <v>-2.1187905009502996e-07</v>
       </c>
       <c r="F11" s="1">
-        <v>-6.0658240081193661e-07</v>
+        <v>-6.0655848357436849e-07</v>
       </c>
       <c r="G11" s="1">
-        <v>1.037315374907832e-06</v>
+        <v>1.0372835343913102e-06</v>
       </c>
       <c r="H11" s="1">
-        <v>-5.2458188137569918e-07</v>
+        <v>-5.2456375684694851e-07</v>
       </c>
       <c r="I11" s="1">
-        <v>-7.2385757696322111e-07</v>
+        <v>-7.2386437956098698e-07</v>
       </c>
       <c r="J11" s="1">
-        <v>1.0435732992641255e-08</v>
+        <v>1.042787316448928e-08</v>
       </c>
       <c r="K11" s="1">
-        <v>3.9619992555178538e-07</v>
+        <v>3.9619265814578576e-07</v>
       </c>
       <c r="L11" s="1">
-        <v>4.8086672709593773e-07</v>
+        <v>4.8086668990035653e-07</v>
       </c>
       <c r="M11" s="1">
-        <v>-6.1390495348876683e-05</v>
+        <v>-6.1390473757683955e-05</v>
       </c>
       <c r="N11" s="1">
-        <v>3.4548189681729344e-05</v>
+        <v>3.4548165068307671e-05</v>
       </c>
       <c r="O11" s="1">
-        <v>-7.3917545360339994e-05</v>
+        <v>-7.3917510065609043e-05</v>
       </c>
       <c r="P11" s="1">
-        <v>6.814589166844079e-05</v>
+        <v>6.8145870560717948e-05</v>
       </c>
       <c r="Q11" s="1">
-        <v>1.4579569372008766e-05</v>
+        <v>1.4579577990524937e-05</v>
       </c>
       <c r="R11" s="1">
-        <v>-0.00023368644689902184</v>
+        <v>-0.00023368641673406933</v>
       </c>
       <c r="S11" s="1">
-        <v>3.8953905999880786e-07</v>
+        <v>3.8953787815550023e-07</v>
       </c>
       <c r="T11" s="1">
-        <v>-6.820218795580135e-07</v>
+        <v>-6.8203769975392545e-07</v>
       </c>
       <c r="U11" s="1">
-        <v>-2.0075991762970689e-06</v>
+        <v>-2.0076084806563729e-06</v>
       </c>
       <c r="V11" s="1">
-        <v>-1.1062979733058719e-06</v>
+        <v>-1.1063031185336115e-06</v>
       </c>
       <c r="W11" s="1">
-        <v>-3.3825335208490267e-06</v>
+        <v>-3.3824762386758957e-06</v>
       </c>
       <c r="X11" s="1">
-        <v>-3.6774796490244396e-07</v>
+        <v>-3.6776831228817367e-07</v>
       </c>
       <c r="Y11" s="1">
-        <v>4.7365960229092957e-07</v>
+        <v>4.7366053320317197e-07</v>
       </c>
       <c r="Z11" s="1">
-        <v>5.9722822623204095e-07</v>
+        <v>5.9718811890069531e-07</v>
       </c>
       <c r="AA11" s="1">
-        <v>-1.0499503897081166e-06</v>
+        <v>-1.0499426511538353e-06</v>
       </c>
       <c r="AB11" s="1">
-        <v>-2.0981157616178544e-06</v>
+        <v>-2.0981096692396596e-06</v>
       </c>
       <c r="AC11" s="1">
-        <v>-2.4346361735282315e-06</v>
+        <v>-2.4346223368784393e-06</v>
       </c>
       <c r="AD11" s="1">
-        <v>-4.5235708657253057e-06</v>
+        <v>-4.5235570759690248e-06</v>
       </c>
       <c r="AE11" s="1">
-        <v>4.4400896091903215e-06</v>
+        <v>4.4400809961128004e-06</v>
       </c>
       <c r="AF11" s="1">
-        <v>4.292905518051713e-07</v>
+        <v>4.2928444219119012e-07</v>
       </c>
       <c r="AG11" s="1">
-        <v>7.5330351062645062e-07</v>
+        <v>7.5329654653562808e-07</v>
       </c>
       <c r="AH11" s="1">
-        <v>1.077298916194304e-06</v>
+        <v>1.0772886760087006e-06</v>
       </c>
       <c r="AI11" s="1">
-        <v>-1.095475173806463e-07</v>
+        <v>-1.0954698894729772e-07</v>
       </c>
       <c r="AJ11" s="1">
-        <v>1.6779554080713748e-05</v>
+        <v>1.6779497768927856e-05</v>
       </c>
     </row>
     <row r="12">
@@ -1824,109 +1824,109 @@
         <v>38</v>
       </c>
       <c r="B12" s="1">
-        <v>-0.28998511618724271</v>
+        <v>-0.28998884622214782</v>
       </c>
       <c r="C12" s="1">
-        <v>-4.4523709050523245e-05</v>
+        <v>-4.4527168894267647e-05</v>
       </c>
       <c r="D12" s="1">
-        <v>4.2679394562569333e-07</v>
+        <v>4.2684847013249517e-07</v>
       </c>
       <c r="E12" s="1">
-        <v>9.3921477680512615e-06</v>
+        <v>9.3424874144738736e-06</v>
       </c>
       <c r="F12" s="1">
-        <v>0.00064215242728752112</v>
+        <v>0.00064181005055088036</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00073382807309752148</v>
+        <v>-0.00073337930801301834</v>
       </c>
       <c r="H12" s="1">
-        <v>0.00068082457015849053</v>
+        <v>0.00068029755409085074</v>
       </c>
       <c r="I12" s="1">
-        <v>0.0014270840841693628</v>
+        <v>0.0014269388288880706</v>
       </c>
       <c r="J12" s="1">
-        <v>0.0014075010316592165</v>
+        <v>0.0014073233157437931</v>
       </c>
       <c r="K12" s="1">
-        <v>0.0014422194831362057</v>
+        <v>0.0014420334946889934</v>
       </c>
       <c r="L12" s="1">
-        <v>-6.1390495348876683e-05</v>
+        <v>-6.1390473757683955e-05</v>
       </c>
       <c r="M12" s="1">
-        <v>0.065340114384321829</v>
+        <v>0.065339989988436556</v>
       </c>
       <c r="N12" s="1">
-        <v>-0.0091167393760310973</v>
+        <v>-0.0091163986873618336</v>
       </c>
       <c r="O12" s="1">
-        <v>0.030800730135419421</v>
+        <v>0.030800291688868955</v>
       </c>
       <c r="P12" s="1">
-        <v>-0.025421848232910649</v>
+        <v>-0.025421330055484592</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.0063069182350576772</v>
+        <v>0.0063070603091155593</v>
       </c>
       <c r="R12" s="1">
-        <v>0.018892821430879822</v>
+        <v>0.018892451525439988</v>
       </c>
       <c r="S12" s="1">
-        <v>-6.176434106275848e-05</v>
+        <v>-6.1767966233298389e-05</v>
       </c>
       <c r="T12" s="1">
-        <v>0.00097810595156381228</v>
+        <v>0.00097813866764100144</v>
       </c>
       <c r="U12" s="1">
-        <v>0.0084581387276010753</v>
+        <v>0.0084582596397184909</v>
       </c>
       <c r="V12" s="1">
-        <v>0.00047431467590572271</v>
+        <v>0.00047438347627766172</v>
       </c>
       <c r="W12" s="1">
-        <v>0.00098362939669067984</v>
+        <v>0.00098336708020826317</v>
       </c>
       <c r="X12" s="1">
-        <v>-0.029357524460412079</v>
+        <v>-0.029357344794247932</v>
       </c>
       <c r="Y12" s="1">
-        <v>5.9547085243396235e-05</v>
+        <v>5.9531254594118624e-05</v>
       </c>
       <c r="Z12" s="1">
-        <v>-0.00027285155723447667</v>
+        <v>-0.00027259908329353813</v>
       </c>
       <c r="AA12" s="1">
-        <v>-0.00010330384485770578</v>
+        <v>-0.00010335621668164832</v>
       </c>
       <c r="AB12" s="1">
-        <v>0.00012965033361487074</v>
+        <v>0.00012961004372782534</v>
       </c>
       <c r="AC12" s="1">
-        <v>-0.00015856665579679389</v>
+        <v>-0.00015865385418542037</v>
       </c>
       <c r="AD12" s="1">
-        <v>0.0003414405195197454</v>
+        <v>0.00034137712015042148</v>
       </c>
       <c r="AE12" s="1">
-        <v>-0.00058770407094079456</v>
+        <v>-0.00058765735309021148</v>
       </c>
       <c r="AF12" s="1">
-        <v>-0.00083940235688644764</v>
+        <v>-0.00083935554587755774</v>
       </c>
       <c r="AG12" s="1">
-        <v>-0.0015312475788527139</v>
+        <v>-0.0015311927441856647</v>
       </c>
       <c r="AH12" s="1">
-        <v>-0.00040689007326995258</v>
+        <v>-0.00040685291637317328</v>
       </c>
       <c r="AI12" s="1">
-        <v>7.8180339552315871e-05</v>
+        <v>7.8179977916636271e-05</v>
       </c>
       <c r="AJ12" s="1">
-        <v>-0.0013021000706258184</v>
+        <v>-0.0013017685543056099</v>
       </c>
     </row>
     <row r="13">
@@ -1934,109 +1934,109 @@
         <v>39</v>
       </c>
       <c r="B13" s="1">
-        <v>-0.11819683813811714</v>
+        <v>-0.11819902361521832</v>
       </c>
       <c r="C13" s="1">
-        <v>-5.7228304060927195e-05</v>
+        <v>-5.7227342843701318e-05</v>
       </c>
       <c r="D13" s="1">
-        <v>7.2068448689796629e-07</v>
+        <v>7.2068097618752903e-07</v>
       </c>
       <c r="E13" s="1">
-        <v>-0.00059293813692799042</v>
+        <v>-0.00059297580610242324</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.003879296986032709</v>
+        <v>-0.0038795319336844751</v>
       </c>
       <c r="G13" s="1">
-        <v>0.0046048708927714684</v>
+        <v>0.0046051864513547841</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.00093205832065126036</v>
+        <v>-0.00093250681573324576</v>
       </c>
       <c r="I13" s="1">
-        <v>0.0010031426474713082</v>
+        <v>0.0010030016475293566</v>
       </c>
       <c r="J13" s="1">
-        <v>0.00056550894896002942</v>
+        <v>0.00056533943955032842</v>
       </c>
       <c r="K13" s="1">
-        <v>0.00048397931343819813</v>
+        <v>0.00048380508951871348</v>
       </c>
       <c r="L13" s="1">
-        <v>3.4548189681729344e-05</v>
+        <v>3.4548165068307671e-05</v>
       </c>
       <c r="M13" s="1">
-        <v>-0.0091167393760310973</v>
+        <v>-0.0091163986873618336</v>
       </c>
       <c r="N13" s="1">
-        <v>0.02497890062760404</v>
+        <v>0.024979136876897227</v>
       </c>
       <c r="O13" s="1">
-        <v>0.0054033869681344967</v>
+        <v>0.005403083609882048</v>
       </c>
       <c r="P13" s="1">
-        <v>0.0048469266433898662</v>
+        <v>0.0048473697012543756</v>
       </c>
       <c r="Q13" s="1">
-        <v>-0.014772718844316945</v>
+        <v>-0.01477258075743995</v>
       </c>
       <c r="R13" s="1">
-        <v>-0.017697155964573812</v>
+        <v>-0.017697452999373874</v>
       </c>
       <c r="S13" s="1">
-        <v>0.00019628192209902165</v>
+        <v>0.00019627055483887381</v>
       </c>
       <c r="T13" s="1">
-        <v>0.00096237607915258827</v>
+        <v>0.00096237875483315308</v>
       </c>
       <c r="U13" s="1">
-        <v>0.0011384981536497597</v>
+        <v>0.0011385983891550942</v>
       </c>
       <c r="V13" s="1">
-        <v>0.00082197941495750361</v>
+        <v>0.00082203897640036267</v>
       </c>
       <c r="W13" s="1">
-        <v>-0.003457545898593773</v>
+        <v>-0.0034576362550748402</v>
       </c>
       <c r="X13" s="1">
-        <v>0.0012411751242396769</v>
+        <v>0.001240874794085354</v>
       </c>
       <c r="Y13" s="1">
-        <v>-0.00013199076244257895</v>
+        <v>-0.0001320004454140593</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.0033274927763847001</v>
+        <v>0.0033276143778159027</v>
       </c>
       <c r="AA13" s="1">
-        <v>0.00030208119971852232</v>
+        <v>0.00030205075697256926</v>
       </c>
       <c r="AB13" s="1">
-        <v>0.0006588108616217759</v>
+        <v>0.00065878614965971525</v>
       </c>
       <c r="AC13" s="1">
-        <v>-6.0746357221063579e-05</v>
+        <v>-6.0793594877364598e-05</v>
       </c>
       <c r="AD13" s="1">
-        <v>-7.7309386278263758e-05</v>
+        <v>-7.7333597548716101e-05</v>
       </c>
       <c r="AE13" s="1">
-        <v>0.0010486135199391446</v>
+        <v>0.0010486336585187345</v>
       </c>
       <c r="AF13" s="1">
-        <v>0.00090958295402581487</v>
+        <v>0.00090959987842161385</v>
       </c>
       <c r="AG13" s="1">
-        <v>0.00060365429806158129</v>
+        <v>0.0006036763224574256</v>
       </c>
       <c r="AH13" s="1">
-        <v>0.00065404642993176253</v>
+        <v>0.0006540534486385067</v>
       </c>
       <c r="AI13" s="1">
-        <v>-3.4080275595777481e-05</v>
+        <v>-3.4078760430860555e-05</v>
       </c>
       <c r="AJ13" s="1">
-        <v>0.0010170009906308327</v>
+        <v>0.0010171896024913155</v>
       </c>
     </row>
     <row r="14">
@@ -2044,109 +2044,109 @@
         <v>40</v>
       </c>
       <c r="B14" s="1">
-        <v>-0.15883592619052253</v>
+        <v>-0.15883312739528122</v>
       </c>
       <c r="C14" s="1">
-        <v>0.00015399678834331212</v>
+        <v>0.00015399549930996125</v>
       </c>
       <c r="D14" s="1">
-        <v>-1.9844840922676206e-06</v>
+        <v>-1.9844786512222254e-06</v>
       </c>
       <c r="E14" s="1">
-        <v>0.00022455807826074657</v>
+        <v>0.00022460739237397919</v>
       </c>
       <c r="F14" s="1">
-        <v>0.0046884330391518082</v>
+        <v>0.0046887397131640321</v>
       </c>
       <c r="G14" s="1">
-        <v>-0.012489113640893394</v>
+        <v>-0.012489518855753492</v>
       </c>
       <c r="H14" s="1">
-        <v>0.001569319215318997</v>
+        <v>0.001569853633891137</v>
       </c>
       <c r="I14" s="1">
-        <v>-0.00026833107522518688</v>
+        <v>-0.00026817277955142288</v>
       </c>
       <c r="J14" s="1">
-        <v>-7.4767172308181501e-05</v>
+        <v>-7.4571543077473997e-05</v>
       </c>
       <c r="K14" s="1">
-        <v>8.8794896298132831e-05</v>
+        <v>8.8996571445917861e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>-7.3917545360339994e-05</v>
+        <v>-7.3917510065609043e-05</v>
       </c>
       <c r="M14" s="1">
-        <v>0.030800730135419421</v>
+        <v>0.030800291688868955</v>
       </c>
       <c r="N14" s="1">
-        <v>0.0054033869681344967</v>
+        <v>0.005403083609882048</v>
       </c>
       <c r="O14" s="1">
-        <v>0.088089263691746508</v>
+        <v>0.088089657450582573</v>
       </c>
       <c r="P14" s="1">
-        <v>-0.025589094981404954</v>
+        <v>-0.025589620671988351</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.01233948774700726</v>
+        <v>0.012339332424850051</v>
       </c>
       <c r="R14" s="1">
-        <v>0.028088150710230627</v>
+        <v>0.02808850827922485</v>
       </c>
       <c r="S14" s="1">
-        <v>-0.00044569076007832574</v>
+        <v>-0.00044567648288913617</v>
       </c>
       <c r="T14" s="1">
-        <v>-0.00087221076685668904</v>
+        <v>-0.00087221551062518761</v>
       </c>
       <c r="U14" s="1">
-        <v>-0.0011379766775325977</v>
+        <v>-0.001138105202561183</v>
       </c>
       <c r="V14" s="1">
-        <v>0.00040641958202692832</v>
+        <v>0.00040634183703845824</v>
       </c>
       <c r="W14" s="1">
-        <v>0.005655981745952182</v>
+        <v>0.005656099228844763</v>
       </c>
       <c r="X14" s="1">
-        <v>-0.0012436206037002926</v>
+        <v>-0.0012432362646927699</v>
       </c>
       <c r="Y14" s="1">
-        <v>-0.00067299511176233074</v>
+        <v>-0.0006729821067201861</v>
       </c>
       <c r="Z14" s="1">
-        <v>-0.0036351044226085498</v>
+        <v>-0.0036352630117154729</v>
       </c>
       <c r="AA14" s="1">
-        <v>-0.00019292040331069389</v>
+        <v>-0.00019288289876176565</v>
       </c>
       <c r="AB14" s="1">
-        <v>0.00010537515792540115</v>
+        <v>0.00010540461684662774</v>
       </c>
       <c r="AC14" s="1">
-        <v>0.0011343643529397095</v>
+        <v>0.0011344237115292494</v>
       </c>
       <c r="AD14" s="1">
-        <v>0.0021325859165402337</v>
+        <v>0.0021326155523656008</v>
       </c>
       <c r="AE14" s="1">
-        <v>-0.0013368946061808468</v>
+        <v>-0.0013369206528558528</v>
       </c>
       <c r="AF14" s="1">
-        <v>-0.00099755028886579179</v>
+        <v>-0.00099757173653873413</v>
       </c>
       <c r="AG14" s="1">
-        <v>-0.00055831274026123582</v>
+        <v>-0.000558340294624602</v>
       </c>
       <c r="AH14" s="1">
-        <v>-0.00082746801792375247</v>
+        <v>-0.00082747705981522923</v>
       </c>
       <c r="AI14" s="1">
-        <v>0.0001052582253889805</v>
+        <v>0.00010525621071217467</v>
       </c>
       <c r="AJ14" s="1">
-        <v>-0.0053909412826583193</v>
+        <v>-0.00539115883428847</v>
       </c>
     </row>
     <row r="15">
@@ -2154,109 +2154,109 @@
         <v>41</v>
       </c>
       <c r="B15" s="1">
-        <v>0.15599831811408837</v>
+        <v>0.15599332642255256</v>
       </c>
       <c r="C15" s="1">
-        <v>-6.3297231391195728e-05</v>
+        <v>-6.32983525634668e-05</v>
       </c>
       <c r="D15" s="1">
-        <v>8.3256089161760051e-07</v>
+        <v>8.3258717768035957e-07</v>
       </c>
       <c r="E15" s="1">
-        <v>-0.00015186954876649926</v>
+        <v>-0.00015193298706182309</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.00089875314838740118</v>
+        <v>-0.00089919654613862055</v>
       </c>
       <c r="G15" s="1">
-        <v>0.0014711210825547759</v>
+        <v>0.001471669729060606</v>
       </c>
       <c r="H15" s="1">
-        <v>-0.0039501903968308955</v>
+        <v>-0.0039502804562873504</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.0017073359197908428</v>
+        <v>-0.0017072126881385308</v>
       </c>
       <c r="J15" s="1">
-        <v>-0.0016398251582653608</v>
+        <v>-0.0016397509598989361</v>
       </c>
       <c r="K15" s="1">
-        <v>-0.0016377252149076184</v>
+        <v>-0.0016376651709522267</v>
       </c>
       <c r="L15" s="1">
-        <v>6.814589166844079e-05</v>
+        <v>6.8145870560717948e-05</v>
       </c>
       <c r="M15" s="1">
-        <v>-0.025421848232910649</v>
+        <v>-0.025421330055484592</v>
       </c>
       <c r="N15" s="1">
-        <v>0.0048469266433898662</v>
+        <v>0.0048473697012543756</v>
       </c>
       <c r="O15" s="1">
-        <v>-0.025589094981404954</v>
+        <v>-0.025589620671988351</v>
       </c>
       <c r="P15" s="1">
-        <v>0.051295699076266223</v>
+        <v>0.051295772284278375</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.021933837896391854</v>
+        <v>0.021933709850580192</v>
       </c>
       <c r="R15" s="1">
-        <v>-0.047734626316777828</v>
+        <v>-0.04773477173098329</v>
       </c>
       <c r="S15" s="1">
-        <v>-0.00013744956687957666</v>
+        <v>-0.00013744848391020599</v>
       </c>
       <c r="T15" s="1">
-        <v>0.00013997237897785591</v>
+        <v>0.00014001499820291349</v>
       </c>
       <c r="U15" s="1">
-        <v>0.0004495454932061777</v>
+        <v>0.00044970276732439517</v>
       </c>
       <c r="V15" s="1">
-        <v>-4.8820224108188045e-06</v>
+        <v>-4.7711235332904888e-06</v>
       </c>
       <c r="W15" s="1">
-        <v>-0.001412406167629365</v>
+        <v>-0.0014126522940104882</v>
       </c>
       <c r="X15" s="1">
-        <v>0.00083571331436946121</v>
+        <v>0.00083527155546368878</v>
       </c>
       <c r="Y15" s="1">
-        <v>-5.3466156708424943e-05</v>
+        <v>-5.3483495606702273e-05</v>
       </c>
       <c r="Z15" s="1">
-        <v>0.0010499349485416098</v>
+        <v>0.0010501997132169075</v>
       </c>
       <c r="AA15" s="1">
-        <v>-0.0013846746279327969</v>
+        <v>-0.0013846369992274038</v>
       </c>
       <c r="AB15" s="1">
-        <v>-0.0013493896941073743</v>
+        <v>-0.0013493484205329192</v>
       </c>
       <c r="AC15" s="1">
-        <v>-0.00099743106951099853</v>
+        <v>-0.00099746076431565713</v>
       </c>
       <c r="AD15" s="1">
-        <v>-0.0017032347213842875</v>
+        <v>-0.0017032201811214059</v>
       </c>
       <c r="AE15" s="1">
-        <v>0.00082274511580136649</v>
+        <v>0.00082279271795957453</v>
       </c>
       <c r="AF15" s="1">
-        <v>0.0002046872350920159</v>
+        <v>0.00020472890353622766</v>
       </c>
       <c r="AG15" s="1">
-        <v>0.00065540162007077479</v>
+        <v>0.0006554222937715376</v>
       </c>
       <c r="AH15" s="1">
-        <v>0.00080271938113848213</v>
+        <v>0.0008027432583743798</v>
       </c>
       <c r="AI15" s="1">
-        <v>-6.4181064908078493e-05</v>
+        <v>-6.4178888676449887e-05</v>
       </c>
       <c r="AJ15" s="1">
-        <v>0.0048065304216768009</v>
+        <v>0.0048064846317256498</v>
       </c>
     </row>
     <row r="16">
@@ -2264,109 +2264,109 @@
         <v>42</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.0096626086780825602</v>
+        <v>-0.0096646471640221866</v>
       </c>
       <c r="C16" s="1">
-        <v>-3.9426247011551877e-05</v>
+        <v>-3.9427885353519204e-05</v>
       </c>
       <c r="D16" s="1">
-        <v>4.33176523057774e-07</v>
+        <v>4.3320016634359458e-07</v>
       </c>
       <c r="E16" s="1">
-        <v>6.9379171881549196e-05</v>
+        <v>6.9359621375737686e-05</v>
       </c>
       <c r="F16" s="1">
-        <v>0.0010894805349598213</v>
+        <v>0.0010893419761174314</v>
       </c>
       <c r="G16" s="1">
-        <v>-0.0003705346102551885</v>
+        <v>-0.00037037125058585045</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.0016904558285760181</v>
+        <v>-0.0016903346272723638</v>
       </c>
       <c r="I16" s="1">
-        <v>-0.0047094338044225753</v>
+        <v>-0.0047093130948772759</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.0034658311367286926</v>
+        <v>-0.0034657233561023533</v>
       </c>
       <c r="K16" s="1">
-        <v>-0.0034788730617994409</v>
+        <v>-0.0034787704794699168</v>
       </c>
       <c r="L16" s="1">
-        <v>1.4579569372008766e-05</v>
+        <v>1.4579577990524937e-05</v>
       </c>
       <c r="M16" s="1">
-        <v>0.0063069182350576772</v>
+        <v>0.0063070603091155593</v>
       </c>
       <c r="N16" s="1">
-        <v>-0.014772718844316945</v>
+        <v>-0.01477258075743995</v>
       </c>
       <c r="O16" s="1">
-        <v>0.01233948774700726</v>
+        <v>0.012339332424850051</v>
       </c>
       <c r="P16" s="1">
-        <v>0.021933837896391854</v>
+        <v>0.021933709850580192</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.055297383055804526</v>
+        <v>0.055297261150509869</v>
       </c>
       <c r="R16" s="1">
-        <v>-0.029327259028154522</v>
+        <v>-0.029327228738965799</v>
       </c>
       <c r="S16" s="1">
-        <v>2.0030531370619038e-05</v>
+        <v>2.0034816682379213e-05</v>
       </c>
       <c r="T16" s="1">
-        <v>-0.00059646787795644273</v>
+        <v>-0.00059644124201359066</v>
       </c>
       <c r="U16" s="1">
-        <v>-0.0019994145453209032</v>
+        <v>-0.0019993668850762825</v>
       </c>
       <c r="V16" s="1">
-        <v>-0.0019155703180055528</v>
+        <v>-0.0019155342860770657</v>
       </c>
       <c r="W16" s="1">
-        <v>-0.0014535863515929854</v>
+        <v>-0.0014536925255353183</v>
       </c>
       <c r="X16" s="1">
-        <v>0.0012736094326992093</v>
+        <v>0.0012734933818371531</v>
       </c>
       <c r="Y16" s="1">
-        <v>-0.00057186220713806172</v>
+        <v>-0.00057186732564113601</v>
       </c>
       <c r="Z16" s="1">
-        <v>-0.0010630236523501871</v>
+        <v>-0.0010629227433674648</v>
       </c>
       <c r="AA16" s="1">
-        <v>-0.0012271984627270404</v>
+        <v>-0.0012271726408477671</v>
       </c>
       <c r="AB16" s="1">
-        <v>-0.0010687838955479323</v>
+        <v>-0.0010687574141367458</v>
       </c>
       <c r="AC16" s="1">
-        <v>-0.0009899582283450334</v>
+        <v>-0.00098996098774364037</v>
       </c>
       <c r="AD16" s="1">
-        <v>-0.001021967531757287</v>
+        <v>-0.0010219560788936339</v>
       </c>
       <c r="AE16" s="1">
-        <v>-0.00027500039645306489</v>
+        <v>-0.00027498171943266436</v>
       </c>
       <c r="AF16" s="1">
-        <v>-0.00039070884820706223</v>
+        <v>-0.0003906930612574877</v>
       </c>
       <c r="AG16" s="1">
-        <v>0.00011919758549663439</v>
+        <v>0.00011920178109120407</v>
       </c>
       <c r="AH16" s="1">
-        <v>7.5570380833825694e-05</v>
+        <v>7.5582502988888207e-05</v>
       </c>
       <c r="AI16" s="1">
-        <v>3.0056149226279118e-05</v>
+        <v>3.0056586912962483e-05</v>
       </c>
       <c r="AJ16" s="1">
-        <v>0.0047876597521996737</v>
+        <v>0.0047875786038323407</v>
       </c>
     </row>
     <row r="17">
@@ -2374,109 +2374,109 @@
         <v>43</v>
       </c>
       <c r="B17" s="1">
-        <v>-0.92229415843489249</v>
+        <v>-0.92229120084689564</v>
       </c>
       <c r="C17" s="1">
-        <v>0.00030701867894046022</v>
+        <v>0.00030701817545530734</v>
       </c>
       <c r="D17" s="1">
-        <v>-3.549840756224113e-06</v>
+        <v>-3.5498434032382622e-06</v>
       </c>
       <c r="E17" s="1">
-        <v>0.00027725399536987331</v>
+        <v>0.00027729744631712738</v>
       </c>
       <c r="F17" s="1">
-        <v>0.0015035074056068561</v>
+        <v>0.0015038049337555018</v>
       </c>
       <c r="G17" s="1">
-        <v>-0.0018700280226454046</v>
+        <v>-0.0018704012042237183</v>
       </c>
       <c r="H17" s="1">
-        <v>0.0026320020380557665</v>
+        <v>0.0026321582842970181</v>
       </c>
       <c r="I17" s="1">
-        <v>0.0019346355101348611</v>
+        <v>0.0019346073941537891</v>
       </c>
       <c r="J17" s="1">
-        <v>0.0016890260551520411</v>
+        <v>0.0016890333024401642</v>
       </c>
       <c r="K17" s="1">
-        <v>0.0015682641419355312</v>
+        <v>0.0015682808384390227</v>
       </c>
       <c r="L17" s="1">
-        <v>-0.00023368644689902184</v>
+        <v>-0.00023368641673406933</v>
       </c>
       <c r="M17" s="1">
-        <v>0.018892821430879822</v>
+        <v>0.018892451525439988</v>
       </c>
       <c r="N17" s="1">
-        <v>-0.017697155964573812</v>
+        <v>-0.017697452999373874</v>
       </c>
       <c r="O17" s="1">
-        <v>0.028088150710230627</v>
+        <v>0.02808850827922485</v>
       </c>
       <c r="P17" s="1">
-        <v>-0.047734626316777828</v>
+        <v>-0.04773477173098329</v>
       </c>
       <c r="Q17" s="1">
-        <v>-0.029327259028154522</v>
+        <v>-0.029327228738965799</v>
       </c>
       <c r="R17" s="1">
-        <v>0.1429237467003073</v>
+        <v>0.14292389700068295</v>
       </c>
       <c r="S17" s="1">
-        <v>7.2223608444031326e-05</v>
+        <v>7.222504230967831e-05</v>
       </c>
       <c r="T17" s="1">
-        <v>0.0012727112928238834</v>
+        <v>0.0012726934365743941</v>
       </c>
       <c r="U17" s="1">
-        <v>-0.0079042716296523919</v>
+        <v>-0.0079043840104836196</v>
       </c>
       <c r="V17" s="1">
-        <v>0.00067998241465348167</v>
+        <v>0.00067990944517630492</v>
       </c>
       <c r="W17" s="1">
-        <v>0.0034011474754036056</v>
+        <v>0.0034012918128186222</v>
       </c>
       <c r="X17" s="1">
-        <v>0.0072990963211219898</v>
+        <v>0.0072994134688928111</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.00032461068621889846</v>
+        <v>0.00032462320935476401</v>
       </c>
       <c r="Z17" s="1">
-        <v>-0.001203064237193607</v>
+        <v>-0.0012032299557497321</v>
       </c>
       <c r="AA17" s="1">
-        <v>0.0015726874179654389</v>
+        <v>0.0015726735246011847</v>
       </c>
       <c r="AB17" s="1">
-        <v>0.0019805528763011909</v>
+        <v>0.0019805358613256769</v>
       </c>
       <c r="AC17" s="1">
-        <v>0.0021896637372197758</v>
+        <v>0.0021896889129765398</v>
       </c>
       <c r="AD17" s="1">
-        <v>0.0030428932784123015</v>
+        <v>0.0030428894952357483</v>
       </c>
       <c r="AE17" s="1">
-        <v>-0.0022741039098323756</v>
+        <v>-0.0022741328759806377</v>
       </c>
       <c r="AF17" s="1">
-        <v>-0.00043031835099130011</v>
+        <v>-0.00043034432677351931</v>
       </c>
       <c r="AG17" s="1">
-        <v>-0.00088213111602639159</v>
+        <v>-0.00088214740572244328</v>
       </c>
       <c r="AH17" s="1">
-        <v>-0.00091133084550964636</v>
+        <v>-0.00091134324601960942</v>
       </c>
       <c r="AI17" s="1">
-        <v>7.6740339025009645e-05</v>
+        <v>7.6738729491253099e-05</v>
       </c>
       <c r="AJ17" s="1">
-        <v>-0.010998605998748573</v>
+        <v>-0.010998614188305545</v>
       </c>
     </row>
     <row r="18">
@@ -2484,109 +2484,109 @@
         <v>44</v>
       </c>
       <c r="B18" s="1">
-        <v>0.074595279732697792</v>
+        <v>0.07459539226047307</v>
       </c>
       <c r="C18" s="1">
-        <v>-1.2760387812585058e-05</v>
+        <v>-1.2760220792588659e-05</v>
       </c>
       <c r="D18" s="1">
-        <v>8.2479551165736072e-08</v>
+        <v>8.2476986461290973e-08</v>
       </c>
       <c r="E18" s="1">
-        <v>0.00021974233489613452</v>
+        <v>0.00021974369811781971</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.00016794487191463704</v>
+        <v>-0.00016793347453158682</v>
       </c>
       <c r="G18" s="1">
-        <v>0.00033323964561803526</v>
+        <v>0.00033322504043537806</v>
       </c>
       <c r="H18" s="1">
-        <v>0.00014501086282175127</v>
+        <v>0.00014501015666834371</v>
       </c>
       <c r="I18" s="1">
-        <v>-6.6709193365269951e-05</v>
+        <v>-6.6713293915070053e-05</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.00022504971246903679</v>
+        <v>-0.00022505293278313421</v>
       </c>
       <c r="K18" s="1">
-        <v>-0.00075745607570977297</v>
+        <v>-0.00075745883223086248</v>
       </c>
       <c r="L18" s="1">
-        <v>3.8953905999880786e-07</v>
+        <v>3.8953787815550023e-07</v>
       </c>
       <c r="M18" s="1">
-        <v>-6.176434106275848e-05</v>
+        <v>-6.1767966233298389e-05</v>
       </c>
       <c r="N18" s="1">
-        <v>0.00019628192209902165</v>
+        <v>0.00019627055483887381</v>
       </c>
       <c r="O18" s="1">
-        <v>-0.00044569076007832574</v>
+        <v>-0.00044567648288913617</v>
       </c>
       <c r="P18" s="1">
-        <v>-0.00013744956687957666</v>
+        <v>-0.00013744848391020599</v>
       </c>
       <c r="Q18" s="1">
-        <v>2.0030531370619038e-05</v>
+        <v>2.0034816682379213e-05</v>
       </c>
       <c r="R18" s="1">
-        <v>7.2223608444031326e-05</v>
+        <v>7.222504230967831e-05</v>
       </c>
       <c r="S18" s="1">
-        <v>0.0016816845262855279</v>
+        <v>0.0016816844903655924</v>
       </c>
       <c r="T18" s="1">
-        <v>0.0004285365828040422</v>
+        <v>0.00042853511152621254</v>
       </c>
       <c r="U18" s="1">
-        <v>0.00016803689817788557</v>
+        <v>0.00016803468884114879</v>
       </c>
       <c r="V18" s="1">
-        <v>-4.1124812647022335e-05</v>
+        <v>-4.1126547724713443e-05</v>
       </c>
       <c r="W18" s="1">
-        <v>-9.4290484247119271e-05</v>
+        <v>-9.4281066061953014e-05</v>
       </c>
       <c r="X18" s="1">
-        <v>-0.00015049531328103247</v>
+        <v>-0.00015049330531996392</v>
       </c>
       <c r="Y18" s="1">
-        <v>7.7522825131117235e-05</v>
+        <v>7.7523287010912767e-05</v>
       </c>
       <c r="Z18" s="1">
-        <v>-8.7707661843647655e-05</v>
+        <v>-8.7715674301149811e-05</v>
       </c>
       <c r="AA18" s="1">
-        <v>9.7321226783976783e-05</v>
+        <v>9.7323530217046365e-05</v>
       </c>
       <c r="AB18" s="1">
-        <v>3.1517055233247985e-05</v>
+        <v>3.1519112336178982e-05</v>
       </c>
       <c r="AC18" s="1">
-        <v>-0.00014215079327973708</v>
+        <v>-0.00014214722817850083</v>
       </c>
       <c r="AD18" s="1">
-        <v>-0.00023048613456717486</v>
+        <v>-0.00023048315153529489</v>
       </c>
       <c r="AE18" s="1">
-        <v>0.00017618675069047652</v>
+        <v>0.00017618521493156114</v>
       </c>
       <c r="AF18" s="1">
-        <v>0.0003121363929166007</v>
+        <v>0.00031213487705179029</v>
       </c>
       <c r="AG18" s="1">
-        <v>7.2295083887269904e-05</v>
+        <v>7.229352290737416e-05</v>
       </c>
       <c r="AH18" s="1">
-        <v>6.486253400155248e-05</v>
+        <v>6.4861127199437874e-05</v>
       </c>
       <c r="AI18" s="1">
-        <v>-6.7537652868699089e-06</v>
+        <v>-6.7537647739472544e-06</v>
       </c>
       <c r="AJ18" s="1">
-        <v>3.1364143138344527e-05</v>
+        <v>3.1360999121017139e-05</v>
       </c>
     </row>
     <row r="19">
@@ -2594,109 +2594,109 @@
         <v>45</v>
       </c>
       <c r="B19" s="1">
-        <v>-0.025031701349021621</v>
+        <v>-0.025031366817250125</v>
       </c>
       <c r="C19" s="1">
-        <v>5.5182437204160897e-05</v>
+        <v>5.5183975946626509e-05</v>
       </c>
       <c r="D19" s="1">
-        <v>-8.4219991143292612e-07</v>
+        <v>-8.4221861976990896e-07</v>
       </c>
       <c r="E19" s="1">
-        <v>-0.00047827977513975351</v>
+        <v>-0.00047827996598539938</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.00095333762545360694</v>
+        <v>-0.00095334010158321721</v>
       </c>
       <c r="G19" s="1">
-        <v>0.00081592853956486647</v>
+        <v>0.00081593268786342194</v>
       </c>
       <c r="H19" s="1">
-        <v>-0.00021078114369537835</v>
+        <v>-0.0002108222183750388</v>
       </c>
       <c r="I19" s="1">
-        <v>0.00056370459443238347</v>
+        <v>0.00056367811840290344</v>
       </c>
       <c r="J19" s="1">
-        <v>0.00018699308905809569</v>
+        <v>0.00018696433573911085</v>
       </c>
       <c r="K19" s="1">
-        <v>0.0002478261232163374</v>
+        <v>0.00024779723191825284</v>
       </c>
       <c r="L19" s="1">
-        <v>-6.820218795580135e-07</v>
+        <v>-6.8203769975392545e-07</v>
       </c>
       <c r="M19" s="1">
-        <v>0.00097810595156381228</v>
+        <v>0.00097813866764100144</v>
       </c>
       <c r="N19" s="1">
-        <v>0.00096237607915258827</v>
+        <v>0.00096237875483315308</v>
       </c>
       <c r="O19" s="1">
-        <v>-0.00087221076685668904</v>
+        <v>-0.00087221551062518761</v>
       </c>
       <c r="P19" s="1">
-        <v>0.00013997237897785591</v>
+        <v>0.00014001499820291349</v>
       </c>
       <c r="Q19" s="1">
-        <v>-0.00059646787795644273</v>
+        <v>-0.00059644124201359066</v>
       </c>
       <c r="R19" s="1">
-        <v>0.0012727112928238834</v>
+        <v>0.0012726934365743941</v>
       </c>
       <c r="S19" s="1">
-        <v>0.0004285365828040422</v>
+        <v>0.00042853511152621254</v>
       </c>
       <c r="T19" s="1">
-        <v>0.003353515497775959</v>
+        <v>0.0033535012971146702</v>
       </c>
       <c r="U19" s="1">
-        <v>-0.00059186641816314531</v>
+        <v>-0.00059186615350185232</v>
       </c>
       <c r="V19" s="1">
-        <v>5.8111888616098117e-05</v>
+        <v>5.8113333686338344e-05</v>
       </c>
       <c r="W19" s="1">
-        <v>0.00018906311205651018</v>
+        <v>0.00018909370078619794</v>
       </c>
       <c r="X19" s="1">
-        <v>-0.000441163000285656</v>
+        <v>-0.00044119672686132046</v>
       </c>
       <c r="Y19" s="1">
-        <v>0.00060628084132132365</v>
+        <v>0.00060628016561644011</v>
       </c>
       <c r="Z19" s="1">
-        <v>0.00095540832820199177</v>
+        <v>0.00095538780375882169</v>
       </c>
       <c r="AA19" s="1">
-        <v>0.00021736448672548994</v>
+        <v>0.000217370270891228</v>
       </c>
       <c r="AB19" s="1">
-        <v>0.0014718242315567116</v>
+        <v>0.0014718284731292312</v>
       </c>
       <c r="AC19" s="1">
-        <v>0.0013251497281150685</v>
+        <v>0.0013251575744512897</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.0013170876056563295</v>
+        <v>0.0013170966214355853</v>
       </c>
       <c r="AE19" s="1">
-        <v>0.00022376987210187766</v>
+        <v>0.00022376598806957007</v>
       </c>
       <c r="AF19" s="1">
-        <v>0.00042249326609627839</v>
+        <v>0.0004224905312752603</v>
       </c>
       <c r="AG19" s="1">
-        <v>-8.6273934951553886e-06</v>
+        <v>-8.630295008686781e-06</v>
       </c>
       <c r="AH19" s="1">
-        <v>2.8575703177091726e-05</v>
+        <v>2.8569507144557567e-05</v>
       </c>
       <c r="AI19" s="1">
-        <v>-2.2950643318548713e-05</v>
+        <v>-2.2950196029828196e-05</v>
       </c>
       <c r="AJ19" s="1">
-        <v>-0.0021652790651327616</v>
+        <v>-0.0021652901197315145</v>
       </c>
     </row>
     <row r="20">
@@ -2704,109 +2704,109 @@
         <v>46</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.50340622526409218</v>
+        <v>-0.50340700318318765</v>
       </c>
       <c r="C20" s="1">
-        <v>0.00014753959923505825</v>
+        <v>0.00014753996167914842</v>
       </c>
       <c r="D20" s="1">
-        <v>-1.1442561150505924e-06</v>
+        <v>-1.1442567367710943e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>0.0013256211304872368</v>
+        <v>0.0013256067323528416</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.0011014759215987552</v>
+        <v>-0.0011015763435854142</v>
       </c>
       <c r="G20" s="1">
-        <v>0.00097945032815097903</v>
+        <v>0.00097958186311035943</v>
       </c>
       <c r="H20" s="1">
-        <v>-0.00034733730726302695</v>
+        <v>-0.0003474965757822785</v>
       </c>
       <c r="I20" s="1">
-        <v>0.0020007433476945972</v>
+        <v>0.0020006945575810403</v>
       </c>
       <c r="J20" s="1">
-        <v>0.0020852839105369382</v>
+        <v>0.0020852217183651473</v>
       </c>
       <c r="K20" s="1">
-        <v>0.0016535279141053228</v>
+        <v>0.0016534625969280695</v>
       </c>
       <c r="L20" s="1">
-        <v>-2.0075991762970689e-06</v>
+        <v>-2.0076084806563729e-06</v>
       </c>
       <c r="M20" s="1">
-        <v>0.0084581387276010753</v>
+        <v>0.0084582596397184909</v>
       </c>
       <c r="N20" s="1">
-        <v>0.0011384981536497597</v>
+        <v>0.0011385983891550942</v>
       </c>
       <c r="O20" s="1">
-        <v>-0.0011379766775325977</v>
+        <v>-0.001138105202561183</v>
       </c>
       <c r="P20" s="1">
-        <v>0.0004495454932061777</v>
+        <v>0.00044970276732439517</v>
       </c>
       <c r="Q20" s="1">
-        <v>-0.0019994145453209032</v>
+        <v>-0.0019993668850762825</v>
       </c>
       <c r="R20" s="1">
-        <v>-0.0079042716296523919</v>
+        <v>-0.0079043840104836196</v>
       </c>
       <c r="S20" s="1">
-        <v>0.00016803689817788557</v>
+        <v>0.00016803468884114879</v>
       </c>
       <c r="T20" s="1">
-        <v>-0.00059186641816314531</v>
+        <v>-0.00059186615350185232</v>
       </c>
       <c r="U20" s="1">
-        <v>0.012553923839255524</v>
+        <v>0.012553964463704981</v>
       </c>
       <c r="V20" s="1">
-        <v>0.0029065837032541059</v>
+        <v>0.0029066055195878923</v>
       </c>
       <c r="W20" s="1">
-        <v>0.00095849786622544293</v>
+        <v>0.0009584502361137772</v>
       </c>
       <c r="X20" s="1">
-        <v>-0.0098434522825526852</v>
+        <v>-0.0098435576618461397</v>
       </c>
       <c r="Y20" s="1">
-        <v>-0.0012425610726507631</v>
+        <v>-0.0012425660570452486</v>
       </c>
       <c r="Z20" s="1">
-        <v>-0.00057030075731183318</v>
+        <v>-0.00057024747048037977</v>
       </c>
       <c r="AA20" s="1">
-        <v>0.001199136301825924</v>
+        <v>0.0011991274970252481</v>
       </c>
       <c r="AB20" s="1">
-        <v>0.0003844508449420259</v>
+        <v>0.00038444393307387624</v>
       </c>
       <c r="AC20" s="1">
-        <v>0.00045895734912721245</v>
+        <v>0.00045893973682302643</v>
       </c>
       <c r="AD20" s="1">
-        <v>0.00052097862207196692</v>
+        <v>0.00052096909584485639</v>
       </c>
       <c r="AE20" s="1">
-        <v>0.00015500000377794039</v>
+        <v>0.0001550095405156598</v>
       </c>
       <c r="AF20" s="1">
-        <v>-5.6273158599957733e-05</v>
+        <v>-5.6264564034130046e-05</v>
       </c>
       <c r="AG20" s="1">
-        <v>-0.00016824470899227733</v>
+        <v>-0.00016823469905785171</v>
       </c>
       <c r="AH20" s="1">
-        <v>-8.7676072208330968e-05</v>
+        <v>-8.7671795737625201e-05</v>
       </c>
       <c r="AI20" s="1">
-        <v>-2.1703262709490235e-05</v>
+        <v>-2.1702851173267926e-05</v>
       </c>
       <c r="AJ20" s="1">
-        <v>-0.0064323605706343061</v>
+        <v>-0.0064322909137250802</v>
       </c>
     </row>
     <row r="21">
@@ -2814,109 +2814,109 @@
         <v>47</v>
       </c>
       <c r="B21" s="1">
-        <v>-0.023666034498190096</v>
+        <v>-0.023666515791934947</v>
       </c>
       <c r="C21" s="1">
-        <v>9.8860343215931979e-05</v>
+        <v>9.8860495273206113e-05</v>
       </c>
       <c r="D21" s="1">
-        <v>-1.0598411567220541e-06</v>
+        <v>-1.0598407018523324e-06</v>
       </c>
       <c r="E21" s="1">
-        <v>0.00085724104851977003</v>
+        <v>0.00085723225974047141</v>
       </c>
       <c r="F21" s="1">
-        <v>-0.00079792068133940951</v>
+        <v>-0.00079798034000817862</v>
       </c>
       <c r="G21" s="1">
-        <v>-0.00030736797364871744</v>
+        <v>-0.00030728834569701031</v>
       </c>
       <c r="H21" s="1">
-        <v>-7.0361546271750287e-06</v>
+        <v>-7.1482463312627946e-06</v>
       </c>
       <c r="I21" s="1">
-        <v>0.0018998803956907944</v>
+        <v>0.0018998436807964958</v>
       </c>
       <c r="J21" s="1">
-        <v>0.0022039971738406923</v>
+        <v>0.0022039524436357296</v>
       </c>
       <c r="K21" s="1">
-        <v>0.0022486683515078368</v>
+        <v>0.0022486218894221823</v>
       </c>
       <c r="L21" s="1">
-        <v>-1.1062979733058719e-06</v>
+        <v>-1.1063031185336115e-06</v>
       </c>
       <c r="M21" s="1">
-        <v>0.00047431467590572271</v>
+        <v>0.00047438347627766172</v>
       </c>
       <c r="N21" s="1">
-        <v>0.00082197941495750361</v>
+        <v>0.00082203897640036267</v>
       </c>
       <c r="O21" s="1">
-        <v>0.00040641958202692832</v>
+        <v>0.00040634183703845824</v>
       </c>
       <c r="P21" s="1">
-        <v>-4.8820224108188045e-06</v>
+        <v>-4.7711235332904888e-06</v>
       </c>
       <c r="Q21" s="1">
-        <v>-0.0019155703180055528</v>
+        <v>-0.0019155342860770657</v>
       </c>
       <c r="R21" s="1">
-        <v>0.00067998241465348167</v>
+        <v>0.00067990944517630492</v>
       </c>
       <c r="S21" s="1">
-        <v>-4.1124812647022335e-05</v>
+        <v>-4.1126547724713443e-05</v>
       </c>
       <c r="T21" s="1">
-        <v>5.8111888616098117e-05</v>
+        <v>5.8113333686338344e-05</v>
       </c>
       <c r="U21" s="1">
-        <v>0.0029065837032541059</v>
+        <v>0.0029066055195878923</v>
       </c>
       <c r="V21" s="1">
-        <v>0.0052767740547924992</v>
+        <v>0.0052767873816776173</v>
       </c>
       <c r="W21" s="1">
-        <v>0.0026831529902438108</v>
+        <v>0.0026831239274204737</v>
       </c>
       <c r="X21" s="1">
-        <v>-0.0013226253790760835</v>
+        <v>-0.0013226847061694469</v>
       </c>
       <c r="Y21" s="1">
-        <v>-0.0033715237476806608</v>
+        <v>-0.0033715264299028708</v>
       </c>
       <c r="Z21" s="1">
-        <v>-0.00033913874543703426</v>
+        <v>-0.0003391062403556625</v>
       </c>
       <c r="AA21" s="1">
-        <v>0.0005690124038665598</v>
+        <v>0.00056900924243066331</v>
       </c>
       <c r="AB21" s="1">
-        <v>0.00094559018026992687</v>
+        <v>0.00094558752779508716</v>
       </c>
       <c r="AC21" s="1">
-        <v>0.0013988845939846015</v>
+        <v>0.0013988751684769272</v>
       </c>
       <c r="AD21" s="1">
-        <v>0.0014976277596562902</v>
+        <v>0.0014976235357974229</v>
       </c>
       <c r="AE21" s="1">
-        <v>0.00039624205824750013</v>
+        <v>0.00039624795617099174</v>
       </c>
       <c r="AF21" s="1">
-        <v>0.00010808242997750175</v>
+        <v>0.00010808781239745116</v>
       </c>
       <c r="AG21" s="1">
-        <v>-9.6583823432491375e-06</v>
+        <v>-9.6530104149574001e-06</v>
       </c>
       <c r="AH21" s="1">
-        <v>0.00034669772075719674</v>
+        <v>0.0003467001962749103</v>
       </c>
       <c r="AI21" s="1">
-        <v>9.5242212030431184e-06</v>
+        <v>9.5244833799189088e-06</v>
       </c>
       <c r="AJ21" s="1">
-        <v>-0.0064858051857528661</v>
+        <v>-0.0064857559771050741</v>
       </c>
     </row>
     <row r="22">
@@ -2924,109 +2924,109 @@
         <v>48</v>
       </c>
       <c r="B22" s="1">
-        <v>0.16241509665800816</v>
+        <v>0.16241471622856332</v>
       </c>
       <c r="C22" s="1">
-        <v>0.00048960940691704098</v>
+        <v>0.00048960431695527348</v>
       </c>
       <c r="D22" s="1">
-        <v>-7.4529894906173297e-06</v>
+        <v>-7.4529299137327028e-06</v>
       </c>
       <c r="E22" s="1">
-        <v>0.00029796563639309059</v>
+        <v>0.00029797915818645214</v>
       </c>
       <c r="F22" s="1">
-        <v>0.0035743485821720391</v>
+        <v>0.0035744384730242119</v>
       </c>
       <c r="G22" s="1">
-        <v>-0.0057129249932653826</v>
+        <v>-0.0057130437672272905</v>
       </c>
       <c r="H22" s="1">
-        <v>0.0014792156226646909</v>
+        <v>0.0014794582710462799</v>
       </c>
       <c r="I22" s="1">
-        <v>0.0013922391631048595</v>
+        <v>0.0013923454247804839</v>
       </c>
       <c r="J22" s="1">
-        <v>0.0013101882111798879</v>
+        <v>0.0013103094283483539</v>
       </c>
       <c r="K22" s="1">
-        <v>0.0026544300983962496</v>
+        <v>0.0026545528042873669</v>
       </c>
       <c r="L22" s="1">
-        <v>-3.3825335208490267e-06</v>
+        <v>-3.3824762386758957e-06</v>
       </c>
       <c r="M22" s="1">
-        <v>0.00098362939669067984</v>
+        <v>0.00098336708020826317</v>
       </c>
       <c r="N22" s="1">
-        <v>-0.003457545898593773</v>
+        <v>-0.0034576362550748402</v>
       </c>
       <c r="O22" s="1">
-        <v>0.005655981745952182</v>
+        <v>0.005656099228844763</v>
       </c>
       <c r="P22" s="1">
-        <v>-0.001412406167629365</v>
+        <v>-0.0014126522940104882</v>
       </c>
       <c r="Q22" s="1">
-        <v>-0.0014535863515929854</v>
+        <v>-0.0014536925255353183</v>
       </c>
       <c r="R22" s="1">
-        <v>0.0034011474754036056</v>
+        <v>0.0034012918128186222</v>
       </c>
       <c r="S22" s="1">
-        <v>-9.4290484247119271e-05</v>
+        <v>-9.4281066061953014e-05</v>
       </c>
       <c r="T22" s="1">
-        <v>0.00018906311205651018</v>
+        <v>0.00018909370078619794</v>
       </c>
       <c r="U22" s="1">
-        <v>0.00095849786622544293</v>
+        <v>0.0009584502361137772</v>
       </c>
       <c r="V22" s="1">
-        <v>0.0026831529902438108</v>
+        <v>0.0026831239274204737</v>
       </c>
       <c r="W22" s="1">
-        <v>0.018759696825401961</v>
+        <v>0.018759626873394414</v>
       </c>
       <c r="X22" s="1">
-        <v>-0.0013201521171483787</v>
+        <v>-0.0013199002654699613</v>
       </c>
       <c r="Y22" s="1">
-        <v>4.3649343751695933e-05</v>
+        <v>4.3653673222629821e-05</v>
       </c>
       <c r="Z22" s="1">
-        <v>-0.006344841120805635</v>
+        <v>-0.0063448183954610739</v>
       </c>
       <c r="AA22" s="1">
-        <v>-0.0025809946348953174</v>
+        <v>-0.0025810058399094536</v>
       </c>
       <c r="AB22" s="1">
-        <v>0.0028437564401453796</v>
+        <v>0.0028437504319016069</v>
       </c>
       <c r="AC22" s="1">
-        <v>0.0044238886112669493</v>
+        <v>0.0044238794411727914</v>
       </c>
       <c r="AD22" s="1">
-        <v>0.0042040847507722207</v>
+        <v>0.0042040633144781996</v>
       </c>
       <c r="AE22" s="1">
-        <v>0.00036201459339322943</v>
+        <v>0.0003620217927259228</v>
       </c>
       <c r="AF22" s="1">
-        <v>0.00031982046674714892</v>
+        <v>0.00031982494042713961</v>
       </c>
       <c r="AG22" s="1">
-        <v>-0.00012040417886888038</v>
+        <v>-0.00012039869753297178</v>
       </c>
       <c r="AH22" s="1">
-        <v>0.00021893459766924878</v>
+        <v>0.00021895507304873184</v>
       </c>
       <c r="AI22" s="1">
-        <v>4.4505427961633655e-05</v>
+        <v>4.4503369386830765e-05</v>
       </c>
       <c r="AJ22" s="1">
-        <v>-0.014883233683877379</v>
+        <v>-0.014883237726560338</v>
       </c>
     </row>
     <row r="23">
@@ -3034,109 +3034,109 @@
         <v>49</v>
       </c>
       <c r="B23" s="1">
-        <v>0.084475871352259882</v>
+        <v>0.084479343256291348</v>
       </c>
       <c r="C23" s="1">
-        <v>4.2528895620748256e-05</v>
+        <v>4.2532632568744637e-05</v>
       </c>
       <c r="D23" s="1">
-        <v>-7.2579344679136176e-07</v>
+        <v>-7.2585024226574455e-07</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.0020644882461998372</v>
+        <v>-0.0020644448798767985</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.0012986065817310053</v>
+        <v>-0.0012983044917876446</v>
       </c>
       <c r="G23" s="1">
-        <v>0.0010797367122114506</v>
+        <v>0.0010793420177027115</v>
       </c>
       <c r="H23" s="1">
-        <v>-0.00088580594736052231</v>
+        <v>-0.00088535264409792046</v>
       </c>
       <c r="I23" s="1">
-        <v>-0.0013621364771101221</v>
+        <v>-0.001362015941516595</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.0016580897846829911</v>
+        <v>-0.0016579413131395302</v>
       </c>
       <c r="K23" s="1">
-        <v>-0.001451262510249515</v>
+        <v>-0.001451106528047876</v>
       </c>
       <c r="L23" s="1">
-        <v>-3.6774796490244396e-07</v>
+        <v>-3.6776831228817367e-07</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.029357524460412079</v>
+        <v>-0.029357344794247932</v>
       </c>
       <c r="N23" s="1">
-        <v>0.0012411751242396769</v>
+        <v>0.001240874794085354</v>
       </c>
       <c r="O23" s="1">
-        <v>-0.0012436206037002926</v>
+        <v>-0.0012432362646927699</v>
       </c>
       <c r="P23" s="1">
-        <v>0.00083571331436946121</v>
+        <v>0.00083527155546368878</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.0012736094326992093</v>
+        <v>0.0012734933818371531</v>
       </c>
       <c r="R23" s="1">
-        <v>0.0072990963211219898</v>
+        <v>0.0072994134688928111</v>
       </c>
       <c r="S23" s="1">
-        <v>-0.00015049531328103247</v>
+        <v>-0.00015049330531996392</v>
       </c>
       <c r="T23" s="1">
-        <v>-0.000441163000285656</v>
+        <v>-0.00044119672686132046</v>
       </c>
       <c r="U23" s="1">
-        <v>-0.0098434522825526852</v>
+        <v>-0.0098435576618461397</v>
       </c>
       <c r="V23" s="1">
-        <v>-0.0013226253790760835</v>
+        <v>-0.0013226847061694469</v>
       </c>
       <c r="W23" s="1">
-        <v>-0.0013201521171483787</v>
+        <v>-0.0013199002654699613</v>
       </c>
       <c r="X23" s="1">
-        <v>0.031448140443164463</v>
+        <v>0.031447909831661701</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.0016870227126542093</v>
+        <v>0.0016870370145621464</v>
       </c>
       <c r="Z23" s="1">
-        <v>0.0027530437071004638</v>
+        <v>0.0027528081247408893</v>
       </c>
       <c r="AA23" s="1">
-        <v>-0.00099836885658841773</v>
+        <v>-0.00099832008734251779</v>
       </c>
       <c r="AB23" s="1">
-        <v>-3.4221704500507488e-05</v>
+        <v>-3.4184264503773739e-05</v>
       </c>
       <c r="AC23" s="1">
-        <v>-1.9188727919082656e-05</v>
+        <v>-1.9107661574141341e-05</v>
       </c>
       <c r="AD23" s="1">
-        <v>-9.9838153052033844e-05</v>
+        <v>-9.9777223667691766e-05</v>
       </c>
       <c r="AE23" s="1">
-        <v>0.0003769908640358129</v>
+        <v>0.00037694680403458784</v>
       </c>
       <c r="AF23" s="1">
-        <v>0.0010964550581072756</v>
+        <v>0.0010964108369845653</v>
       </c>
       <c r="AG23" s="1">
-        <v>0.0015912784212669055</v>
+        <v>0.0015912267080273716</v>
       </c>
       <c r="AH23" s="1">
-        <v>0.00015754607991397008</v>
+        <v>0.00015750949471764002</v>
       </c>
       <c r="AI23" s="1">
-        <v>-5.1615415216511252e-05</v>
+        <v>-5.1614765393145311e-05</v>
       </c>
       <c r="AJ23" s="1">
-        <v>0.0026349564350518851</v>
+        <v>0.0026346536810663633</v>
       </c>
     </row>
     <row r="24">
@@ -3144,109 +3144,109 @@
         <v>50</v>
       </c>
       <c r="B24" s="1">
-        <v>-0.29586965734924497</v>
+        <v>-0.29586957788659995</v>
       </c>
       <c r="C24" s="1">
-        <v>-3.3743639117629024e-05</v>
+        <v>-3.3743635558729646e-05</v>
       </c>
       <c r="D24" s="1">
-        <v>1.769903967788333e-07</v>
+        <v>1.7698986989963004e-07</v>
       </c>
       <c r="E24" s="1">
-        <v>-0.0017276316854921642</v>
+        <v>-0.001727630255680367</v>
       </c>
       <c r="F24" s="1">
-        <v>0.00013911978450791064</v>
+        <v>0.00013912948682769026</v>
       </c>
       <c r="G24" s="1">
-        <v>0.00060282801309254378</v>
+        <v>0.00060281469113584714</v>
       </c>
       <c r="H24" s="1">
-        <v>4.5675007195362049e-05</v>
+        <v>4.5692534344414048e-05</v>
       </c>
       <c r="I24" s="1">
-        <v>0.00055085573727041144</v>
+        <v>0.0005508609500596384</v>
       </c>
       <c r="J24" s="1">
-        <v>0.00026266422473716</v>
+        <v>0.00026267072954944918</v>
       </c>
       <c r="K24" s="1">
-        <v>0.00044895249355682103</v>
+        <v>0.00044895927714875416</v>
       </c>
       <c r="L24" s="1">
-        <v>4.7365960229092957e-07</v>
+        <v>4.7366053320317197e-07</v>
       </c>
       <c r="M24" s="1">
-        <v>5.9547085243396235e-05</v>
+        <v>5.9531254594118624e-05</v>
       </c>
       <c r="N24" s="1">
-        <v>-0.00013199076244257895</v>
+        <v>-0.0001320004454140593</v>
       </c>
       <c r="O24" s="1">
-        <v>-0.00067299511176233074</v>
+        <v>-0.0006729821067201861</v>
       </c>
       <c r="P24" s="1">
-        <v>-5.3466156708424943e-05</v>
+        <v>-5.3483495606702273e-05</v>
       </c>
       <c r="Q24" s="1">
-        <v>-0.00057186220713806172</v>
+        <v>-0.00057186732564113601</v>
       </c>
       <c r="R24" s="1">
-        <v>0.00032461068621889846</v>
+        <v>0.00032462320935476401</v>
       </c>
       <c r="S24" s="1">
-        <v>7.7522825131117235e-05</v>
+        <v>7.7523287010912767e-05</v>
       </c>
       <c r="T24" s="1">
-        <v>0.00060628084132132365</v>
+        <v>0.00060628016561644011</v>
       </c>
       <c r="U24" s="1">
-        <v>-0.0012425610726507631</v>
+        <v>-0.0012425660570452486</v>
       </c>
       <c r="V24" s="1">
-        <v>-0.0033715237476806608</v>
+        <v>-0.0033715264299028708</v>
       </c>
       <c r="W24" s="1">
-        <v>4.3649343751695933e-05</v>
+        <v>4.3653673222629821e-05</v>
       </c>
       <c r="X24" s="1">
-        <v>0.0016870227126542093</v>
+        <v>0.0016870370145621464</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.0088127027542949758</v>
+        <v>0.0088127037574895085</v>
       </c>
       <c r="Z24" s="1">
-        <v>0.0015689403689945459</v>
+        <v>0.001568936222177097</v>
       </c>
       <c r="AA24" s="1">
-        <v>-0.00087530955202509914</v>
+        <v>-0.00087531000732196022</v>
       </c>
       <c r="AB24" s="1">
-        <v>-0.00050077404780717689</v>
+        <v>-0.00050077408182202404</v>
       </c>
       <c r="AC24" s="1">
-        <v>-0.00063934648795909831</v>
+        <v>-0.00063934518325461866</v>
       </c>
       <c r="AD24" s="1">
-        <v>-0.00054275295418507294</v>
+        <v>-0.00054275266514096409</v>
       </c>
       <c r="AE24" s="1">
-        <v>-0.00027790953618879916</v>
+        <v>-0.0002779103528453871</v>
       </c>
       <c r="AF24" s="1">
-        <v>0.00081060085130532243</v>
+        <v>0.00081060045060951864</v>
       </c>
       <c r="AG24" s="1">
-        <v>1.4580298977568003e-05</v>
+        <v>1.4579944281017444e-05</v>
       </c>
       <c r="AH24" s="1">
-        <v>-0.00014861080013463788</v>
+        <v>-0.00014861025833640698</v>
       </c>
       <c r="AI24" s="1">
-        <v>-1.9385936279865803e-05</v>
+        <v>-1.9386021213623964e-05</v>
       </c>
       <c r="AJ24" s="1">
-        <v>0.0022491514371111264</v>
+        <v>0.0022491442655312504</v>
       </c>
     </row>
     <row r="25">
@@ -3254,109 +3254,109 @@
         <v>51</v>
       </c>
       <c r="B25" s="1">
-        <v>0.54168757063951944</v>
+        <v>0.54168732482664839</v>
       </c>
       <c r="C25" s="1">
-        <v>-1.7099215246567118e-05</v>
+        <v>-1.709594055688136e-05</v>
       </c>
       <c r="D25" s="1">
-        <v>-1.6554399894002201e-07</v>
+        <v>-1.6558045543957419e-07</v>
       </c>
       <c r="E25" s="1">
-        <v>-0.0024108920295859947</v>
+        <v>-0.0024109103060657956</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.0033526085689021276</v>
+        <v>-0.0033527300149531736</v>
       </c>
       <c r="G25" s="1">
-        <v>0.003662310011416813</v>
+        <v>0.0036624717139218232</v>
       </c>
       <c r="H25" s="1">
-        <v>-0.0011496162036902613</v>
+        <v>-0.0011498798556034979</v>
       </c>
       <c r="I25" s="1">
-        <v>0.00099958091079303921</v>
+        <v>0.00099947932137634714</v>
       </c>
       <c r="J25" s="1">
-        <v>0.00022785974371266867</v>
+        <v>0.00022774070461687801</v>
       </c>
       <c r="K25" s="1">
-        <v>0.00041184559005387586</v>
+        <v>0.00041172417690653492</v>
       </c>
       <c r="L25" s="1">
-        <v>5.9722822623204095e-07</v>
+        <v>5.9718811890069531e-07</v>
       </c>
       <c r="M25" s="1">
-        <v>-0.00027285155723447667</v>
+        <v>-0.00027259908329353813</v>
       </c>
       <c r="N25" s="1">
-        <v>0.0033274927763847001</v>
+        <v>0.0033276143778159027</v>
       </c>
       <c r="O25" s="1">
-        <v>-0.0036351044226085498</v>
+        <v>-0.0036352630117154729</v>
       </c>
       <c r="P25" s="1">
-        <v>0.0010499349485416098</v>
+        <v>0.0010501997132169075</v>
       </c>
       <c r="Q25" s="1">
-        <v>-0.0010630236523501871</v>
+        <v>-0.0010629227433674648</v>
       </c>
       <c r="R25" s="1">
-        <v>-0.001203064237193607</v>
+        <v>-0.0012032299557497321</v>
       </c>
       <c r="S25" s="1">
-        <v>-8.7707661843647655e-05</v>
+        <v>-8.7715674301149811e-05</v>
       </c>
       <c r="T25" s="1">
-        <v>0.00095540832820199177</v>
+        <v>0.00095538780375882169</v>
       </c>
       <c r="U25" s="1">
-        <v>-0.00057030075731183318</v>
+        <v>-0.00057024747048037977</v>
       </c>
       <c r="V25" s="1">
-        <v>-0.00033913874543703426</v>
+        <v>-0.0003391062403556625</v>
       </c>
       <c r="W25" s="1">
-        <v>-0.006344841120805635</v>
+        <v>-0.0063448183954610739</v>
       </c>
       <c r="X25" s="1">
-        <v>0.0027530437071004638</v>
+        <v>0.0027528081247408893</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.0015689403689945459</v>
+        <v>0.001568936222177097</v>
       </c>
       <c r="Z25" s="1">
-        <v>0.01464740442130957</v>
+        <v>0.014647420489344016</v>
       </c>
       <c r="AA25" s="1">
-        <v>-0.0041168966624746395</v>
+        <v>-0.0041169010434046818</v>
       </c>
       <c r="AB25" s="1">
-        <v>-0.004296450394178925</v>
+        <v>-0.0042964558844576541</v>
       </c>
       <c r="AC25" s="1">
-        <v>-0.0045649412919171453</v>
+        <v>-0.00456495111237814</v>
       </c>
       <c r="AD25" s="1">
-        <v>-0.0043929145622734487</v>
+        <v>-0.004392910459090231</v>
       </c>
       <c r="AE25" s="1">
-        <v>0.00046802280151084685</v>
+        <v>0.00046802323159536737</v>
       </c>
       <c r="AF25" s="1">
-        <v>0.0010389042213836126</v>
+        <v>0.0010389060816005636</v>
       </c>
       <c r="AG25" s="1">
-        <v>0.00096431689757602577</v>
+        <v>0.00096431815534253596</v>
       </c>
       <c r="AH25" s="1">
-        <v>0.00098589782534238266</v>
+        <v>0.00098588627907654578</v>
       </c>
       <c r="AI25" s="1">
-        <v>-5.7772010166039358e-05</v>
+        <v>-5.7770308370495986e-05</v>
       </c>
       <c r="AJ25" s="1">
-        <v>0.0066110299369622856</v>
+        <v>0.0066110870669499602</v>
       </c>
     </row>
     <row r="26">
@@ -3364,109 +3364,109 @@
         <v>52</v>
       </c>
       <c r="B26" s="1">
-        <v>0.048533438245086435</v>
+        <v>0.048533334292617754</v>
       </c>
       <c r="C26" s="1">
-        <v>7.0188735972137942e-06</v>
+        <v>7.0181798006870542e-06</v>
       </c>
       <c r="D26" s="1">
-        <v>5.8699640237404798e-07</v>
+        <v>5.8700408775871764e-07</v>
       </c>
       <c r="E26" s="1">
-        <v>0.0010016955794332359</v>
+        <v>0.0010016998948100487</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.00027200605825754016</v>
+        <v>-0.00027197552282913137</v>
       </c>
       <c r="G26" s="1">
-        <v>0.00060357386612478435</v>
+        <v>0.00060353660414547692</v>
       </c>
       <c r="H26" s="1">
-        <v>0.001488159077545758</v>
+        <v>0.0014881206838272838</v>
       </c>
       <c r="I26" s="1">
-        <v>0.0013055376981238617</v>
+        <v>0.001305511867321525</v>
       </c>
       <c r="J26" s="1">
-        <v>0.0017355079428353437</v>
+        <v>0.0017354861416748555</v>
       </c>
       <c r="K26" s="1">
-        <v>0.00083647023838219091</v>
+        <v>0.00083644848811074415</v>
       </c>
       <c r="L26" s="1">
-        <v>-1.0499503897081166e-06</v>
+        <v>-1.0499426511538353e-06</v>
       </c>
       <c r="M26" s="1">
-        <v>-0.00010330384485770578</v>
+        <v>-0.00010335621668164832</v>
       </c>
       <c r="N26" s="1">
-        <v>0.00030208119971852232</v>
+        <v>0.00030205075697256926</v>
       </c>
       <c r="O26" s="1">
-        <v>-0.00019292040331069389</v>
+        <v>-0.00019288289876176565</v>
       </c>
       <c r="P26" s="1">
-        <v>-0.0013846746279327969</v>
+        <v>-0.0013846369992274038</v>
       </c>
       <c r="Q26" s="1">
-        <v>-0.0012271984627270404</v>
+        <v>-0.0012271726408477671</v>
       </c>
       <c r="R26" s="1">
-        <v>0.0015726874179654389</v>
+        <v>0.0015726735246011847</v>
       </c>
       <c r="S26" s="1">
-        <v>9.7321226783976783e-05</v>
+        <v>9.7323530217046365e-05</v>
       </c>
       <c r="T26" s="1">
-        <v>0.00021736448672548994</v>
+        <v>0.000217370270891228</v>
       </c>
       <c r="U26" s="1">
-        <v>0.001199136301825924</v>
+        <v>0.0011991274970252481</v>
       </c>
       <c r="V26" s="1">
-        <v>0.0005690124038665598</v>
+        <v>0.00056900924243066331</v>
       </c>
       <c r="W26" s="1">
-        <v>-0.0025809946348953174</v>
+        <v>-0.0025810058399094536</v>
       </c>
       <c r="X26" s="1">
-        <v>-0.00099836885658841773</v>
+        <v>-0.00099832008734251779</v>
       </c>
       <c r="Y26" s="1">
-        <v>-0.00087530955202509914</v>
+        <v>-0.00087531000732196022</v>
       </c>
       <c r="Z26" s="1">
-        <v>-0.0041168966624746395</v>
+        <v>-0.0041169010434046818</v>
       </c>
       <c r="AA26" s="1">
-        <v>0.043654628903262001</v>
+        <v>0.043654657103328776</v>
       </c>
       <c r="AB26" s="1">
-        <v>0.033410347013225435</v>
+        <v>0.033410373489918717</v>
       </c>
       <c r="AC26" s="1">
-        <v>0.033090718697742452</v>
+        <v>0.03309074412172882</v>
       </c>
       <c r="AD26" s="1">
-        <v>0.033133671920157051</v>
+        <v>0.033133695109569455</v>
       </c>
       <c r="AE26" s="1">
-        <v>-0.0010152527664961664</v>
+        <v>-0.0010152522136157999</v>
       </c>
       <c r="AF26" s="1">
-        <v>-0.0011136147704747107</v>
+        <v>-0.0011136142109015</v>
       </c>
       <c r="AG26" s="1">
-        <v>-0.0010173437725367121</v>
+        <v>-0.0010173454276143912</v>
       </c>
       <c r="AH26" s="1">
-        <v>-0.0014858547380677285</v>
+        <v>-0.0014858521525196056</v>
       </c>
       <c r="AI26" s="1">
-        <v>8.5119193703503794e-05</v>
+        <v>8.5118980370606006e-05</v>
       </c>
       <c r="AJ26" s="1">
-        <v>-0.036221113988364612</v>
+        <v>-0.036221105274777218</v>
       </c>
     </row>
     <row r="27">
@@ -3474,109 +3474,109 @@
         <v>53</v>
       </c>
       <c r="B27" s="1">
-        <v>0.11015124384203892</v>
+        <v>0.11015116053586904</v>
       </c>
       <c r="C27" s="1">
-        <v>0.00018567670333693382</v>
+        <v>0.0001856761243294749</v>
       </c>
       <c r="D27" s="1">
-        <v>-2.4238604987083328e-06</v>
+        <v>-2.4238540831881245e-06</v>
       </c>
       <c r="E27" s="1">
-        <v>-7.3158754373563379e-05</v>
+        <v>-7.3155372977507183e-05</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.00054904823955806577</v>
+        <v>-0.00054902349042574813</v>
       </c>
       <c r="G27" s="1">
-        <v>5.079873288942513e-05</v>
+        <v>5.0769764369736425e-05</v>
       </c>
       <c r="H27" s="1">
-        <v>0.0012909200246827952</v>
+        <v>0.0012908781300790455</v>
       </c>
       <c r="I27" s="1">
-        <v>0.00095366583503762067</v>
+        <v>0.00095363937490805777</v>
       </c>
       <c r="J27" s="1">
-        <v>0.00080027025396507494</v>
+        <v>0.00080024710286813417</v>
       </c>
       <c r="K27" s="1">
-        <v>0.00075503785750727294</v>
+        <v>0.00075501471886707202</v>
       </c>
       <c r="L27" s="1">
-        <v>-2.0981157616178544e-06</v>
+        <v>-2.0981096692396596e-06</v>
       </c>
       <c r="M27" s="1">
-        <v>0.00012965033361487074</v>
+        <v>0.00012961004372782534</v>
       </c>
       <c r="N27" s="1">
-        <v>0.0006588108616217759</v>
+        <v>0.00065878614965971525</v>
       </c>
       <c r="O27" s="1">
-        <v>0.00010537515792540115</v>
+        <v>0.00010540461684662774</v>
       </c>
       <c r="P27" s="1">
-        <v>-0.0013493896941073743</v>
+        <v>-0.0013493484205329192</v>
       </c>
       <c r="Q27" s="1">
-        <v>-0.0010687838955479323</v>
+        <v>-0.0010687574141367458</v>
       </c>
       <c r="R27" s="1">
-        <v>0.0019805528763011909</v>
+        <v>0.0019805358613256769</v>
       </c>
       <c r="S27" s="1">
-        <v>3.1517055233247985e-05</v>
+        <v>3.1519112336178982e-05</v>
       </c>
       <c r="T27" s="1">
-        <v>0.0014718242315567116</v>
+        <v>0.0014718284731292312</v>
       </c>
       <c r="U27" s="1">
-        <v>0.0003844508449420259</v>
+        <v>0.00038444393307387624</v>
       </c>
       <c r="V27" s="1">
-        <v>0.00094559018026992687</v>
+        <v>0.00094558752779508716</v>
       </c>
       <c r="W27" s="1">
-        <v>0.0028437564401453796</v>
+        <v>0.0028437504319016069</v>
       </c>
       <c r="X27" s="1">
-        <v>-3.4221704500507488e-05</v>
+        <v>-3.4184264503773739e-05</v>
       </c>
       <c r="Y27" s="1">
-        <v>-0.00050077404780717689</v>
+        <v>-0.00050077408182202404</v>
       </c>
       <c r="Z27" s="1">
-        <v>-0.004296450394178925</v>
+        <v>-0.0042964558844576541</v>
       </c>
       <c r="AA27" s="1">
-        <v>0.033410347013225435</v>
+        <v>0.033410373489918717</v>
       </c>
       <c r="AB27" s="1">
-        <v>0.034778083135877047</v>
+        <v>0.034778108976876158</v>
       </c>
       <c r="AC27" s="1">
-        <v>0.033110744601686108</v>
+        <v>0.033110769885681644</v>
       </c>
       <c r="AD27" s="1">
-        <v>0.033110989325248474</v>
+        <v>0.033111012990069043</v>
       </c>
       <c r="AE27" s="1">
-        <v>0.00030098046846332993</v>
+        <v>0.00030098029350094854</v>
       </c>
       <c r="AF27" s="1">
-        <v>-2.4721314694206575e-05</v>
+        <v>-2.4721173483496783e-05</v>
       </c>
       <c r="AG27" s="1">
-        <v>-2.3778582411863869e-05</v>
+        <v>-2.3779876808942974e-05</v>
       </c>
       <c r="AH27" s="1">
-        <v>-0.00041377644828047289</v>
+        <v>-0.00041377455476826301</v>
       </c>
       <c r="AI27" s="1">
-        <v>4.9651179102017887e-05</v>
+        <v>4.9651040352614861e-05</v>
       </c>
       <c r="AJ27" s="1">
-        <v>-0.038007019408667124</v>
+        <v>-0.038007011639291322</v>
       </c>
     </row>
     <row r="28">
@@ -3584,109 +3584,109 @@
         <v>54</v>
       </c>
       <c r="B28" s="1">
-        <v>0.24410154713459353</v>
+        <v>0.24410154982583507</v>
       </c>
       <c r="C28" s="1">
-        <v>0.00027216433663260849</v>
+        <v>0.0002721631116205628</v>
       </c>
       <c r="D28" s="1">
-        <v>-3.2995521669964297e-06</v>
+        <v>-3.2995384669150509e-06</v>
       </c>
       <c r="E28" s="1">
-        <v>-1.1438041462563317e-05</v>
+        <v>-1.1431143622900444e-05</v>
       </c>
       <c r="F28" s="1">
-        <v>0.00021462164673800727</v>
+        <v>0.00021466888148837968</v>
       </c>
       <c r="G28" s="1">
-        <v>-0.0011106461019369637</v>
+        <v>-0.0011107055319055823</v>
       </c>
       <c r="H28" s="1">
-        <v>0.001280286357059708</v>
+        <v>0.0012803152604903157</v>
       </c>
       <c r="I28" s="1">
-        <v>0.00089052257459676658</v>
+        <v>0.00089052550820354454</v>
       </c>
       <c r="J28" s="1">
-        <v>0.00051708052606190395</v>
+        <v>0.00051709016351411013</v>
       </c>
       <c r="K28" s="1">
-        <v>0.00047936991272410907</v>
+        <v>0.00047938011654964505</v>
       </c>
       <c r="L28" s="1">
-        <v>-2.4346361735282315e-06</v>
+        <v>-2.4346223368784393e-06</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.00015856665579679389</v>
+        <v>-0.00015865385418542037</v>
       </c>
       <c r="N28" s="1">
-        <v>-6.0746357221063579e-05</v>
+        <v>-6.0793594877364598e-05</v>
       </c>
       <c r="O28" s="1">
-        <v>0.0011343643529397095</v>
+        <v>0.0011344237115292494</v>
       </c>
       <c r="P28" s="1">
-        <v>-0.00099743106951099853</v>
+        <v>-0.00099746076431565713</v>
       </c>
       <c r="Q28" s="1">
-        <v>-0.0009899582283450334</v>
+        <v>-0.00098996098774364037</v>
       </c>
       <c r="R28" s="1">
-        <v>0.0021896637372197758</v>
+        <v>0.0021896889129765398</v>
       </c>
       <c r="S28" s="1">
-        <v>-0.00014215079327973708</v>
+        <v>-0.00014214722817850083</v>
       </c>
       <c r="T28" s="1">
-        <v>0.0013251497281150685</v>
+        <v>0.0013251575744512897</v>
       </c>
       <c r="U28" s="1">
-        <v>0.00045895734912721245</v>
+        <v>0.00045893973682302643</v>
       </c>
       <c r="V28" s="1">
-        <v>0.0013988845939846015</v>
+        <v>0.0013988751684769272</v>
       </c>
       <c r="W28" s="1">
-        <v>0.0044238886112669493</v>
+        <v>0.0044238794411727914</v>
       </c>
       <c r="X28" s="1">
-        <v>-1.9188727919082656e-05</v>
+        <v>-1.9107661574141341e-05</v>
       </c>
       <c r="Y28" s="1">
-        <v>-0.00063934648795909831</v>
+        <v>-0.00063934518325461866</v>
       </c>
       <c r="Z28" s="1">
-        <v>-0.0045649412919171453</v>
+        <v>-0.00456495111237814</v>
       </c>
       <c r="AA28" s="1">
-        <v>0.033090718697742452</v>
+        <v>0.03309074412172882</v>
       </c>
       <c r="AB28" s="1">
-        <v>0.033110744601686108</v>
+        <v>0.033110769885681644</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.034076604171886626</v>
+        <v>0.034076629970654124</v>
       </c>
       <c r="AD28" s="1">
-        <v>0.033722300174020739</v>
+        <v>0.033722321730033672</v>
       </c>
       <c r="AE28" s="1">
-        <v>-5.8243164690989502e-05</v>
+        <v>-5.8243557058572371e-05</v>
       </c>
       <c r="AF28" s="1">
-        <v>-0.00011531365458565881</v>
+        <v>-0.00011531401975724276</v>
       </c>
       <c r="AG28" s="1">
-        <v>-0.00018458127965678695</v>
+        <v>-0.00018458300005277234</v>
       </c>
       <c r="AH28" s="1">
-        <v>-0.0004244716848399218</v>
+        <v>-0.00042446786424405088</v>
       </c>
       <c r="AI28" s="1">
-        <v>5.2819278881634105e-05</v>
+        <v>5.2818828385813553e-05</v>
       </c>
       <c r="AJ28" s="1">
-        <v>-0.040188561898431015</v>
+        <v>-0.040188573566529218</v>
       </c>
     </row>
     <row r="29">
@@ -3694,109 +3694,109 @@
         <v>55</v>
       </c>
       <c r="B29" s="1">
-        <v>0.26693863652739608</v>
+        <v>0.26693843291278019</v>
       </c>
       <c r="C29" s="1">
-        <v>0.00030867299995009328</v>
+        <v>0.00030867171528705664</v>
       </c>
       <c r="D29" s="1">
-        <v>-3.4769203898458093e-06</v>
+        <v>-3.4769053911115863e-06</v>
       </c>
       <c r="E29" s="1">
-        <v>-0.00018837488119969307</v>
+        <v>-0.00018837144918692252</v>
       </c>
       <c r="F29" s="1">
-        <v>8.8997508597785471e-05</v>
+        <v>8.9021670287227347e-05</v>
       </c>
       <c r="G29" s="1">
-        <v>-0.00092497854492216503</v>
+        <v>-0.00092500781081141588</v>
       </c>
       <c r="H29" s="1">
-        <v>0.0013333477758047602</v>
+        <v>0.0013333321402453685</v>
       </c>
       <c r="I29" s="1">
-        <v>0.0011087375670186116</v>
+        <v>0.0011087260215954862</v>
       </c>
       <c r="J29" s="1">
-        <v>0.00094024159745541747</v>
+        <v>0.00094023421966154923</v>
       </c>
       <c r="K29" s="1">
-        <v>0.00070862514206416615</v>
+        <v>0.00070861775940705344</v>
       </c>
       <c r="L29" s="1">
-        <v>-4.5235708657253057e-06</v>
+        <v>-4.5235570759690248e-06</v>
       </c>
       <c r="M29" s="1">
-        <v>0.0003414405195197454</v>
+        <v>0.00034137712015042148</v>
       </c>
       <c r="N29" s="1">
-        <v>-7.7309386278263758e-05</v>
+        <v>-7.7333597548716101e-05</v>
       </c>
       <c r="O29" s="1">
-        <v>0.0021325859165402337</v>
+        <v>0.0021326155523656008</v>
       </c>
       <c r="P29" s="1">
-        <v>-0.0017032347213842875</v>
+        <v>-0.0017032201811214059</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.001021967531757287</v>
+        <v>-0.0010219560788936339</v>
       </c>
       <c r="R29" s="1">
-        <v>0.0030428932784123015</v>
+        <v>0.0030428894952357483</v>
       </c>
       <c r="S29" s="1">
-        <v>-0.00023048613456717486</v>
+        <v>-0.00023048315153529489</v>
       </c>
       <c r="T29" s="1">
-        <v>0.0013170876056563295</v>
+        <v>0.0013170966214355853</v>
       </c>
       <c r="U29" s="1">
-        <v>0.00052097862207196692</v>
+        <v>0.00052096909584485639</v>
       </c>
       <c r="V29" s="1">
-        <v>0.0014976277596562902</v>
+        <v>0.0014976235357974229</v>
       </c>
       <c r="W29" s="1">
-        <v>0.0042040847507722207</v>
+        <v>0.0042040633144781996</v>
       </c>
       <c r="X29" s="1">
-        <v>-9.9838153052033844e-05</v>
+        <v>-9.9777223667691766e-05</v>
       </c>
       <c r="Y29" s="1">
-        <v>-0.00054275295418507294</v>
+        <v>-0.00054275266514096409</v>
       </c>
       <c r="Z29" s="1">
-        <v>-0.0043929145622734487</v>
+        <v>-0.004392910459090231</v>
       </c>
       <c r="AA29" s="1">
-        <v>0.033133671920157051</v>
+        <v>0.033133695109569455</v>
       </c>
       <c r="AB29" s="1">
-        <v>0.033110989325248474</v>
+        <v>0.033111012990069043</v>
       </c>
       <c r="AC29" s="1">
-        <v>0.033722300174020739</v>
+        <v>0.033722321730033672</v>
       </c>
       <c r="AD29" s="1">
-        <v>0.035136798335526589</v>
+        <v>0.035136817297709941</v>
       </c>
       <c r="AE29" s="1">
-        <v>-0.00017176689705988152</v>
+        <v>-0.00017176492639859112</v>
       </c>
       <c r="AF29" s="1">
-        <v>-0.00014862763542372592</v>
+        <v>-0.00014862599957986972</v>
       </c>
       <c r="AG29" s="1">
-        <v>-0.00035524006558070031</v>
+        <v>-0.00035523944340996524</v>
       </c>
       <c r="AH29" s="1">
-        <v>-0.00045448961569683095</v>
+        <v>-0.00045448431836674248</v>
       </c>
       <c r="AI29" s="1">
-        <v>6.7001977985216158e-05</v>
+        <v>6.7001616334765902e-05</v>
       </c>
       <c r="AJ29" s="1">
-        <v>-0.041779007192421634</v>
+        <v>-0.04177899658376253</v>
       </c>
     </row>
     <row r="30">
@@ -3804,109 +3804,109 @@
         <v>56</v>
       </c>
       <c r="B30" s="1">
-        <v>-0.25184093125705004</v>
+        <v>-0.25184094707735866</v>
       </c>
       <c r="C30" s="1">
-        <v>2.8306155158717983e-05</v>
+        <v>2.830682841456066e-05</v>
       </c>
       <c r="D30" s="1">
-        <v>-4.6530067114586417e-07</v>
+        <v>-4.6530828621832126e-07</v>
       </c>
       <c r="E30" s="1">
-        <v>-0.00012273045915808225</v>
+        <v>-0.00012273342236003787</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.00068920773046776869</v>
+        <v>-0.00068922790808510315</v>
       </c>
       <c r="G30" s="1">
-        <v>0.00036246944289637818</v>
+        <v>0.00036249608349150068</v>
       </c>
       <c r="H30" s="1">
-        <v>-0.00022764615778182317</v>
+        <v>-0.0002276934939397725</v>
       </c>
       <c r="I30" s="1">
-        <v>0.00018515964929681863</v>
+        <v>0.0001851409498239585</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.00015824604240486598</v>
+        <v>-0.0001582678783063271</v>
       </c>
       <c r="K30" s="1">
-        <v>-0.00011139281263663537</v>
+        <v>-0.00011141497727708239</v>
       </c>
       <c r="L30" s="1">
-        <v>4.4400896091903215e-06</v>
+        <v>4.4400809961128004e-06</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.00058770407094079456</v>
+        <v>-0.00058765735309021148</v>
       </c>
       <c r="N30" s="1">
-        <v>0.0010486135199391446</v>
+        <v>0.0010486336585187345</v>
       </c>
       <c r="O30" s="1">
-        <v>-0.0013368946061808468</v>
+        <v>-0.0013369206528558528</v>
       </c>
       <c r="P30" s="1">
-        <v>0.00082274511580136649</v>
+        <v>0.00082279271795957453</v>
       </c>
       <c r="Q30" s="1">
-        <v>-0.00027500039645306489</v>
+        <v>-0.00027498171943266436</v>
       </c>
       <c r="R30" s="1">
-        <v>-0.0022741039098323756</v>
+        <v>-0.0022741328759806377</v>
       </c>
       <c r="S30" s="1">
-        <v>0.00017618675069047652</v>
+        <v>0.00017618521493156114</v>
       </c>
       <c r="T30" s="1">
-        <v>0.00022376987210187766</v>
+        <v>0.00022376598806957007</v>
       </c>
       <c r="U30" s="1">
-        <v>0.00015500000377794039</v>
+        <v>0.0001550095405156598</v>
       </c>
       <c r="V30" s="1">
-        <v>0.00039624205824750013</v>
+        <v>0.00039624795617099174</v>
       </c>
       <c r="W30" s="1">
-        <v>0.00036201459339322943</v>
+        <v>0.0003620217927259228</v>
       </c>
       <c r="X30" s="1">
-        <v>0.0003769908640358129</v>
+        <v>0.00037694680403458784</v>
       </c>
       <c r="Y30" s="1">
-        <v>-0.00027790953618879916</v>
+        <v>-0.0002779103528453871</v>
       </c>
       <c r="Z30" s="1">
-        <v>0.00046802280151084685</v>
+        <v>0.00046802323159536737</v>
       </c>
       <c r="AA30" s="1">
-        <v>-0.0010152527664961664</v>
+        <v>-0.0010152522136157999</v>
       </c>
       <c r="AB30" s="1">
-        <v>0.00030098046846332993</v>
+        <v>0.00030098029350094854</v>
       </c>
       <c r="AC30" s="1">
-        <v>-5.8243164690989502e-05</v>
+        <v>-5.8243557058572371e-05</v>
       </c>
       <c r="AD30" s="1">
-        <v>-0.00017176689705988152</v>
+        <v>-0.00017176492639859112</v>
       </c>
       <c r="AE30" s="1">
-        <v>0.0037641400632581661</v>
+        <v>0.0037641396618699713</v>
       </c>
       <c r="AF30" s="1">
-        <v>0.0015273483635365155</v>
+        <v>0.0015273484024230781</v>
       </c>
       <c r="AG30" s="1">
-        <v>0.0015186569159106288</v>
+        <v>0.0015186569252580186</v>
       </c>
       <c r="AH30" s="1">
-        <v>0.0015405633018791037</v>
+        <v>0.001540560885448253</v>
       </c>
       <c r="AI30" s="1">
-        <v>-4.1847816384267447e-05</v>
+        <v>-4.18475123690236e-05</v>
       </c>
       <c r="AJ30" s="1">
-        <v>-0.0010558889646960254</v>
+        <v>-0.0010558811699179686</v>
       </c>
     </row>
     <row r="31">
@@ -3914,109 +3914,109 @@
         <v>57</v>
       </c>
       <c r="B31" s="1">
-        <v>-0.060629487506229977</v>
+        <v>-0.060629539577290809</v>
       </c>
       <c r="C31" s="1">
-        <v>1.4010557329755002e-05</v>
+        <v>1.4011033407124152e-05</v>
       </c>
       <c r="D31" s="1">
-        <v>-4.2677078782167945e-07</v>
+        <v>-4.2677608011418802e-07</v>
       </c>
       <c r="E31" s="1">
-        <v>-0.00031380160237652751</v>
+        <v>-0.00031380434301005389</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.00074261486021463287</v>
+        <v>-0.00074263182783332999</v>
       </c>
       <c r="G31" s="1">
-        <v>0.0006706085670580399</v>
+        <v>0.00067063065013258814</v>
       </c>
       <c r="H31" s="1">
-        <v>-0.00015800481647704591</v>
+        <v>-0.00015804634116542741</v>
       </c>
       <c r="I31" s="1">
-        <v>0.00014858417056414852</v>
+        <v>0.00014856841844449538</v>
       </c>
       <c r="J31" s="1">
-        <v>-6.9300398554017484e-05</v>
+        <v>-6.9318641952183756e-05</v>
       </c>
       <c r="K31" s="1">
-        <v>5.1587903793503978e-05</v>
+        <v>5.1569399446359352e-05</v>
       </c>
       <c r="L31" s="1">
-        <v>4.292905518051713e-07</v>
+        <v>4.2928444219119012e-07</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.00083940235688644764</v>
+        <v>-0.00083935554587755774</v>
       </c>
       <c r="N31" s="1">
-        <v>0.00090958295402581487</v>
+        <v>0.00090959987842161385</v>
       </c>
       <c r="O31" s="1">
-        <v>-0.00099755028886579179</v>
+        <v>-0.00099757173653873413</v>
       </c>
       <c r="P31" s="1">
-        <v>0.0002046872350920159</v>
+        <v>0.00020472890353622766</v>
       </c>
       <c r="Q31" s="1">
-        <v>-0.00039070884820706223</v>
+        <v>-0.0003906930612574877</v>
       </c>
       <c r="R31" s="1">
-        <v>-0.00043031835099130011</v>
+        <v>-0.00043034432677351931</v>
       </c>
       <c r="S31" s="1">
-        <v>0.0003121363929166007</v>
+        <v>0.00031213487705179029</v>
       </c>
       <c r="T31" s="1">
-        <v>0.00042249326609627839</v>
+        <v>0.0004224905312752603</v>
       </c>
       <c r="U31" s="1">
-        <v>-5.6273158599957733e-05</v>
+        <v>-5.6264564034130046e-05</v>
       </c>
       <c r="V31" s="1">
-        <v>0.00010808242997750175</v>
+        <v>0.00010808781239745116</v>
       </c>
       <c r="W31" s="1">
-        <v>0.00031982046674714892</v>
+        <v>0.00031982494042713961</v>
       </c>
       <c r="X31" s="1">
-        <v>0.0010964550581072756</v>
+        <v>0.0010964108369845653</v>
       </c>
       <c r="Y31" s="1">
-        <v>0.00081060085130532243</v>
+        <v>0.00081060045060951864</v>
       </c>
       <c r="Z31" s="1">
-        <v>0.0010389042213836126</v>
+        <v>0.0010389060816005636</v>
       </c>
       <c r="AA31" s="1">
-        <v>-0.0011136147704747107</v>
+        <v>-0.0011136142109015</v>
       </c>
       <c r="AB31" s="1">
-        <v>-2.4721314694206575e-05</v>
+        <v>-2.4721173483496783e-05</v>
       </c>
       <c r="AC31" s="1">
-        <v>-0.00011531365458565881</v>
+        <v>-0.00011531401975724276</v>
       </c>
       <c r="AD31" s="1">
-        <v>-0.00014862763542372592</v>
+        <v>-0.00014862599957986972</v>
       </c>
       <c r="AE31" s="1">
-        <v>0.0015273483635365155</v>
+        <v>0.0015273484024230781</v>
       </c>
       <c r="AF31" s="1">
-        <v>0.004134083030977522</v>
+        <v>0.0041340831146629954</v>
       </c>
       <c r="AG31" s="1">
-        <v>0.0014952937939715968</v>
+        <v>0.0014952940104161849</v>
       </c>
       <c r="AH31" s="1">
-        <v>0.0015296115370160564</v>
+        <v>0.0015296098529544687</v>
       </c>
       <c r="AI31" s="1">
-        <v>-5.9279594871891383e-05</v>
+        <v>-5.9279351112996112e-05</v>
       </c>
       <c r="AJ31" s="1">
-        <v>-0.00028181972673451322</v>
+        <v>-0.00028181129114678304</v>
       </c>
     </row>
     <row r="32">
@@ -4024,109 +4024,109 @@
         <v>58</v>
       </c>
       <c r="B32" s="1">
-        <v>-0.046200097557822097</v>
+        <v>-0.046200144732788953</v>
       </c>
       <c r="C32" s="1">
-        <v>1.2980007629815834e-05</v>
+        <v>1.2980567515141761e-05</v>
       </c>
       <c r="D32" s="1">
-        <v>-3.3515804808041737e-07</v>
+        <v>-3.3516418809115164e-07</v>
       </c>
       <c r="E32" s="1">
-        <v>-0.00021590371231865863</v>
+        <v>-0.00021590707885969199</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.00052810991246496233</v>
+        <v>-0.00052813191026200123</v>
       </c>
       <c r="G32" s="1">
-        <v>0.00054409039338993727</v>
+        <v>0.00054411851541867748</v>
       </c>
       <c r="H32" s="1">
-        <v>-0.00052665838886137338</v>
+        <v>-0.00052667882768670632</v>
       </c>
       <c r="I32" s="1">
-        <v>-0.00020112699055516723</v>
+        <v>-0.00020113127159360937</v>
       </c>
       <c r="J32" s="1">
-        <v>-0.00054973084875415529</v>
+        <v>-0.00054973821265992106</v>
       </c>
       <c r="K32" s="1">
-        <v>-0.00036123603703072356</v>
+        <v>-0.00036124367583604243</v>
       </c>
       <c r="L32" s="1">
-        <v>7.5330351062645062e-07</v>
+        <v>7.5329654653562808e-07</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.0015312475788527139</v>
+        <v>-0.0015311927441856647</v>
       </c>
       <c r="N32" s="1">
-        <v>0.00060365429806158129</v>
+        <v>0.0006036763224574256</v>
       </c>
       <c r="O32" s="1">
-        <v>-0.00055831274026123582</v>
+        <v>-0.000558340294624602</v>
       </c>
       <c r="P32" s="1">
-        <v>0.00065540162007077479</v>
+        <v>0.0006554222937715376</v>
       </c>
       <c r="Q32" s="1">
-        <v>0.00011919758549663439</v>
+        <v>0.00011920178109120407</v>
       </c>
       <c r="R32" s="1">
-        <v>-0.00088213111602639159</v>
+        <v>-0.00088214740572244328</v>
       </c>
       <c r="S32" s="1">
-        <v>7.2295083887269904e-05</v>
+        <v>7.229352290737416e-05</v>
       </c>
       <c r="T32" s="1">
-        <v>-8.6273934951553886e-06</v>
+        <v>-8.630295008686781e-06</v>
       </c>
       <c r="U32" s="1">
-        <v>-0.00016824470899227733</v>
+        <v>-0.00016823469905785171</v>
       </c>
       <c r="V32" s="1">
-        <v>-9.6583823432491375e-06</v>
+        <v>-9.6530104149574001e-06</v>
       </c>
       <c r="W32" s="1">
-        <v>-0.00012040417886888038</v>
+        <v>-0.00012039869753297178</v>
       </c>
       <c r="X32" s="1">
-        <v>0.0015912784212669055</v>
+        <v>0.0015912267080273716</v>
       </c>
       <c r="Y32" s="1">
-        <v>1.4580298977568003e-05</v>
+        <v>1.4579944281017444e-05</v>
       </c>
       <c r="Z32" s="1">
-        <v>0.00096431689757602577</v>
+        <v>0.00096431815534253596</v>
       </c>
       <c r="AA32" s="1">
-        <v>-0.0010173437725367121</v>
+        <v>-0.0010173454276143912</v>
       </c>
       <c r="AB32" s="1">
-        <v>-2.3778582411863869e-05</v>
+        <v>-2.3779876808942974e-05</v>
       </c>
       <c r="AC32" s="1">
-        <v>-0.00018458127965678695</v>
+        <v>-0.00018458300005277234</v>
       </c>
       <c r="AD32" s="1">
-        <v>-0.00035524006558070031</v>
+        <v>-0.00035523944340996524</v>
       </c>
       <c r="AE32" s="1">
-        <v>0.0015186569159106288</v>
+        <v>0.0015186569252580186</v>
       </c>
       <c r="AF32" s="1">
-        <v>0.0014952937939715968</v>
+        <v>0.0014952940104161849</v>
       </c>
       <c r="AG32" s="1">
-        <v>0.0031117257520295975</v>
+        <v>0.0031117262795438902</v>
       </c>
       <c r="AH32" s="1">
-        <v>0.001534630412742417</v>
+        <v>0.0015346284013570653</v>
       </c>
       <c r="AI32" s="1">
-        <v>-4.375630943063083e-05</v>
+        <v>-4.3756017451500009e-05</v>
       </c>
       <c r="AJ32" s="1">
-        <v>-3.6235736918478287e-05</v>
+        <v>-3.6238890249377073e-05</v>
       </c>
     </row>
     <row r="33">
@@ -4134,109 +4134,109 @@
         <v>59</v>
       </c>
       <c r="B33" s="1">
-        <v>-0.051738269916782237</v>
+        <v>-0.051738108309649547</v>
       </c>
       <c r="C33" s="1">
-        <v>-1.4684746289809949e-05</v>
+        <v>-1.4683798727084237e-05</v>
       </c>
       <c r="D33" s="1">
-        <v>-3.3140509847197309e-08</v>
+        <v>-3.3151959867674149e-08</v>
       </c>
       <c r="E33" s="1">
-        <v>-0.00013733134413083611</v>
+        <v>-0.00013733253135790249</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.00061377970312598783</v>
+        <v>-0.00061378660768325577</v>
       </c>
       <c r="G33" s="1">
-        <v>0.00059340243601426975</v>
+        <v>0.00059341155444972221</v>
       </c>
       <c r="H33" s="1">
-        <v>-0.00032616092452972516</v>
+        <v>-0.00032618408341076569</v>
       </c>
       <c r="I33" s="1">
-        <v>-8.2837029022211385e-05</v>
+        <v>-8.2849051703585063e-05</v>
       </c>
       <c r="J33" s="1">
-        <v>-0.00023504201985235867</v>
+        <v>-0.00023505605931662017</v>
       </c>
       <c r="K33" s="1">
-        <v>-0.00010943466550209239</v>
+        <v>-0.00010944867271054238</v>
       </c>
       <c r="L33" s="1">
-        <v>1.077298916194304e-06</v>
+        <v>1.0772886760087006e-06</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.00040689007326995258</v>
+        <v>-0.00040685291637317328</v>
       </c>
       <c r="N33" s="1">
-        <v>0.00065404642993176253</v>
+        <v>0.0006540534486385067</v>
       </c>
       <c r="O33" s="1">
-        <v>-0.00082746801792375247</v>
+        <v>-0.00082747705981522923</v>
       </c>
       <c r="P33" s="1">
-        <v>0.00080271938113848213</v>
+        <v>0.0008027432583743798</v>
       </c>
       <c r="Q33" s="1">
-        <v>7.5570380833825694e-05</v>
+        <v>7.5582502988888207e-05</v>
       </c>
       <c r="R33" s="1">
-        <v>-0.00091133084550964636</v>
+        <v>-0.00091134324601960942</v>
       </c>
       <c r="S33" s="1">
-        <v>6.486253400155248e-05</v>
+        <v>6.4861127199437874e-05</v>
       </c>
       <c r="T33" s="1">
-        <v>2.8575703177091726e-05</v>
+        <v>2.8569507144557567e-05</v>
       </c>
       <c r="U33" s="1">
-        <v>-8.7676072208330968e-05</v>
+        <v>-8.7671795737625201e-05</v>
       </c>
       <c r="V33" s="1">
-        <v>0.00034669772075719674</v>
+        <v>0.0003467001962749103</v>
       </c>
       <c r="W33" s="1">
-        <v>0.00021893459766924878</v>
+        <v>0.00021895507304873184</v>
       </c>
       <c r="X33" s="1">
-        <v>0.00015754607991397008</v>
+        <v>0.00015750949471764002</v>
       </c>
       <c r="Y33" s="1">
-        <v>-0.00014861080013463788</v>
+        <v>-0.00014861025833640698</v>
       </c>
       <c r="Z33" s="1">
-        <v>0.00098589782534238266</v>
+        <v>0.00098588627907654578</v>
       </c>
       <c r="AA33" s="1">
-        <v>-0.0014858547380677285</v>
+        <v>-0.0014858521525196056</v>
       </c>
       <c r="AB33" s="1">
-        <v>-0.00041377644828047289</v>
+        <v>-0.00041377455476826301</v>
       </c>
       <c r="AC33" s="1">
-        <v>-0.0004244716848399218</v>
+        <v>-0.00042446786424405088</v>
       </c>
       <c r="AD33" s="1">
-        <v>-0.00045448961569683095</v>
+        <v>-0.00045448431836674248</v>
       </c>
       <c r="AE33" s="1">
-        <v>0.0015405633018791037</v>
+        <v>0.001540560885448253</v>
       </c>
       <c r="AF33" s="1">
-        <v>0.0015296115370160564</v>
+        <v>0.0015296098529544687</v>
       </c>
       <c r="AG33" s="1">
-        <v>0.001534630412742417</v>
+        <v>0.0015346284013570653</v>
       </c>
       <c r="AH33" s="1">
-        <v>0.0022512604055832637</v>
+        <v>0.0022512556407537992</v>
       </c>
       <c r="AI33" s="1">
-        <v>-2.871613435686728e-05</v>
+        <v>-2.8715798859384648e-05</v>
       </c>
       <c r="AJ33" s="1">
-        <v>0.00016458093995394232</v>
+        <v>0.00016457147827321199</v>
       </c>
     </row>
     <row r="34">
@@ -4244,109 +4244,109 @@
         <v>60</v>
       </c>
       <c r="B34" s="1">
-        <v>-0.0060244098339248637</v>
+        <v>-0.0060244345143469899</v>
       </c>
       <c r="C34" s="1">
-        <v>1.3508909798347709e-06</v>
+        <v>1.3508352144051095e-06</v>
       </c>
       <c r="D34" s="1">
-        <v>-1.4179325650530169e-08</v>
+        <v>-1.4178591810838709e-08</v>
       </c>
       <c r="E34" s="1">
-        <v>1.255474364764266e-05</v>
+        <v>1.2554507273252845e-05</v>
       </c>
       <c r="F34" s="1">
-        <v>2.8263956674194945e-05</v>
+        <v>2.8262430894677129e-05</v>
       </c>
       <c r="G34" s="1">
-        <v>-4.9085173872531317e-06</v>
+        <v>-4.9064600933876577e-06</v>
       </c>
       <c r="H34" s="1">
-        <v>1.741585922386649e-05</v>
+        <v>1.741361451819347e-05</v>
       </c>
       <c r="I34" s="1">
-        <v>-1.1382031392512905e-05</v>
+        <v>-1.1382495404554734e-05</v>
       </c>
       <c r="J34" s="1">
-        <v>1.6892235833482138e-05</v>
+        <v>1.6891683437225403e-05</v>
       </c>
       <c r="K34" s="1">
-        <v>6.92294932858807e-06</v>
+        <v>6.9223646815861164e-06</v>
       </c>
       <c r="L34" s="1">
-        <v>-1.095475173806463e-07</v>
+        <v>-1.0954698894729772e-07</v>
       </c>
       <c r="M34" s="1">
-        <v>7.8180339552315871e-05</v>
+        <v>7.8179977916636271e-05</v>
       </c>
       <c r="N34" s="1">
-        <v>-3.4080275595777481e-05</v>
+        <v>-3.4078760430860555e-05</v>
       </c>
       <c r="O34" s="1">
-        <v>0.0001052582253889805</v>
+        <v>0.00010525621071217467</v>
       </c>
       <c r="P34" s="1">
-        <v>-6.4181064908078493e-05</v>
+        <v>-6.4178888676449887e-05</v>
       </c>
       <c r="Q34" s="1">
-        <v>3.0056149226279118e-05</v>
+        <v>3.0056586912962483e-05</v>
       </c>
       <c r="R34" s="1">
-        <v>7.6740339025009645e-05</v>
+        <v>7.6738729491253099e-05</v>
       </c>
       <c r="S34" s="1">
-        <v>-6.7537652868699089e-06</v>
+        <v>-6.7537647739472544e-06</v>
       </c>
       <c r="T34" s="1">
-        <v>-2.2950643318548713e-05</v>
+        <v>-2.2950196029828196e-05</v>
       </c>
       <c r="U34" s="1">
-        <v>-2.1703262709490235e-05</v>
+        <v>-2.1702851173267926e-05</v>
       </c>
       <c r="V34" s="1">
-        <v>9.5242212030431184e-06</v>
+        <v>9.5244833799189088e-06</v>
       </c>
       <c r="W34" s="1">
-        <v>4.4505427961633655e-05</v>
+        <v>4.4503369386830765e-05</v>
       </c>
       <c r="X34" s="1">
-        <v>-5.1615415216511252e-05</v>
+        <v>-5.1614765393145311e-05</v>
       </c>
       <c r="Y34" s="1">
-        <v>-1.9385936279865803e-05</v>
+        <v>-1.9386021213623964e-05</v>
       </c>
       <c r="Z34" s="1">
-        <v>-5.7772010166039358e-05</v>
+        <v>-5.7770308370495986e-05</v>
       </c>
       <c r="AA34" s="1">
-        <v>8.5119193703503794e-05</v>
+        <v>8.5118980370606006e-05</v>
       </c>
       <c r="AB34" s="1">
-        <v>4.9651179102017887e-05</v>
+        <v>4.9651040352614861e-05</v>
       </c>
       <c r="AC34" s="1">
-        <v>5.2819278881634105e-05</v>
+        <v>5.2818828385813553e-05</v>
       </c>
       <c r="AD34" s="1">
-        <v>6.7001977985216158e-05</v>
+        <v>6.7001616334765902e-05</v>
       </c>
       <c r="AE34" s="1">
-        <v>-4.1847816384267447e-05</v>
+        <v>-4.18475123690236e-05</v>
       </c>
       <c r="AF34" s="1">
-        <v>-5.9279594871891383e-05</v>
+        <v>-5.9279351112996112e-05</v>
       </c>
       <c r="AG34" s="1">
-        <v>-4.375630943063083e-05</v>
+        <v>-4.3756017451500009e-05</v>
       </c>
       <c r="AH34" s="1">
-        <v>-2.871613435686728e-05</v>
+        <v>-2.8715798859384648e-05</v>
       </c>
       <c r="AI34" s="1">
-        <v>1.7327282620786212e-05</v>
+        <v>1.7327270256940869e-05</v>
       </c>
       <c r="AJ34" s="1">
-        <v>-0.00035286124494220676</v>
+        <v>-0.00035285907174844282</v>
       </c>
     </row>
     <row r="35">
@@ -4354,109 +4354,109 @@
         <v>61</v>
       </c>
       <c r="B35" s="1">
-        <v>-2.7723564291793328</v>
+        <v>-2.7723575260364464</v>
       </c>
       <c r="C35" s="1">
-        <v>-0.0013737123397219745</v>
+        <v>-0.0013737078679931687</v>
       </c>
       <c r="D35" s="1">
-        <v>1.5790998508530073e-05</v>
+        <v>1.5790947878286583e-05</v>
       </c>
       <c r="E35" s="1">
-        <v>-0.0016426316723233468</v>
+        <v>-0.0016426595337495859</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.0011750187512226927</v>
+        <v>-0.001175206529903489</v>
       </c>
       <c r="G35" s="1">
-        <v>0.003153343902905724</v>
+        <v>0.0031535685407946853</v>
       </c>
       <c r="H35" s="1">
-        <v>-0.0041704967322112648</v>
+        <v>-0.0041704531396316007</v>
       </c>
       <c r="I35" s="1">
-        <v>-0.0050700104057033457</v>
+        <v>-0.0050699305737094292</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.0042334005449576658</v>
+        <v>-0.0042333473785687919</v>
       </c>
       <c r="K35" s="1">
-        <v>-0.0035354693203620263</v>
+        <v>-0.003535421964164176</v>
       </c>
       <c r="L35" s="1">
-        <v>1.6779554080713748e-05</v>
+        <v>1.6779497768927856e-05</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.0013021000706258184</v>
+        <v>-0.0013017685543056099</v>
       </c>
       <c r="N35" s="1">
-        <v>0.0010170009906308327</v>
+        <v>0.0010171896024913155</v>
       </c>
       <c r="O35" s="1">
-        <v>-0.0053909412826583193</v>
+        <v>-0.00539115883428847</v>
       </c>
       <c r="P35" s="1">
-        <v>0.0048065304216768009</v>
+        <v>0.0048064846317256498</v>
       </c>
       <c r="Q35" s="1">
-        <v>0.0047876597521996737</v>
+        <v>0.0047875786038323407</v>
       </c>
       <c r="R35" s="1">
-        <v>-0.010998605998748573</v>
+        <v>-0.010998614188305545</v>
       </c>
       <c r="S35" s="1">
-        <v>3.1364143138344527e-05</v>
+        <v>3.1360999121017139e-05</v>
       </c>
       <c r="T35" s="1">
-        <v>-0.0021652790651327616</v>
+        <v>-0.0021652901197315145</v>
       </c>
       <c r="U35" s="1">
-        <v>-0.0064323605706343061</v>
+        <v>-0.0064322909137250802</v>
       </c>
       <c r="V35" s="1">
-        <v>-0.0064858051857528661</v>
+        <v>-0.0064857559771050741</v>
       </c>
       <c r="W35" s="1">
-        <v>-0.014883233683877379</v>
+        <v>-0.014883237726560338</v>
       </c>
       <c r="X35" s="1">
-        <v>0.0026349564350518851</v>
+        <v>0.0026346536810663633</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.0022491514371111264</v>
+        <v>0.0022491442655312504</v>
       </c>
       <c r="Z35" s="1">
-        <v>0.0066110299369622856</v>
+        <v>0.0066110870669499602</v>
       </c>
       <c r="AA35" s="1">
-        <v>-0.036221113988364612</v>
+        <v>-0.036221105274777218</v>
       </c>
       <c r="AB35" s="1">
-        <v>-0.038007019408667124</v>
+        <v>-0.038007011639291322</v>
       </c>
       <c r="AC35" s="1">
-        <v>-0.040188561898431015</v>
+        <v>-0.040188573566529218</v>
       </c>
       <c r="AD35" s="1">
-        <v>-0.041779007192421634</v>
+        <v>-0.04177899658376253</v>
       </c>
       <c r="AE35" s="1">
-        <v>-0.0010558889646960254</v>
+        <v>-0.0010558811699179686</v>
       </c>
       <c r="AF35" s="1">
-        <v>-0.00028181972673451322</v>
+        <v>-0.00028181129114678304</v>
       </c>
       <c r="AG35" s="1">
-        <v>-3.6235736918478287e-05</v>
+        <v>-3.6238890249377073e-05</v>
       </c>
       <c r="AH35" s="1">
-        <v>0.00016458093995394232</v>
+        <v>0.00016457147827321199</v>
       </c>
       <c r="AI35" s="1">
-        <v>-0.00035286124494220676</v>
+        <v>-0.00035285907174844282</v>
       </c>
       <c r="AJ35" s="1">
-        <v>0.078769514084071943</v>
+        <v>0.078769372297352522</v>
       </c>
     </row>
   </sheetData>
@@ -4571,97 +4571,97 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>-0.025228605010735879</v>
+        <v>-0.025228497416873625</v>
       </c>
       <c r="C2" s="1">
-        <v>0.00055806143968301688</v>
+        <v>0.00055806930973726547</v>
       </c>
       <c r="D2" s="1">
-        <v>-6.0548675242872845e-06</v>
+        <v>-6.0548233648848763e-06</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.00058292138627771611</v>
+        <v>-0.00058303130056590021</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.00086673648140286278</v>
+        <v>-0.00086719470323466837</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.00035776438291415047</v>
+        <v>-0.00035770895224943467</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.00028850856852084914</v>
+        <v>-0.00028869149003215959</v>
       </c>
       <c r="I2" s="1">
-        <v>0.00063526755217745514</v>
+        <v>0.00063515809289935144</v>
       </c>
       <c r="J2" s="1">
-        <v>0.00010883418281920675</v>
+        <v>0.00010867570444683845</v>
       </c>
       <c r="K2" s="1">
-        <v>-0.00029724231765264602</v>
+        <v>-0.00029738610970855405</v>
       </c>
       <c r="L2" s="1">
-        <v>0.00058630261660466004</v>
+        <v>0.00058635472405529996</v>
       </c>
       <c r="M2" s="1">
-        <v>0.00040615024740175455</v>
+        <v>0.00040613142250768564</v>
       </c>
       <c r="N2" s="1">
-        <v>5.1871304811644016e-05</v>
+        <v>5.1858262607997092e-05</v>
       </c>
       <c r="O2" s="1">
-        <v>-0.00039732740847369871</v>
+        <v>-0.0003972812937142918</v>
       </c>
       <c r="P2" s="1">
-        <v>9.2906843662638253e-05</v>
+        <v>9.2841113122441726e-05</v>
       </c>
       <c r="Q2" s="1">
-        <v>2.8976100766404771e-05</v>
+        <v>2.896817457769419e-05</v>
       </c>
       <c r="R2" s="1">
-        <v>0.0015184973318481448</v>
+        <v>0.001518478574723589</v>
       </c>
       <c r="S2" s="1">
-        <v>1.0520651332400315e-05</v>
+        <v>1.0501160474891405e-05</v>
       </c>
       <c r="T2" s="1">
-        <v>-0.00045865257229149234</v>
+        <v>-0.00045863943671137089</v>
       </c>
       <c r="U2" s="1">
-        <v>0.0011027093129918984</v>
+        <v>0.0011026803263152309</v>
       </c>
       <c r="V2" s="1">
-        <v>-0.0009892943672806789</v>
+        <v>-0.0009895375374750796</v>
       </c>
       <c r="W2" s="1">
-        <v>9.2701637546029579e-05</v>
+        <v>9.2652958846682967e-05</v>
       </c>
       <c r="X2" s="1">
-        <v>0.00030853261464035622</v>
+        <v>0.00030818262871681185</v>
       </c>
       <c r="Y2" s="1">
-        <v>-0.00014697756733043649</v>
+        <v>-0.00014700104082355245</v>
       </c>
       <c r="Z2" s="1">
-        <v>0.00011497494913592221</v>
+        <v>0.00011500059771742547</v>
       </c>
       <c r="AA2" s="1">
-        <v>0.00065169033588002726</v>
+        <v>0.00065214208182064149</v>
       </c>
       <c r="AB2" s="1">
-        <v>-3.8732907299534637e-05</v>
+        <v>-3.8680784890090126e-05</v>
       </c>
       <c r="AC2" s="1">
-        <v>-0.000147587177066099</v>
+        <v>-0.00014729948729630057</v>
       </c>
       <c r="AD2" s="1">
-        <v>0.00010274618997860177</v>
+        <v>0.00010276638437329102</v>
       </c>
       <c r="AE2" s="1">
-        <v>2.6141751044661801e-05</v>
+        <v>2.6144706029497245e-05</v>
       </c>
       <c r="AF2" s="1">
-        <v>-0.010614376038956951</v>
+        <v>-0.010614498167765676</v>
       </c>
     </row>
     <row r="3">
@@ -4669,97 +4669,97 @@
         <v>29</v>
       </c>
       <c r="B3" s="1">
-        <v>0.00014919346363708301</v>
+        <v>0.00014922269784997715</v>
       </c>
       <c r="C3" s="1">
-        <v>-6.0548675242872845e-06</v>
+        <v>-6.0548233648848763e-06</v>
       </c>
       <c r="D3" s="1">
-        <v>6.8222303972525167e-08</v>
+        <v>6.8219835418417251e-08</v>
       </c>
       <c r="E3" s="1">
-        <v>6.6133715607650777e-06</v>
+        <v>6.6147627552976248e-06</v>
       </c>
       <c r="F3" s="1">
-        <v>8.6147112032745318e-06</v>
+        <v>8.6199839308308948e-06</v>
       </c>
       <c r="G3" s="1">
-        <v>4.0332390210531401e-06</v>
+        <v>4.0323756556498344e-06</v>
       </c>
       <c r="H3" s="1">
-        <v>3.7819850672219892e-06</v>
+        <v>3.7842797569758618e-06</v>
       </c>
       <c r="I3" s="1">
-        <v>-8.0842216270716474e-06</v>
+        <v>-8.0822305290457766e-06</v>
       </c>
       <c r="J3" s="1">
-        <v>-2.3370906597462319e-06</v>
+        <v>-2.3352322271232367e-06</v>
       </c>
       <c r="K3" s="1">
-        <v>3.7295822495040406e-06</v>
+        <v>3.7316596672387842e-06</v>
       </c>
       <c r="L3" s="1">
-        <v>-4.6457822898359784e-06</v>
+        <v>-4.6462561144584131e-06</v>
       </c>
       <c r="M3" s="1">
-        <v>-5.0587603803650411e-06</v>
+        <v>-5.0570431605787784e-06</v>
       </c>
       <c r="N3" s="1">
-        <v>-1.2704636922521972e-06</v>
+        <v>-1.2701290837922185e-06</v>
       </c>
       <c r="O3" s="1">
-        <v>5.3175098867573448e-06</v>
+        <v>5.3171043960905713e-06</v>
       </c>
       <c r="P3" s="1">
-        <v>1.0853919800766598e-06</v>
+        <v>1.0859342145632734e-06</v>
       </c>
       <c r="Q3" s="1">
-        <v>-5.8582608760348963e-07</v>
+        <v>-5.8569067118482079e-07</v>
       </c>
       <c r="R3" s="1">
-        <v>-1.4660322295479498e-05</v>
+        <v>-1.4660467405360627e-05</v>
       </c>
       <c r="S3" s="1">
-        <v>-2.1327916486797621e-07</v>
+        <v>-2.1299974450117101e-07</v>
       </c>
       <c r="T3" s="1">
-        <v>5.5853845800064462e-06</v>
+        <v>5.5841075914792298e-06</v>
       </c>
       <c r="U3" s="1">
-        <v>-1.0693020969368576e-05</v>
+        <v>-1.0691314006568004e-05</v>
       </c>
       <c r="V3" s="1">
-        <v>1.0809410040125773e-05</v>
+        <v>1.081223894793852e-05</v>
       </c>
       <c r="W3" s="1">
-        <v>-1.7025664952467065e-06</v>
+        <v>-1.7019799862173715e-06</v>
       </c>
       <c r="X3" s="1">
-        <v>-5.6627160457223163e-06</v>
+        <v>-5.6578646048215589e-06</v>
       </c>
       <c r="Y3" s="1">
-        <v>1.857897305991809e-06</v>
+        <v>1.8581638906659715e-06</v>
       </c>
       <c r="Z3" s="1">
-        <v>-1.3300806781679558e-06</v>
+        <v>-1.3304142294645212e-06</v>
       </c>
       <c r="AA3" s="1">
-        <v>-7.9663804186865604e-06</v>
+        <v>-7.9695031017307817e-06</v>
       </c>
       <c r="AB3" s="1">
-        <v>-5.0578810310689305e-07</v>
+        <v>-5.0616611283514846e-07</v>
       </c>
       <c r="AC3" s="1">
-        <v>9.7138945875580095e-08</v>
+        <v>9.4553104331150965e-08</v>
       </c>
       <c r="AD3" s="1">
-        <v>-1.5181966061238353e-06</v>
+        <v>-1.5177199524424971e-06</v>
       </c>
       <c r="AE3" s="1">
-        <v>-4.5037755042926681e-07</v>
+        <v>-4.5044237099095631e-07</v>
       </c>
       <c r="AF3" s="1">
-        <v>0.00011078841403356981</v>
+        <v>0.00011078767982932816</v>
       </c>
     </row>
     <row r="4">
@@ -4767,97 +4767,97 @@
         <v>63</v>
       </c>
       <c r="B4" s="1">
-        <v>0.074218997070014989</v>
+        <v>0.074189916801101721</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.00058292138627771611</v>
+        <v>-0.00058303130056590021</v>
       </c>
       <c r="D4" s="1">
-        <v>6.6133715607650777e-06</v>
+        <v>6.6147627552976248e-06</v>
       </c>
       <c r="E4" s="1">
-        <v>0.014209185643186257</v>
+        <v>0.014208847298534284</v>
       </c>
       <c r="F4" s="1">
-        <v>0.013317249129513681</v>
+        <v>0.013317490380419527</v>
       </c>
       <c r="G4" s="1">
-        <v>0.00045965506076561758</v>
+        <v>0.00045978989565839809</v>
       </c>
       <c r="H4" s="1">
-        <v>0.00073223082804729778</v>
+        <v>0.00073288266094649786</v>
       </c>
       <c r="I4" s="1">
-        <v>0.00040081820685343667</v>
+        <v>0.00040107019735460413</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.0011983389580258533</v>
+        <v>-0.0011986048442180746</v>
       </c>
       <c r="K4" s="1">
-        <v>0.0014368481778030779</v>
+        <v>0.0014371842442672473</v>
       </c>
       <c r="L4" s="1">
-        <v>0.0029540055739564787</v>
+        <v>0.0029535918093388878</v>
       </c>
       <c r="M4" s="1">
-        <v>0.00093374336850073937</v>
+        <v>0.00093332564282579654</v>
       </c>
       <c r="N4" s="1">
-        <v>0.0062011323897199454</v>
+        <v>0.0062004002121010199</v>
       </c>
       <c r="O4" s="1">
-        <v>0.00045447921865683898</v>
+        <v>0.00045424419029427461</v>
       </c>
       <c r="P4" s="1">
-        <v>-0.00080710408424799866</v>
+        <v>-0.00080730401759544421</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.002201258170083837</v>
+        <v>0.0022010532400660505</v>
       </c>
       <c r="R4" s="1">
-        <v>0.0014497736700591246</v>
+        <v>0.0014502686579398797</v>
       </c>
       <c r="S4" s="1">
-        <v>-0.00039407648331260352</v>
+        <v>-0.00039407209790613717</v>
       </c>
       <c r="T4" s="1">
-        <v>0.00046648736794849808</v>
+        <v>0.00046772431505343417</v>
       </c>
       <c r="U4" s="1">
-        <v>-0.0018356746561110741</v>
+        <v>-0.0018356337508171798</v>
       </c>
       <c r="V4" s="1">
-        <v>0.0022430250989063428</v>
+        <v>0.0022439948854310219</v>
       </c>
       <c r="W4" s="1">
-        <v>0.0012585498626353452</v>
+        <v>0.0012588481491565781</v>
       </c>
       <c r="X4" s="1">
-        <v>0.0026611890586119105</v>
+        <v>0.0026619990007030149</v>
       </c>
       <c r="Y4" s="1">
-        <v>0.00095689076066440327</v>
+        <v>0.00095696929383812083</v>
       </c>
       <c r="Z4" s="1">
-        <v>-0.00069160532020677925</v>
+        <v>-0.00069164950415299986</v>
       </c>
       <c r="AA4" s="1">
-        <v>-0.0037843467410189572</v>
+        <v>-0.0037858160615621339</v>
       </c>
       <c r="AB4" s="1">
-        <v>-0.0024005257371109471</v>
+        <v>-0.0024000386009211082</v>
       </c>
       <c r="AC4" s="1">
-        <v>-0.0042835709592460667</v>
+        <v>-0.004284314060355481</v>
       </c>
       <c r="AD4" s="1">
-        <v>-0.0041564706663223261</v>
+        <v>-0.0041562824117170744</v>
       </c>
       <c r="AE4" s="1">
-        <v>0.0001499549302403266</v>
+        <v>0.00015002425862876048</v>
       </c>
       <c r="AF4" s="1">
-        <v>-0.013751893641947632</v>
+        <v>-0.013751819662359565</v>
       </c>
     </row>
     <row r="5">
@@ -4865,97 +4865,97 @@
         <v>64</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.049264298795034016</v>
+        <v>-0.049315301924236964</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.00086673648140286278</v>
+        <v>-0.00086719470323466837</v>
       </c>
       <c r="D5" s="1">
-        <v>8.6147112032745318e-06</v>
+        <v>8.6199839308308948e-06</v>
       </c>
       <c r="E5" s="1">
-        <v>0.013317249129513681</v>
+        <v>0.013317490380419527</v>
       </c>
       <c r="F5" s="1">
-        <v>0.034329741456215354</v>
+        <v>0.034332090246890025</v>
       </c>
       <c r="G5" s="1">
-        <v>0.00081671658408049783</v>
+        <v>0.0008171861843239937</v>
       </c>
       <c r="H5" s="1">
-        <v>-0.0013845171469111682</v>
+        <v>-0.0013845239149541371</v>
       </c>
       <c r="I5" s="1">
-        <v>0.0010644537788237446</v>
+        <v>0.0010669448991634466</v>
       </c>
       <c r="J5" s="1">
-        <v>0.00091130459447580619</v>
+        <v>0.00091034655922443957</v>
       </c>
       <c r="K5" s="1">
-        <v>0.001857805412468219</v>
+        <v>0.0018565265606451326</v>
       </c>
       <c r="L5" s="1">
-        <v>0.0040158046482611839</v>
+        <v>0.0040134463166489089</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.012801959689575808</v>
+        <v>-0.012803908000962243</v>
       </c>
       <c r="N5" s="1">
-        <v>0.0068774280949140997</v>
+        <v>0.0068769080193742376</v>
       </c>
       <c r="O5" s="1">
-        <v>-0.00094113315930592113</v>
+        <v>-0.0009407251103027061</v>
       </c>
       <c r="P5" s="1">
-        <v>-0.002076916372796573</v>
+        <v>-0.0020756027363128954</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.002547900433469758</v>
+        <v>0.0025480356842784067</v>
       </c>
       <c r="R5" s="1">
-        <v>0.0058529334276241785</v>
+        <v>0.0058527150873944984</v>
       </c>
       <c r="S5" s="1">
-        <v>3.8626887678542155e-05</v>
+        <v>3.85804930322837e-05</v>
       </c>
       <c r="T5" s="1">
-        <v>0.0017572323529160658</v>
+        <v>0.0017587890816792235</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.001881839297210074</v>
+        <v>-0.0018827211130703105</v>
       </c>
       <c r="V5" s="1">
-        <v>0.0048378358178606962</v>
+        <v>0.0048381771861404433</v>
       </c>
       <c r="W5" s="1">
-        <v>-0.00030239303778861358</v>
+        <v>-0.00030111707552052175</v>
       </c>
       <c r="X5" s="1">
-        <v>0.0013642555221142424</v>
+        <v>0.00136326716625407</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.00021080186338524117</v>
+        <v>0.00021090704360667012</v>
       </c>
       <c r="Z5" s="1">
-        <v>-0.00043666377981133747</v>
+        <v>-0.00043658004124101987</v>
       </c>
       <c r="AA5" s="1">
-        <v>-0.0099642365473466069</v>
+        <v>-0.0099672215274162548</v>
       </c>
       <c r="AB5" s="1">
-        <v>-0.0026979202661507355</v>
+        <v>-0.0026980484016750597</v>
       </c>
       <c r="AC5" s="1">
-        <v>-0.0033150579265489779</v>
+        <v>-0.0033165668491301568</v>
       </c>
       <c r="AD5" s="1">
-        <v>-0.0059809280294555092</v>
+        <v>-0.0059813983501883928</v>
       </c>
       <c r="AE5" s="1">
-        <v>0.00042162719398394083</v>
+        <v>0.00042171803809626965</v>
       </c>
       <c r="AF5" s="1">
-        <v>-0.0051680041175217115</v>
+        <v>-0.0051608300928908911</v>
       </c>
     </row>
     <row r="6">
@@ -4963,97 +4963,97 @@
         <v>65</v>
       </c>
       <c r="B6" s="1">
-        <v>0.075893445602928364</v>
+        <v>0.075898426746660891</v>
       </c>
       <c r="C6" s="1">
-        <v>-0.00035776438291415047</v>
+        <v>-0.00035770895224943467</v>
       </c>
       <c r="D6" s="1">
-        <v>4.0332390210531401e-06</v>
+        <v>4.0323756556498344e-06</v>
       </c>
       <c r="E6" s="1">
-        <v>0.00045965506076561758</v>
+        <v>0.00045978989565839809</v>
       </c>
       <c r="F6" s="1">
-        <v>0.00081671658408049783</v>
+        <v>0.0008171861843239937</v>
       </c>
       <c r="G6" s="1">
-        <v>0.040088001007434794</v>
+        <v>0.040088111199852235</v>
       </c>
       <c r="H6" s="1">
-        <v>0.028246004436860969</v>
+        <v>0.028246329205680848</v>
       </c>
       <c r="I6" s="1">
-        <v>-0.0095142444908688315</v>
+        <v>-0.0095138943472219059</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.0088240406645987285</v>
+        <v>-0.0088242134603440138</v>
       </c>
       <c r="K6" s="1">
-        <v>-0.00951060281071512</v>
+        <v>-0.0095107237223370014</v>
       </c>
       <c r="L6" s="1">
-        <v>-0.0098024152415709456</v>
+        <v>-0.0098027859315454949</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.00072526573997591659</v>
+        <v>-0.00072480578807190832</v>
       </c>
       <c r="N6" s="1">
-        <v>-0.00017292209778534823</v>
+        <v>-0.00017287746366296403</v>
       </c>
       <c r="O6" s="1">
-        <v>0.028991479374938428</v>
+        <v>0.028991645571448385</v>
       </c>
       <c r="P6" s="1">
-        <v>0.029008600418814645</v>
+        <v>0.029008780715772647</v>
       </c>
       <c r="Q6" s="1">
-        <v>-0.00041472147044492591</v>
+        <v>-0.00041469455882463604</v>
       </c>
       <c r="R6" s="1">
-        <v>-0.00095618379498573283</v>
+        <v>-0.00095611973083117863</v>
       </c>
       <c r="S6" s="1">
-        <v>-9.3572320403238762e-05</v>
+        <v>-9.3553630891004061e-05</v>
       </c>
       <c r="T6" s="1">
-        <v>0.00041371130008838533</v>
+        <v>0.00041350238069366371</v>
       </c>
       <c r="U6" s="1">
-        <v>-0.0010154447702044045</v>
+        <v>-0.00101535118482729</v>
       </c>
       <c r="V6" s="1">
-        <v>-0.001438404571426008</v>
+        <v>-0.0014382342181563298</v>
       </c>
       <c r="W6" s="1">
-        <v>0.00035394075808484887</v>
+        <v>0.00035399717215720342</v>
       </c>
       <c r="X6" s="1">
-        <v>-0.00091466057047992488</v>
+        <v>-0.00091400598066742472</v>
       </c>
       <c r="Y6" s="1">
-        <v>-6.1965184269964502e-05</v>
+        <v>-6.1947748022474387e-05</v>
       </c>
       <c r="Z6" s="1">
-        <v>2.46536907510214e-05</v>
+        <v>2.462999742743879e-05</v>
       </c>
       <c r="AA6" s="1">
-        <v>-0.00049925845134164357</v>
+        <v>-0.0004991765079753567</v>
       </c>
       <c r="AB6" s="1">
-        <v>-0.0013463390914037823</v>
+        <v>-0.0013464007137241329</v>
       </c>
       <c r="AC6" s="1">
-        <v>-0.00069258469308254578</v>
+        <v>-0.00069284822911654109</v>
       </c>
       <c r="AD6" s="1">
-        <v>0.00023912383880336091</v>
+        <v>0.00023920938060293349</v>
       </c>
       <c r="AE6" s="1">
-        <v>8.7447931551082602e-05</v>
+        <v>8.7448195901297741e-05</v>
       </c>
       <c r="AF6" s="1">
-        <v>-0.012767715221919274</v>
+        <v>-0.012768720242568088</v>
       </c>
     </row>
     <row r="7">
@@ -5061,97 +5061,97 @@
         <v>66</v>
       </c>
       <c r="B7" s="1">
-        <v>0.076499577724728915</v>
+        <v>0.076476947593305936</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.00028850856852084914</v>
+        <v>-0.00028869149003215959</v>
       </c>
       <c r="D7" s="1">
-        <v>3.7819850672219892e-06</v>
+        <v>3.7842797569758618e-06</v>
       </c>
       <c r="E7" s="1">
-        <v>0.00073223082804729778</v>
+        <v>0.00073288266094649786</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.0013845171469111682</v>
+        <v>-0.0013845239149541371</v>
       </c>
       <c r="G7" s="1">
-        <v>0.028246004436860969</v>
+        <v>0.028246329205680848</v>
       </c>
       <c r="H7" s="1">
-        <v>0.033216232654038474</v>
+        <v>0.033216548729735298</v>
       </c>
       <c r="I7" s="1">
-        <v>-0.0087376779628357583</v>
+        <v>-0.0087380057449871033</v>
       </c>
       <c r="J7" s="1">
-        <v>-0.0057609323352084997</v>
+        <v>-0.0057612426537833397</v>
       </c>
       <c r="K7" s="1">
-        <v>-0.0033716894410805234</v>
+        <v>-0.0033726410833120682</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.0037534773944519206</v>
+        <v>-0.0037545514858044193</v>
       </c>
       <c r="M7" s="1">
-        <v>0.0019702710076034968</v>
+        <v>0.0019697965121689698</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.0014653182185220548</v>
+        <v>-0.0014651463169171527</v>
       </c>
       <c r="O7" s="1">
-        <v>0.027940811066074184</v>
+        <v>0.027940991257504336</v>
       </c>
       <c r="P7" s="1">
-        <v>0.02771619134917222</v>
+        <v>0.027716815090456259</v>
       </c>
       <c r="Q7" s="1">
-        <v>-0.00032054734588526229</v>
+        <v>-0.00032026894606322631</v>
       </c>
       <c r="R7" s="1">
-        <v>0.00075761882746456372</v>
+        <v>0.00075812500757416884</v>
       </c>
       <c r="S7" s="1">
-        <v>7.4871670742658256e-05</v>
+        <v>7.4816765532280047e-05</v>
       </c>
       <c r="T7" s="1">
-        <v>0.00073091059248681089</v>
+        <v>0.00073196697999018678</v>
       </c>
       <c r="U7" s="1">
-        <v>-0.00029076418028923384</v>
+        <v>-0.00029256339077822491</v>
       </c>
       <c r="V7" s="1">
-        <v>0.0016331949963545589</v>
+        <v>0.0016327562441045482</v>
       </c>
       <c r="W7" s="1">
-        <v>-0.0014134107965974065</v>
+        <v>-0.0014134547717662219</v>
       </c>
       <c r="X7" s="1">
-        <v>0.00067963993729942829</v>
+        <v>0.00067873171958456741</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.00025128143599299161</v>
+        <v>0.00025134042650310981</v>
       </c>
       <c r="Z7" s="1">
-        <v>-0.00020296993036536103</v>
+        <v>-0.00020294446641170834</v>
       </c>
       <c r="AA7" s="1">
-        <v>-0.0017457780081271031</v>
+        <v>-0.0017466794361852885</v>
       </c>
       <c r="AB7" s="1">
-        <v>-0.00058496898057508115</v>
+        <v>-0.00058523187646863234</v>
       </c>
       <c r="AC7" s="1">
-        <v>-0.0025706151916638637</v>
+        <v>-0.0025716628695043459</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.00034027765895977037</v>
+        <v>0.00033945851191353495</v>
       </c>
       <c r="AE7" s="1">
-        <v>-9.5847773255686443e-05</v>
+        <v>-9.5837210419994726e-05</v>
       </c>
       <c r="AF7" s="1">
-        <v>-0.018095772569022839</v>
+        <v>-0.018093167866381488</v>
       </c>
     </row>
     <row r="8">
@@ -5159,97 +5159,97 @@
         <v>67</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.17468564780953338</v>
+        <v>-0.174749711835616</v>
       </c>
       <c r="C8" s="1">
-        <v>0.00063526755217745514</v>
+        <v>0.00063515809289935144</v>
       </c>
       <c r="D8" s="1">
-        <v>-8.0842216270716474e-06</v>
+        <v>-8.0822305290457766e-06</v>
       </c>
       <c r="E8" s="1">
-        <v>0.00040081820685343667</v>
+        <v>0.00040107019735460413</v>
       </c>
       <c r="F8" s="1">
-        <v>0.0010644537788237446</v>
+        <v>0.0010669448991634466</v>
       </c>
       <c r="G8" s="1">
-        <v>-0.0095142444908688315</v>
+        <v>-0.0095138943472219059</v>
       </c>
       <c r="H8" s="1">
-        <v>-0.0087376779628357583</v>
+        <v>-0.0087380057449871033</v>
       </c>
       <c r="I8" s="1">
-        <v>0.084246681411470584</v>
+        <v>0.084250490712054774</v>
       </c>
       <c r="J8" s="1">
-        <v>0.066104691007100091</v>
+        <v>0.066105041165806094</v>
       </c>
       <c r="K8" s="1">
-        <v>0.06699126499169672</v>
+        <v>0.06699166437249901</v>
       </c>
       <c r="L8" s="1">
-        <v>0.066468649854556597</v>
+        <v>0.066469949327708736</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.0060626108356745811</v>
+        <v>-0.0060671949424608296</v>
       </c>
       <c r="N8" s="1">
-        <v>-0.00093529219746711634</v>
+        <v>-0.00093523148862247052</v>
       </c>
       <c r="O8" s="1">
-        <v>-0.0076938033479172913</v>
+        <v>-0.007695289587637405</v>
       </c>
       <c r="P8" s="1">
-        <v>-0.0078020472022430343</v>
+        <v>-0.0078035059839278165</v>
       </c>
       <c r="Q8" s="1">
-        <v>-0.00069880426969678305</v>
+        <v>-0.00069868610877775114</v>
       </c>
       <c r="R8" s="1">
-        <v>-0.001035244874353157</v>
+        <v>-0.0010332106510416786</v>
       </c>
       <c r="S8" s="1">
-        <v>-0.00019090688058965612</v>
+        <v>-0.00019094939071115369</v>
       </c>
       <c r="T8" s="1">
-        <v>-0.00030601820410952954</v>
+        <v>-0.00030321851669773761</v>
       </c>
       <c r="U8" s="1">
-        <v>0.00062651870494007111</v>
+        <v>0.0006236628235322117</v>
       </c>
       <c r="V8" s="1">
-        <v>0.00051291445271776925</v>
+        <v>0.00051241405122458283</v>
       </c>
       <c r="W8" s="1">
-        <v>-0.0028792630846383033</v>
+        <v>-0.0028818214296326555</v>
       </c>
       <c r="X8" s="1">
-        <v>0.009362859467561685</v>
+        <v>0.0093620616567857071</v>
       </c>
       <c r="Y8" s="1">
-        <v>-0.00026383027319300256</v>
+        <v>-0.00026398426971852886</v>
       </c>
       <c r="Z8" s="1">
-        <v>9.1513919158038842e-05</v>
+        <v>9.1555477018827758e-05</v>
       </c>
       <c r="AA8" s="1">
-        <v>0.00092354159150524404</v>
+        <v>0.00092080152027874604</v>
       </c>
       <c r="AB8" s="1">
-        <v>-0.00026606775547067391</v>
+        <v>-0.00026591086669353059</v>
       </c>
       <c r="AC8" s="1">
-        <v>0.00048391500991182279</v>
+        <v>0.00048299115424998984</v>
       </c>
       <c r="AD8" s="1">
-        <v>-0.00011580546055463443</v>
+        <v>-0.00011774888398092404</v>
       </c>
       <c r="AE8" s="1">
-        <v>7.0899346365670303e-05</v>
+        <v>7.0915562794835428e-05</v>
       </c>
       <c r="AF8" s="1">
-        <v>-0.068998689710599803</v>
+        <v>-0.068996966864805831</v>
       </c>
     </row>
     <row r="9">
@@ -5257,97 +5257,97 @@
         <v>68</v>
       </c>
       <c r="B9" s="1">
-        <v>-0.11257776812481735</v>
+        <v>-0.11258540986128915</v>
       </c>
       <c r="C9" s="1">
-        <v>0.00010883418281920675</v>
+        <v>0.00010867570444683845</v>
       </c>
       <c r="D9" s="1">
-        <v>-2.3370906597462319e-06</v>
+        <v>-2.3352322271232367e-06</v>
       </c>
       <c r="E9" s="1">
-        <v>-0.0011983389580258533</v>
+        <v>-0.0011986048442180746</v>
       </c>
       <c r="F9" s="1">
-        <v>0.00091130459447580619</v>
+        <v>0.00091034655922443957</v>
       </c>
       <c r="G9" s="1">
-        <v>-0.0088240406645987285</v>
+        <v>-0.0088242134603440138</v>
       </c>
       <c r="H9" s="1">
-        <v>-0.0057609323352084997</v>
+        <v>-0.0057612426537833397</v>
       </c>
       <c r="I9" s="1">
-        <v>0.066104691007100091</v>
+        <v>0.066105041165806094</v>
       </c>
       <c r="J9" s="1">
-        <v>0.071737069276111287</v>
+        <v>0.07173708738587492</v>
       </c>
       <c r="K9" s="1">
-        <v>0.065988232178993952</v>
+        <v>0.065987989175095962</v>
       </c>
       <c r="L9" s="1">
-        <v>0.065749188359066651</v>
+        <v>0.065748778359601912</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.001342327811732047</v>
+        <v>-0.001342099346608755</v>
       </c>
       <c r="N9" s="1">
-        <v>-0.0016492913151383154</v>
+        <v>-0.0016497060451723389</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.0055971981905800217</v>
+        <v>-0.0055973810199870105</v>
       </c>
       <c r="P9" s="1">
-        <v>-0.0067156289497538324</v>
+        <v>-0.0067161223412074977</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.00089833280106171517</v>
+        <v>-0.00089844571028317374</v>
       </c>
       <c r="R9" s="1">
-        <v>-0.0037508098559934748</v>
+        <v>-0.0037505692006763527</v>
       </c>
       <c r="S9" s="1">
-        <v>0.0001499357588552637</v>
+        <v>0.00014994622172047507</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.00021440021372751139</v>
+        <v>-0.00021382490631467049</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.00062060930067314724</v>
+        <v>-0.00062110481985735988</v>
       </c>
       <c r="V9" s="1">
-        <v>-0.00063510936392942308</v>
+        <v>-0.00063524505066432646</v>
       </c>
       <c r="W9" s="1">
-        <v>-0.0027563885705779861</v>
+        <v>-0.002756199586255538</v>
       </c>
       <c r="X9" s="1">
-        <v>0.0062420625365775251</v>
+        <v>0.0062413356155310712</v>
       </c>
       <c r="Y9" s="1">
-        <v>0.00025098317994858878</v>
+        <v>0.00025095827349803923</v>
       </c>
       <c r="Z9" s="1">
-        <v>-0.00018233766985622591</v>
+        <v>-0.00018227229737820998</v>
       </c>
       <c r="AA9" s="1">
-        <v>0.0029016825084582469</v>
+        <v>0.0029018503138717559</v>
       </c>
       <c r="AB9" s="1">
-        <v>0.0011530807454680561</v>
+        <v>0.0011535542130373944</v>
       </c>
       <c r="AC9" s="1">
-        <v>0.0014685168136921167</v>
+        <v>0.0014690896350707527</v>
       </c>
       <c r="AD9" s="1">
-        <v>0.0011811697392704549</v>
+        <v>0.0011814705578534722</v>
       </c>
       <c r="AE9" s="1">
-        <v>0.00014199123407152703</v>
+        <v>0.0001419957463768386</v>
       </c>
       <c r="AF9" s="1">
-        <v>-0.061060832753046135</v>
+        <v>-0.061057112231170163</v>
       </c>
     </row>
     <row r="10">
@@ -5355,97 +5355,97 @@
         <v>69</v>
       </c>
       <c r="B10" s="1">
-        <v>0.064993300251369929</v>
+        <v>0.064990782119800333</v>
       </c>
       <c r="C10" s="1">
-        <v>-0.00029724231765264602</v>
+        <v>-0.00029738610970855405</v>
       </c>
       <c r="D10" s="1">
-        <v>3.7295822495040406e-06</v>
+        <v>3.7316596672387842e-06</v>
       </c>
       <c r="E10" s="1">
-        <v>0.0014368481778030779</v>
+        <v>0.0014371842442672473</v>
       </c>
       <c r="F10" s="1">
-        <v>0.001857805412468219</v>
+        <v>0.0018565265606451326</v>
       </c>
       <c r="G10" s="1">
-        <v>-0.00951060281071512</v>
+        <v>-0.0095107237223370014</v>
       </c>
       <c r="H10" s="1">
-        <v>-0.0033716894410805234</v>
+        <v>-0.0033726410833120682</v>
       </c>
       <c r="I10" s="1">
-        <v>0.06699126499169672</v>
+        <v>0.06699166437249901</v>
       </c>
       <c r="J10" s="1">
-        <v>0.065988232178993952</v>
+        <v>0.065987989175095962</v>
       </c>
       <c r="K10" s="1">
-        <v>0.074077393908303049</v>
+        <v>0.074076444805731861</v>
       </c>
       <c r="L10" s="1">
-        <v>0.071718238627623651</v>
+        <v>0.071717255023871676</v>
       </c>
       <c r="M10" s="1">
-        <v>0.001847516177188091</v>
+        <v>0.0018478093900806403</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.00023681263454762569</v>
+        <v>-0.00023666505836313079</v>
       </c>
       <c r="O10" s="1">
-        <v>-0.0053152603584907393</v>
+        <v>-0.0053152974030070688</v>
       </c>
       <c r="P10" s="1">
-        <v>-0.005203921921903637</v>
+        <v>-0.0052033053691981912</v>
       </c>
       <c r="Q10" s="1">
-        <v>-0.0006235820914812229</v>
+        <v>-0.00062341590064904709</v>
       </c>
       <c r="R10" s="1">
-        <v>9.7336724158004345e-05</v>
+        <v>9.7371923864515014e-05</v>
       </c>
       <c r="S10" s="1">
-        <v>-0.00010207681881281398</v>
+        <v>-0.00010214902129486621</v>
       </c>
       <c r="T10" s="1">
-        <v>-5.5945222326131416e-05</v>
+        <v>-5.5474497427404623e-05</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.00031670091867075367</v>
+        <v>-0.00031743518974487739</v>
       </c>
       <c r="V10" s="1">
-        <v>0.0021355654362460175</v>
+        <v>0.0021347147795553606</v>
       </c>
       <c r="W10" s="1">
-        <v>-0.0018053321695528993</v>
+        <v>-0.0018050294737179187</v>
       </c>
       <c r="X10" s="1">
-        <v>0.0064759020855304911</v>
+        <v>0.0064740959740147569</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.00021001139853322158</v>
+        <v>0.0002100312695931042</v>
       </c>
       <c r="Z10" s="1">
-        <v>-0.00019993622368279446</v>
+        <v>-0.00019985758052004296</v>
       </c>
       <c r="AA10" s="1">
-        <v>0.004258716805124154</v>
+        <v>0.0042580412129635294</v>
       </c>
       <c r="AB10" s="1">
-        <v>-0.00010199714511317792</v>
+        <v>-0.00010255171588161721</v>
       </c>
       <c r="AC10" s="1">
-        <v>0.0013096736271885484</v>
+        <v>0.0013091168460373087</v>
       </c>
       <c r="AD10" s="1">
-        <v>0.00058387692770418137</v>
+        <v>0.00058323379953770758</v>
       </c>
       <c r="AE10" s="1">
-        <v>-0.00023104565420874412</v>
+        <v>-0.00023106772669192932</v>
       </c>
       <c r="AF10" s="1">
-        <v>-0.059845235413058862</v>
+        <v>-0.059842135022758924</v>
       </c>
     </row>
     <row r="11">
@@ -5453,97 +5453,97 @@
         <v>70</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.079310045801739157</v>
+        <v>-0.079276049104757468</v>
       </c>
       <c r="C11" s="1">
-        <v>0.00058630261660466004</v>
+        <v>0.00058635472405529996</v>
       </c>
       <c r="D11" s="1">
-        <v>-4.6457822898359784e-06</v>
+        <v>-4.6462561144584131e-06</v>
       </c>
       <c r="E11" s="1">
-        <v>0.0029540055739564787</v>
+        <v>0.0029535918093388878</v>
       </c>
       <c r="F11" s="1">
-        <v>0.0040158046482611839</v>
+        <v>0.0040134463166489089</v>
       </c>
       <c r="G11" s="1">
-        <v>-0.0098024152415709456</v>
+        <v>-0.0098027859315454949</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.0037534773944519206</v>
+        <v>-0.0037545514858044193</v>
       </c>
       <c r="I11" s="1">
-        <v>0.066468649854556597</v>
+        <v>0.066469949327708736</v>
       </c>
       <c r="J11" s="1">
-        <v>0.065749188359066651</v>
+        <v>0.065748778359601912</v>
       </c>
       <c r="K11" s="1">
-        <v>0.071718238627623651</v>
+        <v>0.071717255023871676</v>
       </c>
       <c r="L11" s="1">
-        <v>0.087480217664745452</v>
+        <v>0.087479231093459023</v>
       </c>
       <c r="M11" s="1">
-        <v>-4.8026468667194955e-05</v>
+        <v>-4.6617351518646322e-05</v>
       </c>
       <c r="N11" s="1">
-        <v>0.0014043269112202633</v>
+        <v>0.0014043543933405511</v>
       </c>
       <c r="O11" s="1">
-        <v>-0.0060790899041727742</v>
+        <v>-0.006078994257483511</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.0072444129550462977</v>
+        <v>-0.0072439958220565648</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.00081739997007414938</v>
+        <v>0.00081738304951394988</v>
       </c>
       <c r="R11" s="1">
-        <v>-0.0026418490959096118</v>
+        <v>-0.002643137819772521</v>
       </c>
       <c r="S11" s="1">
-        <v>-0.00010055428478924523</v>
+        <v>-0.00010055153065839824</v>
       </c>
       <c r="T11" s="1">
-        <v>-0.0012315477548496198</v>
+        <v>-0.001233055444856055</v>
       </c>
       <c r="U11" s="1">
-        <v>0.0012787820064078109</v>
+        <v>0.0012805134025535708</v>
       </c>
       <c r="V11" s="1">
-        <v>-0.00021548390084895341</v>
+        <v>-0.00021629334145598089</v>
       </c>
       <c r="W11" s="1">
-        <v>-0.0014111857038698952</v>
+        <v>-0.0014106100267221103</v>
       </c>
       <c r="X11" s="1">
-        <v>0.0049644120035823164</v>
+        <v>0.0049631991762064537</v>
       </c>
       <c r="Y11" s="1">
-        <v>-0.00032823607663604731</v>
+        <v>-0.00032824478845880876</v>
       </c>
       <c r="Z11" s="1">
-        <v>0.00014284198111331027</v>
+        <v>0.00014290619083299301</v>
       </c>
       <c r="AA11" s="1">
-        <v>-0.0001403026252940788</v>
+        <v>-0.00013949485416626939</v>
       </c>
       <c r="AB11" s="1">
-        <v>-0.0040235784459010937</v>
+        <v>-0.0040239800228877853</v>
       </c>
       <c r="AC11" s="1">
-        <v>-0.00089895557460789588</v>
+        <v>-0.0008979110796655948</v>
       </c>
       <c r="AD11" s="1">
-        <v>-0.0023052511722490166</v>
+        <v>-0.0023049512441189867</v>
       </c>
       <c r="AE11" s="1">
-        <v>-0.00028216260394437772</v>
+        <v>-0.0002822379105273438</v>
       </c>
       <c r="AF11" s="1">
-        <v>-0.078181719933197336</v>
+        <v>-0.078179773455942736</v>
       </c>
     </row>
     <row r="12">
@@ -5551,97 +5551,97 @@
         <v>71</v>
       </c>
       <c r="B12" s="1">
-        <v>0.41795542997590091</v>
+        <v>0.41791542212384564</v>
       </c>
       <c r="C12" s="1">
-        <v>0.00040615024740175455</v>
+        <v>0.00040613142250768564</v>
       </c>
       <c r="D12" s="1">
-        <v>-5.0587603803650411e-06</v>
+        <v>-5.0570431605787784e-06</v>
       </c>
       <c r="E12" s="1">
-        <v>0.00093374336850073937</v>
+        <v>0.00093332564282579654</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.012801959689575808</v>
+        <v>-0.012803908000962243</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00072526573997591659</v>
+        <v>-0.00072480578807190832</v>
       </c>
       <c r="H12" s="1">
-        <v>0.0019702710076034968</v>
+        <v>0.0019697965121689698</v>
       </c>
       <c r="I12" s="1">
-        <v>-0.0060626108356745811</v>
+        <v>-0.0060671949424608296</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.001342327811732047</v>
+        <v>-0.001342099346608755</v>
       </c>
       <c r="K12" s="1">
-        <v>0.001847516177188091</v>
+        <v>0.0018478093900806403</v>
       </c>
       <c r="L12" s="1">
-        <v>-4.8026468667194955e-05</v>
+        <v>-4.6617351518646322e-05</v>
       </c>
       <c r="M12" s="1">
-        <v>0.026444674731224208</v>
+        <v>0.026445403241316022</v>
       </c>
       <c r="N12" s="1">
-        <v>0.00060386780153831587</v>
+        <v>0.00060336033432268699</v>
       </c>
       <c r="O12" s="1">
-        <v>0.0044014038173023603</v>
+        <v>0.0044011138302158768</v>
       </c>
       <c r="P12" s="1">
-        <v>0.0023687816870236779</v>
+        <v>0.0023682680893353531</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.00086056052931677597</v>
+        <v>0.00086051346721631125</v>
       </c>
       <c r="R12" s="1">
-        <v>-0.0014696905863382311</v>
+        <v>-0.0014683424281879856</v>
       </c>
       <c r="S12" s="1">
-        <v>-0.00046131559670120072</v>
+        <v>-0.00046152364145616524</v>
       </c>
       <c r="T12" s="1">
-        <v>-0.0026171168716646433</v>
+        <v>-0.0026147582696338188</v>
       </c>
       <c r="U12" s="1">
-        <v>0.00046626078473472644</v>
+        <v>0.00046473028461104741</v>
       </c>
       <c r="V12" s="1">
-        <v>-0.0065386960732516271</v>
+        <v>-0.0065400655396834675</v>
       </c>
       <c r="W12" s="1">
-        <v>-0.0032993410215361673</v>
+        <v>-0.0033013850929321537</v>
       </c>
       <c r="X12" s="1">
-        <v>-0.0043032396905059262</v>
+        <v>-0.0043061327577890423</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.00024971946276748039</v>
+        <v>0.000249657255360821</v>
       </c>
       <c r="Z12" s="1">
-        <v>-7.5104905997438711e-05</v>
+        <v>-7.5050942173584872e-05</v>
       </c>
       <c r="AA12" s="1">
-        <v>0.013496910717562132</v>
+        <v>0.013496231763663109</v>
       </c>
       <c r="AB12" s="1">
-        <v>0.00011610516205111756</v>
+        <v>0.00011616711754149685</v>
       </c>
       <c r="AC12" s="1">
-        <v>0.002878171544353738</v>
+        <v>0.0028778645375370196</v>
       </c>
       <c r="AD12" s="1">
-        <v>0.0013832700431817054</v>
+        <v>0.0013818389966908638</v>
       </c>
       <c r="AE12" s="1">
-        <v>1.1822318785110767e-05</v>
+        <v>1.1883689623908834e-05</v>
       </c>
       <c r="AF12" s="1">
-        <v>-0.015282588862388254</v>
+        <v>-0.015285433752252293</v>
       </c>
     </row>
     <row r="13">
@@ -5649,97 +5649,97 @@
         <v>72</v>
       </c>
       <c r="B13" s="1">
-        <v>0.25953095995713532</v>
+        <v>0.25951885248574708</v>
       </c>
       <c r="C13" s="1">
-        <v>5.1871304811644016e-05</v>
+        <v>5.1858262607997092e-05</v>
       </c>
       <c r="D13" s="1">
-        <v>-1.2704636922521972e-06</v>
+        <v>-1.2701290837922185e-06</v>
       </c>
       <c r="E13" s="1">
-        <v>0.0062011323897199454</v>
+        <v>0.0062004002121010199</v>
       </c>
       <c r="F13" s="1">
-        <v>0.0068774280949140997</v>
+        <v>0.0068769080193742376</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.00017292209778534823</v>
+        <v>-0.00017287746366296403</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.0014653182185220548</v>
+        <v>-0.0014651463169171527</v>
       </c>
       <c r="I13" s="1">
-        <v>-0.00093529219746711634</v>
+        <v>-0.00093523148862247052</v>
       </c>
       <c r="J13" s="1">
-        <v>-0.0016492913151383154</v>
+        <v>-0.0016497060451723389</v>
       </c>
       <c r="K13" s="1">
-        <v>-0.00023681263454762569</v>
+        <v>-0.00023666505836313079</v>
       </c>
       <c r="L13" s="1">
-        <v>0.0014043269112202633</v>
+        <v>0.0014043543933405511</v>
       </c>
       <c r="M13" s="1">
-        <v>0.00060386780153831587</v>
+        <v>0.00060336033432268699</v>
       </c>
       <c r="N13" s="1">
-        <v>0.011150285740338486</v>
+        <v>0.011149574959028678</v>
       </c>
       <c r="O13" s="1">
-        <v>-0.0014479926592455335</v>
+        <v>-0.0014483470824668849</v>
       </c>
       <c r="P13" s="1">
-        <v>7.9653528872045826e-05</v>
+        <v>7.9390528359653267e-05</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.0015471834595138243</v>
+        <v>0.0015468488688475711</v>
       </c>
       <c r="R13" s="1">
-        <v>-0.00031841218940888388</v>
+        <v>-0.00031836058825438179</v>
       </c>
       <c r="S13" s="1">
-        <v>-0.00030834743108780211</v>
+        <v>-0.00030829894631073987</v>
       </c>
       <c r="T13" s="1">
-        <v>-1.7945846838063328e-05</v>
+        <v>-1.7439017630032803e-05</v>
       </c>
       <c r="U13" s="1">
-        <v>-0.001745777983112146</v>
+        <v>-0.0017447489930474376</v>
       </c>
       <c r="V13" s="1">
-        <v>-0.0013470458641735793</v>
+        <v>-0.0013464018344086439</v>
       </c>
       <c r="W13" s="1">
-        <v>0.0032967613674810907</v>
+        <v>0.0032970833137214452</v>
       </c>
       <c r="X13" s="1">
-        <v>0.0025665351990561119</v>
+        <v>0.0025666826976767547</v>
       </c>
       <c r="Y13" s="1">
-        <v>-0.00036875167953741891</v>
+        <v>-0.00036883330035738951</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.0001410707182361352</v>
+        <v>0.00014112318618050666</v>
       </c>
       <c r="AA13" s="1">
-        <v>-0.0035576678246611653</v>
+        <v>-0.0035585517090466288</v>
       </c>
       <c r="AB13" s="1">
-        <v>-0.00185634361414935</v>
+        <v>-0.0018557035753981009</v>
       </c>
       <c r="AC13" s="1">
-        <v>-0.0031644797077319776</v>
+        <v>-0.0031638353169584198</v>
       </c>
       <c r="AD13" s="1">
-        <v>-0.0010489907700071876</v>
+        <v>-0.0010483077908032066</v>
       </c>
       <c r="AE13" s="1">
-        <v>8.935015113416476e-06</v>
+        <v>8.9837293119081627e-06</v>
       </c>
       <c r="AF13" s="1">
-        <v>-0.008620041528395652</v>
+        <v>-0.0086199135976611808</v>
       </c>
     </row>
     <row r="14">
@@ -5747,97 +5747,97 @@
         <v>73</v>
       </c>
       <c r="B14" s="1">
-        <v>0.091040129196686748</v>
+        <v>0.091029737590281573</v>
       </c>
       <c r="C14" s="1">
-        <v>-0.00039732740847369871</v>
+        <v>-0.0003972812937142918</v>
       </c>
       <c r="D14" s="1">
-        <v>5.3175098867573448e-06</v>
+        <v>5.3171043960905713e-06</v>
       </c>
       <c r="E14" s="1">
-        <v>0.00045447921865683898</v>
+        <v>0.00045424419029427461</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.00094113315930592113</v>
+        <v>-0.0009407251103027061</v>
       </c>
       <c r="G14" s="1">
-        <v>0.028991479374938428</v>
+        <v>0.028991645571448385</v>
       </c>
       <c r="H14" s="1">
-        <v>0.027940811066074184</v>
+        <v>0.027940991257504336</v>
       </c>
       <c r="I14" s="1">
-        <v>-0.0076938033479172913</v>
+        <v>-0.007695289587637405</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.0055971981905800217</v>
+        <v>-0.0055973810199870105</v>
       </c>
       <c r="K14" s="1">
-        <v>-0.0053152603584907393</v>
+        <v>-0.0053152974030070688</v>
       </c>
       <c r="L14" s="1">
-        <v>-0.0060790899041727742</v>
+        <v>-0.006078994257483511</v>
       </c>
       <c r="M14" s="1">
-        <v>0.0044014038173023603</v>
+        <v>0.0044011138302158768</v>
       </c>
       <c r="N14" s="1">
-        <v>-0.0014479926592455335</v>
+        <v>-0.0014483470824668849</v>
       </c>
       <c r="O14" s="1">
-        <v>0.035876736122117669</v>
+        <v>0.035876558416541415</v>
       </c>
       <c r="P14" s="1">
-        <v>0.031738935270278323</v>
+        <v>0.031738411486305657</v>
       </c>
       <c r="Q14" s="1">
-        <v>-0.00042341926792400716</v>
+        <v>-0.00042359286485224926</v>
       </c>
       <c r="R14" s="1">
-        <v>-0.00017218039280908135</v>
+        <v>-0.00017163687074456604</v>
       </c>
       <c r="S14" s="1">
-        <v>-0.00017618855438986808</v>
+        <v>-0.0001761752477657131</v>
       </c>
       <c r="T14" s="1">
-        <v>-0.0013309852321201077</v>
+        <v>-0.0013305943167576696</v>
       </c>
       <c r="U14" s="1">
-        <v>0.00099322895966694885</v>
+        <v>0.00099330312486047012</v>
       </c>
       <c r="V14" s="1">
-        <v>0.0022830490981062893</v>
+        <v>0.0022830289127716286</v>
       </c>
       <c r="W14" s="1">
-        <v>-0.00066580861874460107</v>
+        <v>-0.00066640640272944834</v>
       </c>
       <c r="X14" s="1">
-        <v>-0.0015802490537481506</v>
+        <v>-0.0015803212711456294</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.00019354574632545699</v>
+        <v>0.00019349501244015233</v>
       </c>
       <c r="Z14" s="1">
-        <v>4.2988289961127038e-05</v>
+        <v>4.298949763617381e-05</v>
       </c>
       <c r="AA14" s="1">
-        <v>0.0028278459236341161</v>
+        <v>0.0028275240864089439</v>
       </c>
       <c r="AB14" s="1">
-        <v>-0.0014742708959440236</v>
+        <v>-0.0014740961349801393</v>
       </c>
       <c r="AC14" s="1">
-        <v>-0.0019250434399147448</v>
+        <v>-0.0019250231983625604</v>
       </c>
       <c r="AD14" s="1">
-        <v>-8.8941269648956309e-05</v>
+        <v>-8.9071949532386341e-05</v>
       </c>
       <c r="AE14" s="1">
-        <v>-0.00010329328279637878</v>
+        <v>-0.00010328002727435053</v>
       </c>
       <c r="AF14" s="1">
-        <v>-0.017483004318354312</v>
+        <v>-0.01748337991926277</v>
       </c>
     </row>
     <row r="15">
@@ -5845,97 +5845,97 @@
         <v>74</v>
       </c>
       <c r="B15" s="1">
-        <v>0.40718442961297024</v>
+        <v>0.40716241121210089</v>
       </c>
       <c r="C15" s="1">
-        <v>9.2906843662638253e-05</v>
+        <v>9.2841113122441726e-05</v>
       </c>
       <c r="D15" s="1">
-        <v>1.0853919800766598e-06</v>
+        <v>1.0859342145632734e-06</v>
       </c>
       <c r="E15" s="1">
-        <v>-0.00080710408424799866</v>
+        <v>-0.00080730401759544421</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.002076916372796573</v>
+        <v>-0.0020756027363128954</v>
       </c>
       <c r="G15" s="1">
-        <v>0.029008600418814645</v>
+        <v>0.029008780715772647</v>
       </c>
       <c r="H15" s="1">
-        <v>0.02771619134917222</v>
+        <v>0.027716815090456259</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.0078020472022430343</v>
+        <v>-0.0078035059839278165</v>
       </c>
       <c r="J15" s="1">
-        <v>-0.0067156289497538324</v>
+        <v>-0.0067161223412074977</v>
       </c>
       <c r="K15" s="1">
-        <v>-0.005203921921903637</v>
+        <v>-0.0052033053691981912</v>
       </c>
       <c r="L15" s="1">
-        <v>-0.0072444129550462977</v>
+        <v>-0.0072439958220565648</v>
       </c>
       <c r="M15" s="1">
-        <v>0.0023687816870236779</v>
+        <v>0.0023682680893353531</v>
       </c>
       <c r="N15" s="1">
-        <v>7.9653528872045826e-05</v>
+        <v>7.9390528359653267e-05</v>
       </c>
       <c r="O15" s="1">
-        <v>0.031738935270278323</v>
+        <v>0.031738411486305657</v>
       </c>
       <c r="P15" s="1">
-        <v>0.040389692234006569</v>
+        <v>0.040388884713405515</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.00036771879588927761</v>
+        <v>0.00036757399134817667</v>
       </c>
       <c r="R15" s="1">
-        <v>0.0010880310657556715</v>
+        <v>0.0010884828635845945</v>
       </c>
       <c r="S15" s="1">
-        <v>-0.0003761245760155324</v>
+        <v>-0.0003760728113235759</v>
       </c>
       <c r="T15" s="1">
-        <v>-0.00019289588968131668</v>
+        <v>-0.00019218164150009917</v>
       </c>
       <c r="U15" s="1">
-        <v>-0.00012625673643303081</v>
+        <v>-0.00012684599627271753</v>
       </c>
       <c r="V15" s="1">
-        <v>0.0025194366289275072</v>
+        <v>0.0025198959150417102</v>
       </c>
       <c r="W15" s="1">
-        <v>-0.0020341296748685352</v>
+        <v>-0.0020351945051013849</v>
       </c>
       <c r="X15" s="1">
-        <v>9.0311832528472413e-05</v>
+        <v>9.0989837195916412e-05</v>
       </c>
       <c r="Y15" s="1">
-        <v>0.00024696711313505499</v>
+        <v>0.00024691224012850059</v>
       </c>
       <c r="Z15" s="1">
-        <v>-0.00012249696350331851</v>
+        <v>-0.00012253818123856902</v>
       </c>
       <c r="AA15" s="1">
-        <v>-0.0022493192821444637</v>
+        <v>-0.0022490080030262254</v>
       </c>
       <c r="AB15" s="1">
-        <v>-0.003612424832579935</v>
+        <v>-0.0036116145004107987</v>
       </c>
       <c r="AC15" s="1">
-        <v>-0.0049835014833747443</v>
+        <v>-0.0049828789386939659</v>
       </c>
       <c r="AD15" s="1">
-        <v>-0.00046749395670935869</v>
+        <v>-0.00046724999950301799</v>
       </c>
       <c r="AE15" s="1">
-        <v>4.914540092129513e-05</v>
+        <v>4.916748255345739e-05</v>
       </c>
       <c r="AF15" s="1">
-        <v>-0.03354000099045501</v>
+        <v>-0.033538578540351499</v>
       </c>
     </row>
     <row r="16">
@@ -5943,97 +5943,97 @@
         <v>75</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.087507929206346466</v>
+        <v>-0.087517808347148771</v>
       </c>
       <c r="C16" s="1">
-        <v>2.8976100766404771e-05</v>
+        <v>2.896817457769419e-05</v>
       </c>
       <c r="D16" s="1">
-        <v>-5.8582608760348963e-07</v>
+        <v>-5.8569067118482079e-07</v>
       </c>
       <c r="E16" s="1">
-        <v>0.002201258170083837</v>
+        <v>0.0022010532400660505</v>
       </c>
       <c r="F16" s="1">
-        <v>0.002547900433469758</v>
+        <v>0.0025480356842784067</v>
       </c>
       <c r="G16" s="1">
-        <v>-0.00041472147044492591</v>
+        <v>-0.00041469455882463604</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.00032054734588526229</v>
+        <v>-0.00032026894606322631</v>
       </c>
       <c r="I16" s="1">
-        <v>-0.00069880426969678305</v>
+        <v>-0.00069868610877775114</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.00089833280106171517</v>
+        <v>-0.00089844571028317374</v>
       </c>
       <c r="K16" s="1">
-        <v>-0.0006235820914812229</v>
+        <v>-0.00062341590064904709</v>
       </c>
       <c r="L16" s="1">
-        <v>0.00081739997007414938</v>
+        <v>0.00081738304951394988</v>
       </c>
       <c r="M16" s="1">
-        <v>0.00086056052931677597</v>
+        <v>0.00086051346721631125</v>
       </c>
       <c r="N16" s="1">
-        <v>0.0015471834595138243</v>
+        <v>0.0015468488688475711</v>
       </c>
       <c r="O16" s="1">
-        <v>-0.00042341926792400716</v>
+        <v>-0.00042359286485224926</v>
       </c>
       <c r="P16" s="1">
-        <v>0.00036771879588927761</v>
+        <v>0.00036757399134817667</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.0020712092989697574</v>
+        <v>0.0020711614798683427</v>
       </c>
       <c r="R16" s="1">
-        <v>0.0015363584386332589</v>
+        <v>0.0015366113221214847</v>
       </c>
       <c r="S16" s="1">
-        <v>-0.00022995650732730467</v>
+        <v>-0.00022993922463479579</v>
       </c>
       <c r="T16" s="1">
-        <v>0.00016665909265195961</v>
+        <v>0.00016699050519485128</v>
       </c>
       <c r="U16" s="1">
-        <v>-0.0010063197998703653</v>
+        <v>-0.0010059695343259982</v>
       </c>
       <c r="V16" s="1">
-        <v>0.00067052376879978503</v>
+        <v>0.00067097281833265233</v>
       </c>
       <c r="W16" s="1">
-        <v>-0.00040371712388593661</v>
+        <v>-0.00040367136103699683</v>
       </c>
       <c r="X16" s="1">
-        <v>0.0013481388222978635</v>
+        <v>0.0013485231933132468</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.0002166049885797245</v>
+        <v>0.00021660808059820473</v>
       </c>
       <c r="Z16" s="1">
-        <v>-0.00029001795921239327</v>
+        <v>-0.00029003317082067741</v>
       </c>
       <c r="AA16" s="1">
-        <v>-0.0013422110993098482</v>
+        <v>-0.0013426352032309562</v>
       </c>
       <c r="AB16" s="1">
-        <v>-0.0010861304713089667</v>
+        <v>-0.0010858132870287507</v>
       </c>
       <c r="AC16" s="1">
-        <v>-0.0012415074124061164</v>
+        <v>-0.0012414791282805994</v>
       </c>
       <c r="AD16" s="1">
-        <v>-0.0016831970111100515</v>
+        <v>-0.0016829685945807028</v>
       </c>
       <c r="AE16" s="1">
-        <v>8.4953870720705794e-05</v>
+        <v>8.4985396806276761e-05</v>
       </c>
       <c r="AF16" s="1">
-        <v>-0.0079694921540220398</v>
+        <v>-0.0079701762010025747</v>
       </c>
     </row>
     <row r="17">
@@ -6041,97 +6041,97 @@
         <v>76</v>
       </c>
       <c r="B17" s="1">
-        <v>0.71070590739030204</v>
+        <v>0.71073092715840769</v>
       </c>
       <c r="C17" s="1">
-        <v>0.0015184973318481448</v>
+        <v>0.001518478574723589</v>
       </c>
       <c r="D17" s="1">
-        <v>-1.4660322295479498e-05</v>
+        <v>-1.4660467405360627e-05</v>
       </c>
       <c r="E17" s="1">
-        <v>0.0014497736700591246</v>
+        <v>0.0014502686579398797</v>
       </c>
       <c r="F17" s="1">
-        <v>0.0058529334276241785</v>
+        <v>0.0058527150873944984</v>
       </c>
       <c r="G17" s="1">
-        <v>-0.00095618379498573283</v>
+        <v>-0.00095611973083117863</v>
       </c>
       <c r="H17" s="1">
-        <v>0.00075761882746456372</v>
+        <v>0.00075812500757416884</v>
       </c>
       <c r="I17" s="1">
-        <v>-0.001035244874353157</v>
+        <v>-0.0010332106510416786</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.0037508098559934748</v>
+        <v>-0.0037505692006763527</v>
       </c>
       <c r="K17" s="1">
-        <v>9.7336724158004345e-05</v>
+        <v>9.7371923864515014e-05</v>
       </c>
       <c r="L17" s="1">
-        <v>-0.0026418490959096118</v>
+        <v>-0.002643137819772521</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.0014696905863382311</v>
+        <v>-0.0014683424281879856</v>
       </c>
       <c r="N17" s="1">
-        <v>-0.00031841218940888388</v>
+        <v>-0.00031836058825438179</v>
       </c>
       <c r="O17" s="1">
-        <v>-0.00017218039280908135</v>
+        <v>-0.00017163687074456604</v>
       </c>
       <c r="P17" s="1">
-        <v>0.0010880310657556715</v>
+        <v>0.0010884828635845945</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.0015363584386332589</v>
+        <v>0.0015366113221214847</v>
       </c>
       <c r="R17" s="1">
-        <v>0.047173451226111773</v>
+        <v>0.047174150707854308</v>
       </c>
       <c r="S17" s="1">
-        <v>7.1829136085272858e-05</v>
+        <v>7.1884959073192532e-05</v>
       </c>
       <c r="T17" s="1">
-        <v>0.00095204634816553721</v>
+        <v>0.00095182224764144311</v>
       </c>
       <c r="U17" s="1">
-        <v>0.0027770016300276579</v>
+        <v>0.0027770839850395149</v>
       </c>
       <c r="V17" s="1">
-        <v>0.0022672822042871651</v>
+        <v>0.0022677746844394116</v>
       </c>
       <c r="W17" s="1">
-        <v>0.0019342719790237115</v>
+        <v>0.0019351895676318991</v>
       </c>
       <c r="X17" s="1">
-        <v>0.0032562735840861567</v>
+        <v>0.0032570414656091055</v>
       </c>
       <c r="Y17" s="1">
-        <v>-2.4337496060907989e-05</v>
+        <v>-2.4294148171322225e-05</v>
       </c>
       <c r="Z17" s="1">
-        <v>-0.00027031618437338997</v>
+        <v>-0.00027034518268931519</v>
       </c>
       <c r="AA17" s="1">
-        <v>0.00020076323910737416</v>
+        <v>0.00020268697753502178</v>
       </c>
       <c r="AB17" s="1">
-        <v>-0.00045124903281041446</v>
+        <v>-0.0004508820311436095</v>
       </c>
       <c r="AC17" s="1">
-        <v>-0.0024637071187699339</v>
+        <v>-0.0024636215296158885</v>
       </c>
       <c r="AD17" s="1">
-        <v>-0.00061581176232115972</v>
+        <v>-0.00061495095966362684</v>
       </c>
       <c r="AE17" s="1">
-        <v>0.00031207789997465346</v>
+        <v>0.00031209729978026198</v>
       </c>
       <c r="AF17" s="1">
-        <v>-0.047038033738147161</v>
+        <v>-0.04703955051040784</v>
       </c>
     </row>
     <row r="18">
@@ -6139,97 +6139,97 @@
         <v>77</v>
       </c>
       <c r="B18" s="1">
-        <v>-0.012069752751993679</v>
+        <v>-0.012072205449875219</v>
       </c>
       <c r="C18" s="1">
-        <v>1.0520651332400315e-05</v>
+        <v>1.0501160474891405e-05</v>
       </c>
       <c r="D18" s="1">
-        <v>-2.1327916486797621e-07</v>
+        <v>-2.1299974450117101e-07</v>
       </c>
       <c r="E18" s="1">
-        <v>-0.00039407648331260352</v>
+        <v>-0.00039407209790613717</v>
       </c>
       <c r="F18" s="1">
-        <v>3.8626887678542155e-05</v>
+        <v>3.85804930322837e-05</v>
       </c>
       <c r="G18" s="1">
-        <v>-9.3572320403238762e-05</v>
+        <v>-9.3553630891004061e-05</v>
       </c>
       <c r="H18" s="1">
-        <v>7.4871670742658256e-05</v>
+        <v>7.4816765532280047e-05</v>
       </c>
       <c r="I18" s="1">
-        <v>-0.00019090688058965612</v>
+        <v>-0.00019094939071115369</v>
       </c>
       <c r="J18" s="1">
-        <v>0.0001499357588552637</v>
+        <v>0.00014994622172047507</v>
       </c>
       <c r="K18" s="1">
-        <v>-0.00010207681881281398</v>
+        <v>-0.00010214902129486621</v>
       </c>
       <c r="L18" s="1">
-        <v>-0.00010055428478924523</v>
+        <v>-0.00010055153065839824</v>
       </c>
       <c r="M18" s="1">
-        <v>-0.00046131559670120072</v>
+        <v>-0.00046152364145616524</v>
       </c>
       <c r="N18" s="1">
-        <v>-0.00030834743108780211</v>
+        <v>-0.00030829894631073987</v>
       </c>
       <c r="O18" s="1">
-        <v>-0.00017618855438986808</v>
+        <v>-0.0001761752477657131</v>
       </c>
       <c r="P18" s="1">
-        <v>-0.0003761245760155324</v>
+        <v>-0.0003760728113235759</v>
       </c>
       <c r="Q18" s="1">
-        <v>-0.00022995650732730467</v>
+        <v>-0.00022993922463479579</v>
       </c>
       <c r="R18" s="1">
-        <v>7.1829136085272858e-05</v>
+        <v>7.1884959073192532e-05</v>
       </c>
       <c r="S18" s="1">
-        <v>0.00017177738871478068</v>
+        <v>0.00017177272393445274</v>
       </c>
       <c r="T18" s="1">
-        <v>-2.0343395523219528e-05</v>
+        <v>-2.023782614388654e-05</v>
       </c>
       <c r="U18" s="1">
-        <v>0.00040989916910966938</v>
+        <v>0.00040970196059846535</v>
       </c>
       <c r="V18" s="1">
-        <v>0.0003464727379276746</v>
+        <v>0.00034638871488803082</v>
       </c>
       <c r="W18" s="1">
-        <v>5.0477146665997108e-05</v>
+        <v>5.0430289544430766e-05</v>
       </c>
       <c r="X18" s="1">
-        <v>-0.00023297855346745151</v>
+        <v>-0.00023323262369073097</v>
       </c>
       <c r="Y18" s="1">
-        <v>-0.00014656352015167732</v>
+        <v>-0.00014657594556716073</v>
       </c>
       <c r="Z18" s="1">
-        <v>7.0568159217257264e-05</v>
+        <v>7.0582603004535948e-05</v>
       </c>
       <c r="AA18" s="1">
-        <v>-0.00043173076572971354</v>
+        <v>-0.0004317916883661314</v>
       </c>
       <c r="AB18" s="1">
-        <v>0.00039959248269041833</v>
+        <v>0.00039956288263457286</v>
       </c>
       <c r="AC18" s="1">
-        <v>0.00045773027151638451</v>
+        <v>0.00045772864985413157</v>
       </c>
       <c r="AD18" s="1">
-        <v>0.00019935639147438116</v>
+        <v>0.00019926348932433255</v>
       </c>
       <c r="AE18" s="1">
-        <v>1.7470663531584631e-06</v>
+        <v>1.7443319388007536e-06</v>
       </c>
       <c r="AF18" s="1">
-        <v>0.0019753055981819958</v>
+        <v>0.0019757628031543111</v>
       </c>
     </row>
     <row r="19">
@@ -6237,97 +6237,97 @@
         <v>31</v>
       </c>
       <c r="B19" s="1">
-        <v>-0.14391923021688505</v>
+        <v>-0.14387616333377459</v>
       </c>
       <c r="C19" s="1">
-        <v>-0.00045865257229149234</v>
+        <v>-0.00045863943671137089</v>
       </c>
       <c r="D19" s="1">
-        <v>5.5853845800064462e-06</v>
+        <v>5.5841075914792298e-06</v>
       </c>
       <c r="E19" s="1">
-        <v>0.00046648736794849808</v>
+        <v>0.00046772431505343417</v>
       </c>
       <c r="F19" s="1">
-        <v>0.0017572323529160658</v>
+        <v>0.0017587890816792235</v>
       </c>
       <c r="G19" s="1">
-        <v>0.00041371130008838533</v>
+        <v>0.00041350238069366371</v>
       </c>
       <c r="H19" s="1">
-        <v>0.00073091059248681089</v>
+        <v>0.00073196697999018678</v>
       </c>
       <c r="I19" s="1">
-        <v>-0.00030601820410952954</v>
+        <v>-0.00030321851669773761</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.00021440021372751139</v>
+        <v>-0.00021382490631467049</v>
       </c>
       <c r="K19" s="1">
-        <v>-5.5945222326131416e-05</v>
+        <v>-5.5474497427404623e-05</v>
       </c>
       <c r="L19" s="1">
-        <v>-0.0012315477548496198</v>
+        <v>-0.001233055444856055</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.0026171168716646433</v>
+        <v>-0.0026147582696338188</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.7945846838063328e-05</v>
+        <v>-1.7439017630032803e-05</v>
       </c>
       <c r="O19" s="1">
-        <v>-0.0013309852321201077</v>
+        <v>-0.0013305943167576696</v>
       </c>
       <c r="P19" s="1">
-        <v>-0.00019289588968131668</v>
+        <v>-0.00019218164150009917</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.00016665909265195961</v>
+        <v>0.00016699050519485128</v>
       </c>
       <c r="R19" s="1">
-        <v>0.00095204634816553721</v>
+        <v>0.00095182224764144311</v>
       </c>
       <c r="S19" s="1">
-        <v>-2.0343395523219528e-05</v>
+        <v>-2.023782614388654e-05</v>
       </c>
       <c r="T19" s="1">
-        <v>0.0040924909731388367</v>
+        <v>0.0040912376970404889</v>
       </c>
       <c r="U19" s="1">
-        <v>-0.0033571728645248339</v>
+        <v>-0.0033557501493333827</v>
       </c>
       <c r="V19" s="1">
-        <v>-0.00066371368920386598</v>
+        <v>-0.00066249016623321714</v>
       </c>
       <c r="W19" s="1">
-        <v>-0.0017797817501494497</v>
+        <v>-0.0017788384468890028</v>
       </c>
       <c r="X19" s="1">
-        <v>-0.0013435558454069105</v>
+        <v>-0.001340655896713088</v>
       </c>
       <c r="Y19" s="1">
-        <v>-5.8982036669753102e-05</v>
+        <v>-5.8787690239169618e-05</v>
       </c>
       <c r="Z19" s="1">
-        <v>8.5565984786116516e-05</v>
+        <v>8.5394588529473652e-05</v>
       </c>
       <c r="AA19" s="1">
-        <v>-0.0033164761548033681</v>
+        <v>-0.0033154987797418952</v>
       </c>
       <c r="AB19" s="1">
-        <v>0.0020064878332121203</v>
+        <v>0.0020064830622246715</v>
       </c>
       <c r="AC19" s="1">
-        <v>-0.00092983207063345504</v>
+        <v>-0.00093053632416962087</v>
       </c>
       <c r="AD19" s="1">
-        <v>-0.0011761698488092654</v>
+        <v>-0.001175309741267715</v>
       </c>
       <c r="AE19" s="1">
-        <v>-6.8160495177782255e-06</v>
+        <v>-6.8492705357745381e-06</v>
       </c>
       <c r="AF19" s="1">
-        <v>0.0083184824836872104</v>
+        <v>0.0083168674174860097</v>
       </c>
     </row>
     <row r="20">
@@ -6335,97 +6335,97 @@
         <v>32</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.014972156623068004</v>
+        <v>-0.014986240450253912</v>
       </c>
       <c r="C20" s="1">
-        <v>0.0011027093129918984</v>
+        <v>0.0011026803263152309</v>
       </c>
       <c r="D20" s="1">
-        <v>-1.0693020969368576e-05</v>
+        <v>-1.0691314006568004e-05</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.0018356746561110741</v>
+        <v>-0.0018356337508171798</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.001881839297210074</v>
+        <v>-0.0018827211130703105</v>
       </c>
       <c r="G20" s="1">
-        <v>-0.0010154447702044045</v>
+        <v>-0.00101535118482729</v>
       </c>
       <c r="H20" s="1">
-        <v>-0.00029076418028923384</v>
+        <v>-0.00029256339077822491</v>
       </c>
       <c r="I20" s="1">
-        <v>0.00062651870494007111</v>
+        <v>0.0006236628235322117</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.00062060930067314724</v>
+        <v>-0.00062110481985735988</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.00031670091867075367</v>
+        <v>-0.00031743518974487739</v>
       </c>
       <c r="L20" s="1">
-        <v>0.0012787820064078109</v>
+        <v>0.0012805134025535708</v>
       </c>
       <c r="M20" s="1">
-        <v>0.00046626078473472644</v>
+        <v>0.00046473028461104741</v>
       </c>
       <c r="N20" s="1">
-        <v>-0.001745777983112146</v>
+        <v>-0.0017447489930474376</v>
       </c>
       <c r="O20" s="1">
-        <v>0.00099322895966694885</v>
+        <v>0.00099330312486047012</v>
       </c>
       <c r="P20" s="1">
-        <v>-0.00012625673643303081</v>
+        <v>-0.00012684599627271753</v>
       </c>
       <c r="Q20" s="1">
-        <v>-0.0010063197998703653</v>
+        <v>-0.0010059695343259982</v>
       </c>
       <c r="R20" s="1">
-        <v>0.0027770016300276579</v>
+        <v>0.0027770839850395149</v>
       </c>
       <c r="S20" s="1">
-        <v>0.00040989916910966938</v>
+        <v>0.00040970196059846535</v>
       </c>
       <c r="T20" s="1">
-        <v>-0.0033571728645248339</v>
+        <v>-0.0033557501493333827</v>
       </c>
       <c r="U20" s="1">
-        <v>0.0139107303621222</v>
+        <v>0.013909727477069613</v>
       </c>
       <c r="V20" s="1">
-        <v>0.00063454843575419442</v>
+        <v>0.00063161426966451464</v>
       </c>
       <c r="W20" s="1">
-        <v>-0.00025936770622228024</v>
+        <v>-0.00026179732558983312</v>
       </c>
       <c r="X20" s="1">
-        <v>-0.0027604794834116628</v>
+        <v>-0.0027654933104835303</v>
       </c>
       <c r="Y20" s="1">
-        <v>-0.00083728986649022968</v>
+        <v>-0.00083757602006811257</v>
       </c>
       <c r="Z20" s="1">
-        <v>0.00053874202019034445</v>
+        <v>0.00053899418628940762</v>
       </c>
       <c r="AA20" s="1">
-        <v>0.0036721148427105469</v>
+        <v>0.0036750416106563241</v>
       </c>
       <c r="AB20" s="1">
-        <v>-0.0004255985233907523</v>
+        <v>-0.00042568263285550382</v>
       </c>
       <c r="AC20" s="1">
-        <v>0.0011050696836739232</v>
+        <v>0.0011058191971859248</v>
       </c>
       <c r="AD20" s="1">
-        <v>0.0010537603953175501</v>
+        <v>0.0010519856041419995</v>
       </c>
       <c r="AE20" s="1">
-        <v>0.00013193134986326407</v>
+        <v>0.00013193796421005159</v>
       </c>
       <c r="AF20" s="1">
-        <v>-0.020190512709002375</v>
+        <v>-0.020190340773793385</v>
       </c>
     </row>
     <row r="21">
@@ -6433,97 +6433,97 @@
         <v>78</v>
       </c>
       <c r="B21" s="1">
-        <v>0.52693490683344657</v>
+        <v>0.52692161323651543</v>
       </c>
       <c r="C21" s="1">
-        <v>-0.0009892943672806789</v>
+        <v>-0.0009895375374750796</v>
       </c>
       <c r="D21" s="1">
-        <v>1.0809410040125773e-05</v>
+        <v>1.081223894793852e-05</v>
       </c>
       <c r="E21" s="1">
-        <v>0.0022430250989063428</v>
+        <v>0.0022439948854310219</v>
       </c>
       <c r="F21" s="1">
-        <v>0.0048378358178606962</v>
+        <v>0.0048381771861404433</v>
       </c>
       <c r="G21" s="1">
-        <v>-0.001438404571426008</v>
+        <v>-0.0014382342181563298</v>
       </c>
       <c r="H21" s="1">
-        <v>0.0016331949963545589</v>
+        <v>0.0016327562441045482</v>
       </c>
       <c r="I21" s="1">
-        <v>0.00051291445271776925</v>
+        <v>0.00051241405122458283</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.00063510936392942308</v>
+        <v>-0.00063524505066432646</v>
       </c>
       <c r="K21" s="1">
-        <v>0.0021355654362460175</v>
+        <v>0.0021347147795553606</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.00021548390084895341</v>
+        <v>-0.00021629334145598089</v>
       </c>
       <c r="M21" s="1">
-        <v>-0.0065386960732516271</v>
+        <v>-0.0065400655396834675</v>
       </c>
       <c r="N21" s="1">
-        <v>-0.0013470458641735793</v>
+        <v>-0.0013464018344086439</v>
       </c>
       <c r="O21" s="1">
-        <v>0.0022830490981062893</v>
+        <v>0.0022830289127716286</v>
       </c>
       <c r="P21" s="1">
-        <v>0.0025194366289275072</v>
+        <v>0.0025198959150417102</v>
       </c>
       <c r="Q21" s="1">
-        <v>0.00067052376879978503</v>
+        <v>0.00067097281833265233</v>
       </c>
       <c r="R21" s="1">
-        <v>0.0022672822042871651</v>
+        <v>0.0022677746844394116</v>
       </c>
       <c r="S21" s="1">
-        <v>0.0003464727379276746</v>
+        <v>0.00034638871488803082</v>
       </c>
       <c r="T21" s="1">
-        <v>-0.00066371368920386598</v>
+        <v>-0.00066249016623321714</v>
       </c>
       <c r="U21" s="1">
-        <v>0.00063454843575419442</v>
+        <v>0.00063161426966451464</v>
       </c>
       <c r="V21" s="1">
-        <v>0.026857886416478835</v>
+        <v>0.026858439061956552</v>
       </c>
       <c r="W21" s="1">
-        <v>0.0018671467180474575</v>
+        <v>0.0018669775750452368</v>
       </c>
       <c r="X21" s="1">
-        <v>0.014542023017402539</v>
+        <v>0.014541847539075364</v>
       </c>
       <c r="Y21" s="1">
-        <v>0.0019515116837796592</v>
+        <v>0.0019516703948443057</v>
       </c>
       <c r="Z21" s="1">
-        <v>-0.0021439442767982931</v>
+        <v>-0.0021440662178584861</v>
       </c>
       <c r="AA21" s="1">
-        <v>-0.0052842265731220632</v>
+        <v>-0.0052854534782083842</v>
       </c>
       <c r="AB21" s="1">
-        <v>0.0027804854982056365</v>
+        <v>0.0027802685070858315</v>
       </c>
       <c r="AC21" s="1">
-        <v>-0.00053027848334434753</v>
+        <v>-0.00053141430735959352</v>
       </c>
       <c r="AD21" s="1">
-        <v>0.0005129421361022734</v>
+        <v>0.00051199328211104099</v>
       </c>
       <c r="AE21" s="1">
-        <v>-0.00016072277592358688</v>
+        <v>-0.00016068888804098163</v>
       </c>
       <c r="AF21" s="1">
-        <v>0.0012979534655555951</v>
+        <v>0.0013004832590765604</v>
       </c>
     </row>
     <row r="22">
@@ -6531,97 +6531,97 @@
         <v>79</v>
       </c>
       <c r="B22" s="1">
-        <v>0.058439808737788479</v>
+        <v>0.058416239599165524</v>
       </c>
       <c r="C22" s="1">
-        <v>9.2701637546029579e-05</v>
+        <v>9.2652958846682967e-05</v>
       </c>
       <c r="D22" s="1">
-        <v>-1.7025664952467065e-06</v>
+        <v>-1.7019799862173715e-06</v>
       </c>
       <c r="E22" s="1">
-        <v>0.0012585498626353452</v>
+        <v>0.0012588481491565781</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.00030239303778861358</v>
+        <v>-0.00030111707552052175</v>
       </c>
       <c r="G22" s="1">
-        <v>0.00035394075808484887</v>
+        <v>0.00035399717215720342</v>
       </c>
       <c r="H22" s="1">
-        <v>-0.0014134107965974065</v>
+        <v>-0.0014134547717662219</v>
       </c>
       <c r="I22" s="1">
-        <v>-0.0028792630846383033</v>
+        <v>-0.0028818214296326555</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.0027563885705779861</v>
+        <v>-0.002756199586255538</v>
       </c>
       <c r="K22" s="1">
-        <v>-0.0018053321695528993</v>
+        <v>-0.0018050294737179187</v>
       </c>
       <c r="L22" s="1">
-        <v>-0.0014111857038698952</v>
+        <v>-0.0014106100267221103</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.0032993410215361673</v>
+        <v>-0.0033013850929321537</v>
       </c>
       <c r="N22" s="1">
-        <v>0.0032967613674810907</v>
+        <v>0.0032970833137214452</v>
       </c>
       <c r="O22" s="1">
-        <v>-0.00066580861874460107</v>
+        <v>-0.00066640640272944834</v>
       </c>
       <c r="P22" s="1">
-        <v>-0.0020341296748685352</v>
+        <v>-0.0020351945051013849</v>
       </c>
       <c r="Q22" s="1">
-        <v>-0.00040371712388593661</v>
+        <v>-0.00040367136103699683</v>
       </c>
       <c r="R22" s="1">
-        <v>0.0019342719790237115</v>
+        <v>0.0019351895676318991</v>
       </c>
       <c r="S22" s="1">
-        <v>5.0477146665997108e-05</v>
+        <v>5.0430289544430766e-05</v>
       </c>
       <c r="T22" s="1">
-        <v>-0.0017797817501494497</v>
+        <v>-0.0017788384468890028</v>
       </c>
       <c r="U22" s="1">
-        <v>-0.00025936770622228024</v>
+        <v>-0.00026179732558983312</v>
       </c>
       <c r="V22" s="1">
-        <v>0.0018671467180474575</v>
+        <v>0.0018669775750452368</v>
       </c>
       <c r="W22" s="1">
-        <v>0.018521264112191675</v>
+        <v>0.018521762349131356</v>
       </c>
       <c r="X22" s="1">
-        <v>0.0079837560939668168</v>
+        <v>0.0079841772710874063</v>
       </c>
       <c r="Y22" s="1">
-        <v>0.00022810006791117035</v>
+        <v>0.00022811669708066684</v>
       </c>
       <c r="Z22" s="1">
-        <v>0.00055145728337661513</v>
+        <v>0.00055144115222208136</v>
       </c>
       <c r="AA22" s="1">
-        <v>-0.0011796421429830241</v>
+        <v>-0.0011808832961128439</v>
       </c>
       <c r="AB22" s="1">
-        <v>-0.0003796511404041596</v>
+        <v>-0.00037957478609586216</v>
       </c>
       <c r="AC22" s="1">
-        <v>-0.00054449931794199428</v>
+        <v>-0.00054487030887119189</v>
       </c>
       <c r="AD22" s="1">
-        <v>0.0028269757838661593</v>
+        <v>0.0028264646734079387</v>
       </c>
       <c r="AE22" s="1">
-        <v>-4.5405516495696327e-06</v>
+        <v>-4.5070648056820611e-06</v>
       </c>
       <c r="AF22" s="1">
-        <v>-0.0040790662797016916</v>
+        <v>-0.0040788347355657367</v>
       </c>
     </row>
     <row r="23">
@@ -6629,97 +6629,97 @@
         <v>80</v>
       </c>
       <c r="B23" s="1">
-        <v>0.33282396635330652</v>
+        <v>0.33276771791581911</v>
       </c>
       <c r="C23" s="1">
-        <v>0.00030853261464035622</v>
+        <v>0.00030818262871681185</v>
       </c>
       <c r="D23" s="1">
-        <v>-5.6627160457223163e-06</v>
+        <v>-5.6578646048215589e-06</v>
       </c>
       <c r="E23" s="1">
-        <v>0.0026611890586119105</v>
+        <v>0.0026619990007030149</v>
       </c>
       <c r="F23" s="1">
-        <v>0.0013642555221142424</v>
+        <v>0.00136326716625407</v>
       </c>
       <c r="G23" s="1">
-        <v>-0.00091466057047992488</v>
+        <v>-0.00091400598066742472</v>
       </c>
       <c r="H23" s="1">
-        <v>0.00067963993729942829</v>
+        <v>0.00067873171958456741</v>
       </c>
       <c r="I23" s="1">
-        <v>0.009362859467561685</v>
+        <v>0.0093620616567857071</v>
       </c>
       <c r="J23" s="1">
-        <v>0.0062420625365775251</v>
+        <v>0.0062413356155310712</v>
       </c>
       <c r="K23" s="1">
-        <v>0.0064759020855304911</v>
+        <v>0.0064740959740147569</v>
       </c>
       <c r="L23" s="1">
-        <v>0.0049644120035823164</v>
+        <v>0.0049631991762064537</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.0043032396905059262</v>
+        <v>-0.0043061327577890423</v>
       </c>
       <c r="N23" s="1">
-        <v>0.0025665351990561119</v>
+        <v>0.0025666826976767547</v>
       </c>
       <c r="O23" s="1">
-        <v>-0.0015802490537481506</v>
+        <v>-0.0015803212711456294</v>
       </c>
       <c r="P23" s="1">
-        <v>9.0311832528472413e-05</v>
+        <v>9.0989837195916412e-05</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.0013481388222978635</v>
+        <v>0.0013485231933132468</v>
       </c>
       <c r="R23" s="1">
-        <v>0.0032562735840861567</v>
+        <v>0.0032570414656091055</v>
       </c>
       <c r="S23" s="1">
-        <v>-0.00023297855346745151</v>
+        <v>-0.00023323262369073097</v>
       </c>
       <c r="T23" s="1">
-        <v>-0.0013435558454069105</v>
+        <v>-0.001340655896713088</v>
       </c>
       <c r="U23" s="1">
-        <v>-0.0027604794834116628</v>
+        <v>-0.0027654933104835303</v>
       </c>
       <c r="V23" s="1">
-        <v>0.014542023017402539</v>
+        <v>0.014541847539075364</v>
       </c>
       <c r="W23" s="1">
-        <v>0.0079837560939668168</v>
+        <v>0.0079841772710874063</v>
       </c>
       <c r="X23" s="1">
-        <v>0.027674077533072806</v>
+        <v>0.027673484724557579</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.0025949835959312053</v>
+        <v>0.0025952345513820807</v>
       </c>
       <c r="Z23" s="1">
-        <v>-0.001911762893729668</v>
+        <v>-0.0019117940629116534</v>
       </c>
       <c r="AA23" s="1">
-        <v>-0.001161391151662086</v>
+        <v>-0.0011645891641090221</v>
       </c>
       <c r="AB23" s="1">
-        <v>0.002793454355260792</v>
+        <v>0.0027929473944384503</v>
       </c>
       <c r="AC23" s="1">
-        <v>0.00017231677209440105</v>
+        <v>0.00017036215457953002</v>
       </c>
       <c r="AD23" s="1">
-        <v>0.0027786184959867079</v>
+        <v>0.0027768424478441457</v>
       </c>
       <c r="AE23" s="1">
-        <v>-0.00013414137523227017</v>
+        <v>-0.00013404186026758953</v>
       </c>
       <c r="AF23" s="1">
-        <v>-0.033925049769673879</v>
+        <v>-0.033922468878720274</v>
       </c>
     </row>
     <row r="24">
@@ -6727,97 +6727,97 @@
         <v>81</v>
       </c>
       <c r="B24" s="1">
-        <v>0.022633862604240877</v>
+        <v>0.02263049658577811</v>
       </c>
       <c r="C24" s="1">
-        <v>-0.00014697756733043649</v>
+        <v>-0.00014700104082355245</v>
       </c>
       <c r="D24" s="1">
-        <v>1.857897305991809e-06</v>
+        <v>1.8581638906659715e-06</v>
       </c>
       <c r="E24" s="1">
-        <v>0.00095689076066440327</v>
+        <v>0.00095696929383812083</v>
       </c>
       <c r="F24" s="1">
-        <v>0.00021080186338524117</v>
+        <v>0.00021090704360667012</v>
       </c>
       <c r="G24" s="1">
-        <v>-6.1965184269964502e-05</v>
+        <v>-6.1947748022474387e-05</v>
       </c>
       <c r="H24" s="1">
-        <v>0.00025128143599299161</v>
+        <v>0.00025134042650310981</v>
       </c>
       <c r="I24" s="1">
-        <v>-0.00026383027319300256</v>
+        <v>-0.00026398426971852886</v>
       </c>
       <c r="J24" s="1">
-        <v>0.00025098317994858878</v>
+        <v>0.00025095827349803923</v>
       </c>
       <c r="K24" s="1">
-        <v>0.00021001139853322158</v>
+        <v>0.0002100312695931042</v>
       </c>
       <c r="L24" s="1">
-        <v>-0.00032823607663604731</v>
+        <v>-0.00032824478845880876</v>
       </c>
       <c r="M24" s="1">
-        <v>0.00024971946276748039</v>
+        <v>0.000249657255360821</v>
       </c>
       <c r="N24" s="1">
-        <v>-0.00036875167953741891</v>
+        <v>-0.00036883330035738951</v>
       </c>
       <c r="O24" s="1">
-        <v>0.00019354574632545699</v>
+        <v>0.00019349501244015233</v>
       </c>
       <c r="P24" s="1">
-        <v>0.00024696711313505499</v>
+        <v>0.00024691224012850059</v>
       </c>
       <c r="Q24" s="1">
-        <v>0.0002166049885797245</v>
+        <v>0.00021660808059820473</v>
       </c>
       <c r="R24" s="1">
-        <v>-2.4337496060907989e-05</v>
+        <v>-2.4294148171322225e-05</v>
       </c>
       <c r="S24" s="1">
-        <v>-0.00014656352015167732</v>
+        <v>-0.00014657594556716073</v>
       </c>
       <c r="T24" s="1">
-        <v>-5.8982036669753102e-05</v>
+        <v>-5.8787690239169618e-05</v>
       </c>
       <c r="U24" s="1">
-        <v>-0.00083728986649022968</v>
+        <v>-0.00083757602006811257</v>
       </c>
       <c r="V24" s="1">
-        <v>0.0019515116837796592</v>
+        <v>0.0019516703948443057</v>
       </c>
       <c r="W24" s="1">
-        <v>0.00022810006791117035</v>
+        <v>0.00022811669708066684</v>
       </c>
       <c r="X24" s="1">
-        <v>0.0025949835959312053</v>
+        <v>0.0025952345513820807</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.00079468531270293684</v>
+        <v>0.0007947320379636597</v>
       </c>
       <c r="Z24" s="1">
-        <v>-0.00051292958394740429</v>
+        <v>-0.00051295931890412111</v>
       </c>
       <c r="AA24" s="1">
-        <v>0.00024236761031686622</v>
+        <v>0.00024206461258122409</v>
       </c>
       <c r="AB24" s="1">
-        <v>0.00025543372932147995</v>
+        <v>0.00025543764695068656</v>
       </c>
       <c r="AC24" s="1">
-        <v>-0.00025872017104079919</v>
+        <v>-0.00025894926025840865</v>
       </c>
       <c r="AD24" s="1">
-        <v>0.00017533389255705144</v>
+        <v>0.00017524915025632018</v>
       </c>
       <c r="AE24" s="1">
-        <v>-5.5787116662466511e-05</v>
+        <v>-5.5776254740601778e-05</v>
       </c>
       <c r="AF24" s="1">
-        <v>-0.0030107540991782273</v>
+        <v>-0.0030108073736972692</v>
       </c>
     </row>
     <row r="25">
@@ -6825,97 +6825,97 @@
         <v>82</v>
       </c>
       <c r="B25" s="1">
-        <v>-0.012348655879188103</v>
+        <v>-0.012346256929629753</v>
       </c>
       <c r="C25" s="1">
-        <v>0.00011497494913592221</v>
+        <v>0.00011500059771742547</v>
       </c>
       <c r="D25" s="1">
-        <v>-1.3300806781679558e-06</v>
+        <v>-1.3304142294645212e-06</v>
       </c>
       <c r="E25" s="1">
-        <v>-0.00069160532020677925</v>
+        <v>-0.00069164950415299986</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.00043666377981133747</v>
+        <v>-0.00043658004124101987</v>
       </c>
       <c r="G25" s="1">
-        <v>2.46536907510214e-05</v>
+        <v>2.462999742743879e-05</v>
       </c>
       <c r="H25" s="1">
-        <v>-0.00020296993036536103</v>
+        <v>-0.00020294446641170834</v>
       </c>
       <c r="I25" s="1">
-        <v>9.1513919158038842e-05</v>
+        <v>9.1555477018827758e-05</v>
       </c>
       <c r="J25" s="1">
-        <v>-0.00018233766985622591</v>
+        <v>-0.00018227229737820998</v>
       </c>
       <c r="K25" s="1">
-        <v>-0.00019993622368279446</v>
+        <v>-0.00019985758052004296</v>
       </c>
       <c r="L25" s="1">
-        <v>0.00014284198111331027</v>
+        <v>0.00014290619083299301</v>
       </c>
       <c r="M25" s="1">
-        <v>-7.5104905997438711e-05</v>
+        <v>-7.5050942173584872e-05</v>
       </c>
       <c r="N25" s="1">
-        <v>0.0001410707182361352</v>
+        <v>0.00014112318618050666</v>
       </c>
       <c r="O25" s="1">
-        <v>4.2988289961127038e-05</v>
+        <v>4.298949763617381e-05</v>
       </c>
       <c r="P25" s="1">
-        <v>-0.00012249696350331851</v>
+        <v>-0.00012253818123856902</v>
       </c>
       <c r="Q25" s="1">
-        <v>-0.00029001795921239327</v>
+        <v>-0.00029003317082067741</v>
       </c>
       <c r="R25" s="1">
-        <v>-0.00027031618437338997</v>
+        <v>-0.00027034518268931519</v>
       </c>
       <c r="S25" s="1">
-        <v>7.0568159217257264e-05</v>
+        <v>7.0582603004535948e-05</v>
       </c>
       <c r="T25" s="1">
-        <v>8.5565984786116516e-05</v>
+        <v>8.5394588529473652e-05</v>
       </c>
       <c r="U25" s="1">
-        <v>0.00053874202019034445</v>
+        <v>0.00053899418628940762</v>
       </c>
       <c r="V25" s="1">
-        <v>-0.0021439442767982931</v>
+        <v>-0.0021440662178584861</v>
       </c>
       <c r="W25" s="1">
-        <v>0.00055145728337661513</v>
+        <v>0.00055144115222208136</v>
       </c>
       <c r="X25" s="1">
-        <v>-0.001911762893729668</v>
+        <v>-0.0019117940629116534</v>
       </c>
       <c r="Y25" s="1">
-        <v>-0.00051292958394740429</v>
+        <v>-0.00051295931890412111</v>
       </c>
       <c r="Z25" s="1">
-        <v>0.00046213877980456365</v>
+        <v>0.00046215579383050872</v>
       </c>
       <c r="AA25" s="1">
-        <v>5.8990237588245955e-05</v>
+        <v>5.9227066005893345e-05</v>
       </c>
       <c r="AB25" s="1">
-        <v>-0.00035628028783960442</v>
+        <v>-0.00035627010761101532</v>
       </c>
       <c r="AC25" s="1">
-        <v>2.4694324459781326e-05</v>
+        <v>2.4850808760310114e-05</v>
       </c>
       <c r="AD25" s="1">
-        <v>-9.1464947717501404e-05</v>
+        <v>-9.1387308110469847e-05</v>
       </c>
       <c r="AE25" s="1">
-        <v>3.8931382972244111e-05</v>
+        <v>3.8922183847342438e-05</v>
       </c>
       <c r="AF25" s="1">
-        <v>0.001759812046446884</v>
+        <v>0.0017597151343675976</v>
       </c>
     </row>
     <row r="26">
@@ -6923,97 +6923,97 @@
         <v>56</v>
       </c>
       <c r="B26" s="1">
-        <v>-0.20229140178973259</v>
+        <v>-0.20230443611494622</v>
       </c>
       <c r="C26" s="1">
-        <v>0.00065169033588002726</v>
+        <v>0.00065214208182064149</v>
       </c>
       <c r="D26" s="1">
-        <v>-7.9663804186865604e-06</v>
+        <v>-7.9695031017307817e-06</v>
       </c>
       <c r="E26" s="1">
-        <v>-0.0037843467410189572</v>
+        <v>-0.0037858160615621339</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.0099642365473466069</v>
+        <v>-0.0099672215274162548</v>
       </c>
       <c r="G26" s="1">
-        <v>-0.00049925845134164357</v>
+        <v>-0.0004991765079753567</v>
       </c>
       <c r="H26" s="1">
-        <v>-0.0017457780081271031</v>
+        <v>-0.0017466794361852885</v>
       </c>
       <c r="I26" s="1">
-        <v>0.00092354159150524404</v>
+        <v>0.00092080152027874604</v>
       </c>
       <c r="J26" s="1">
-        <v>0.0029016825084582469</v>
+        <v>0.0029018503138717559</v>
       </c>
       <c r="K26" s="1">
-        <v>0.004258716805124154</v>
+        <v>0.0042580412129635294</v>
       </c>
       <c r="L26" s="1">
-        <v>-0.0001403026252940788</v>
+        <v>-0.00013949485416626939</v>
       </c>
       <c r="M26" s="1">
-        <v>0.013496910717562132</v>
+        <v>0.013496231763663109</v>
       </c>
       <c r="N26" s="1">
-        <v>-0.0035576678246611653</v>
+        <v>-0.0035585517090466288</v>
       </c>
       <c r="O26" s="1">
-        <v>0.0028278459236341161</v>
+        <v>0.0028275240864089439</v>
       </c>
       <c r="P26" s="1">
-        <v>-0.0022493192821444637</v>
+        <v>-0.0022490080030262254</v>
       </c>
       <c r="Q26" s="1">
-        <v>-0.0013422110993098482</v>
+        <v>-0.0013426352032309562</v>
       </c>
       <c r="R26" s="1">
-        <v>0.00020076323910737416</v>
+        <v>0.00020268697753502178</v>
       </c>
       <c r="S26" s="1">
-        <v>-0.00043173076572971354</v>
+        <v>-0.0004317916883661314</v>
       </c>
       <c r="T26" s="1">
-        <v>-0.0033164761548033681</v>
+        <v>-0.0033154987797418952</v>
       </c>
       <c r="U26" s="1">
-        <v>0.0036721148427105469</v>
+        <v>0.0036750416106563241</v>
       </c>
       <c r="V26" s="1">
-        <v>-0.0052842265731220632</v>
+        <v>-0.0052854534782083842</v>
       </c>
       <c r="W26" s="1">
-        <v>-0.0011796421429830241</v>
+        <v>-0.0011808832961128439</v>
       </c>
       <c r="X26" s="1">
-        <v>-0.001161391151662086</v>
+        <v>-0.0011645891641090221</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.00024236761031686622</v>
+        <v>0.00024206461258122409</v>
       </c>
       <c r="Z26" s="1">
-        <v>5.8990237588245955e-05</v>
+        <v>5.9227066005893345e-05</v>
       </c>
       <c r="AA26" s="1">
-        <v>0.03182039694789205</v>
+        <v>0.031820876347521308</v>
       </c>
       <c r="AB26" s="1">
-        <v>0.008977243576511024</v>
+        <v>0.0089773599460180858</v>
       </c>
       <c r="AC26" s="1">
-        <v>0.0076123113035095145</v>
+        <v>0.0076127745596222974</v>
       </c>
       <c r="AD26" s="1">
-        <v>0.0094240893452002834</v>
+        <v>0.0094237438067434637</v>
       </c>
       <c r="AE26" s="1">
-        <v>-0.0003627926087152978</v>
+        <v>-0.00036278004682541339</v>
       </c>
       <c r="AF26" s="1">
-        <v>-0.011939865908177916</v>
+        <v>-0.011949041492964663</v>
       </c>
     </row>
     <row r="27">
@@ -7021,97 +7021,97 @@
         <v>57</v>
       </c>
       <c r="B27" s="1">
-        <v>0.055762336073328325</v>
+        <v>0.055772223598255961</v>
       </c>
       <c r="C27" s="1">
-        <v>-3.8732907299534637e-05</v>
+        <v>-3.8680784890090126e-05</v>
       </c>
       <c r="D27" s="1">
-        <v>-5.0578810310689305e-07</v>
+        <v>-5.0616611283514846e-07</v>
       </c>
       <c r="E27" s="1">
-        <v>-0.0024005257371109471</v>
+        <v>-0.0024000386009211082</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.0026979202661507355</v>
+        <v>-0.0026980484016750597</v>
       </c>
       <c r="G27" s="1">
-        <v>-0.0013463390914037823</v>
+        <v>-0.0013464007137241329</v>
       </c>
       <c r="H27" s="1">
-        <v>-0.00058496898057508115</v>
+        <v>-0.00058523187646863234</v>
       </c>
       <c r="I27" s="1">
-        <v>-0.00026606775547067391</v>
+        <v>-0.00026591086669353059</v>
       </c>
       <c r="J27" s="1">
-        <v>0.0011530807454680561</v>
+        <v>0.0011535542130373944</v>
       </c>
       <c r="K27" s="1">
-        <v>-0.00010199714511317792</v>
+        <v>-0.00010255171588161721</v>
       </c>
       <c r="L27" s="1">
-        <v>-0.0040235784459010937</v>
+        <v>-0.0040239800228877853</v>
       </c>
       <c r="M27" s="1">
-        <v>0.00011610516205111756</v>
+        <v>0.00011616711754149685</v>
       </c>
       <c r="N27" s="1">
-        <v>-0.00185634361414935</v>
+        <v>-0.0018557035753981009</v>
       </c>
       <c r="O27" s="1">
-        <v>-0.0014742708959440236</v>
+        <v>-0.0014740961349801393</v>
       </c>
       <c r="P27" s="1">
-        <v>-0.003612424832579935</v>
+        <v>-0.0036116145004107987</v>
       </c>
       <c r="Q27" s="1">
-        <v>-0.0010861304713089667</v>
+        <v>-0.0010858132870287507</v>
       </c>
       <c r="R27" s="1">
-        <v>-0.00045124903281041446</v>
+        <v>-0.0004508820311436095</v>
       </c>
       <c r="S27" s="1">
-        <v>0.00039959248269041833</v>
+        <v>0.00039956288263457286</v>
       </c>
       <c r="T27" s="1">
-        <v>0.0020064878332121203</v>
+        <v>0.0020064830622246715</v>
       </c>
       <c r="U27" s="1">
-        <v>-0.0004255985233907523</v>
+        <v>-0.00042568263285550382</v>
       </c>
       <c r="V27" s="1">
-        <v>0.0027804854982056365</v>
+        <v>0.0027802685070858315</v>
       </c>
       <c r="W27" s="1">
-        <v>-0.0003796511404041596</v>
+        <v>-0.00037957478609586216</v>
       </c>
       <c r="X27" s="1">
-        <v>0.002793454355260792</v>
+        <v>0.0027929473944384503</v>
       </c>
       <c r="Y27" s="1">
-        <v>0.00025543372932147995</v>
+        <v>0.00025543764695068656</v>
       </c>
       <c r="Z27" s="1">
-        <v>-0.00035628028783960442</v>
+        <v>-0.00035627010761101532</v>
       </c>
       <c r="AA27" s="1">
-        <v>0.008977243576511024</v>
+        <v>0.0089773599460180858</v>
       </c>
       <c r="AB27" s="1">
-        <v>0.021564723748773083</v>
+        <v>0.021564176022279894</v>
       </c>
       <c r="AC27" s="1">
-        <v>0.0085710014626418189</v>
+        <v>0.0085705678836949968</v>
       </c>
       <c r="AD27" s="1">
-        <v>0.0085708062922522851</v>
+        <v>0.008570550341913924</v>
       </c>
       <c r="AE27" s="1">
-        <v>-0.00052816464204864398</v>
+        <v>-0.00052819961778781421</v>
       </c>
       <c r="AF27" s="1">
-        <v>0.0082310665558321915</v>
+        <v>0.0082293751470244314</v>
       </c>
     </row>
     <row r="28">
@@ -7119,97 +7119,97 @@
         <v>58</v>
       </c>
       <c r="B28" s="1">
-        <v>-0.013341397668277001</v>
+        <v>-0.013306882591998991</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.000147587177066099</v>
+        <v>-0.00014729948729630057</v>
       </c>
       <c r="D28" s="1">
-        <v>9.7138945875580095e-08</v>
+        <v>9.4553104331150965e-08</v>
       </c>
       <c r="E28" s="1">
-        <v>-0.0042835709592460667</v>
+        <v>-0.004284314060355481</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.0033150579265489779</v>
+        <v>-0.0033165668491301568</v>
       </c>
       <c r="G28" s="1">
-        <v>-0.00069258469308254578</v>
+        <v>-0.00069284822911654109</v>
       </c>
       <c r="H28" s="1">
-        <v>-0.0025706151916638637</v>
+        <v>-0.0025716628695043459</v>
       </c>
       <c r="I28" s="1">
-        <v>0.00048391500991182279</v>
+        <v>0.00048299115424998984</v>
       </c>
       <c r="J28" s="1">
-        <v>0.0014685168136921167</v>
+        <v>0.0014690896350707527</v>
       </c>
       <c r="K28" s="1">
-        <v>0.0013096736271885484</v>
+        <v>0.0013091168460373087</v>
       </c>
       <c r="L28" s="1">
-        <v>-0.00089895557460789588</v>
+        <v>-0.0008979110796655948</v>
       </c>
       <c r="M28" s="1">
-        <v>0.002878171544353738</v>
+        <v>0.0028778645375370196</v>
       </c>
       <c r="N28" s="1">
-        <v>-0.0031644797077319776</v>
+        <v>-0.0031638353169584198</v>
       </c>
       <c r="O28" s="1">
-        <v>-0.0019250434399147448</v>
+        <v>-0.0019250231983625604</v>
       </c>
       <c r="P28" s="1">
-        <v>-0.0049835014833747443</v>
+        <v>-0.0049828789386939659</v>
       </c>
       <c r="Q28" s="1">
-        <v>-0.0012415074124061164</v>
+        <v>-0.0012414791282805994</v>
       </c>
       <c r="R28" s="1">
-        <v>-0.0024637071187699339</v>
+        <v>-0.0024636215296158885</v>
       </c>
       <c r="S28" s="1">
-        <v>0.00045773027151638451</v>
+        <v>0.00045772864985413157</v>
       </c>
       <c r="T28" s="1">
-        <v>-0.00092983207063345504</v>
+        <v>-0.00093053632416962087</v>
       </c>
       <c r="U28" s="1">
-        <v>0.0011050696836739232</v>
+        <v>0.0011058191971859248</v>
       </c>
       <c r="V28" s="1">
-        <v>-0.00053027848334434753</v>
+        <v>-0.00053141430735959352</v>
       </c>
       <c r="W28" s="1">
-        <v>-0.00054449931794199428</v>
+        <v>-0.00054487030887119189</v>
       </c>
       <c r="X28" s="1">
-        <v>0.00017231677209440105</v>
+        <v>0.00017036215457953002</v>
       </c>
       <c r="Y28" s="1">
-        <v>-0.00025872017104079919</v>
+        <v>-0.00025894926025840865</v>
       </c>
       <c r="Z28" s="1">
-        <v>2.4694324459781326e-05</v>
+        <v>2.4850808760310114e-05</v>
       </c>
       <c r="AA28" s="1">
-        <v>0.0076123113035095145</v>
+        <v>0.0076127745596222974</v>
       </c>
       <c r="AB28" s="1">
-        <v>0.0085710014626418189</v>
+        <v>0.0085705678836949968</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.015345559555905455</v>
+        <v>0.015345885387164407</v>
       </c>
       <c r="AD28" s="1">
-        <v>0.0089088741221740007</v>
+        <v>0.008908824401265834</v>
       </c>
       <c r="AE28" s="1">
-        <v>-0.00012832685653025591</v>
+        <v>-0.0001284022172339173</v>
       </c>
       <c r="AF28" s="1">
-        <v>0.011302393444868053</v>
+        <v>0.0112991217873336</v>
       </c>
     </row>
     <row r="29">
@@ -7217,97 +7217,97 @@
         <v>59</v>
       </c>
       <c r="B29" s="1">
-        <v>0.081688239854002004</v>
+        <v>0.08168271188558876</v>
       </c>
       <c r="C29" s="1">
-        <v>0.00010274618997860177</v>
+        <v>0.00010276638437329102</v>
       </c>
       <c r="D29" s="1">
-        <v>-1.5181966061238353e-06</v>
+        <v>-1.5177199524424971e-06</v>
       </c>
       <c r="E29" s="1">
-        <v>-0.0041564706663223261</v>
+        <v>-0.0041562824117170744</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.0059809280294555092</v>
+        <v>-0.0059813983501883928</v>
       </c>
       <c r="G29" s="1">
-        <v>0.00023912383880336091</v>
+        <v>0.00023920938060293349</v>
       </c>
       <c r="H29" s="1">
-        <v>0.00034027765895977037</v>
+        <v>0.00033945851191353495</v>
       </c>
       <c r="I29" s="1">
-        <v>-0.00011580546055463443</v>
+        <v>-0.00011774888398092404</v>
       </c>
       <c r="J29" s="1">
-        <v>0.0011811697392704549</v>
+        <v>0.0011814705578534722</v>
       </c>
       <c r="K29" s="1">
-        <v>0.00058387692770418137</v>
+        <v>0.00058323379953770758</v>
       </c>
       <c r="L29" s="1">
-        <v>-0.0023052511722490166</v>
+        <v>-0.0023049512441189867</v>
       </c>
       <c r="M29" s="1">
-        <v>0.0013832700431817054</v>
+        <v>0.0013818389966908638</v>
       </c>
       <c r="N29" s="1">
-        <v>-0.0010489907700071876</v>
+        <v>-0.0010483077908032066</v>
       </c>
       <c r="O29" s="1">
-        <v>-8.8941269648956309e-05</v>
+        <v>-8.9071949532386341e-05</v>
       </c>
       <c r="P29" s="1">
-        <v>-0.00046749395670935869</v>
+        <v>-0.00046724999950301799</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.0016831970111100515</v>
+        <v>-0.0016829685945807028</v>
       </c>
       <c r="R29" s="1">
-        <v>-0.00061581176232115972</v>
+        <v>-0.00061495095966362684</v>
       </c>
       <c r="S29" s="1">
-        <v>0.00019935639147438116</v>
+        <v>0.00019926348932433255</v>
       </c>
       <c r="T29" s="1">
-        <v>-0.0011761698488092654</v>
+        <v>-0.001175309741267715</v>
       </c>
       <c r="U29" s="1">
-        <v>0.0010537603953175501</v>
+        <v>0.0010519856041419995</v>
       </c>
       <c r="V29" s="1">
-        <v>0.0005129421361022734</v>
+        <v>0.00051199328211104099</v>
       </c>
       <c r="W29" s="1">
-        <v>0.0028269757838661593</v>
+        <v>0.0028264646734079387</v>
       </c>
       <c r="X29" s="1">
-        <v>0.0027786184959867079</v>
+        <v>0.0027768424478441457</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.00017533389255705144</v>
+        <v>0.00017524915025632018</v>
       </c>
       <c r="Z29" s="1">
-        <v>-9.1464947717501404e-05</v>
+        <v>-9.1387308110469847e-05</v>
       </c>
       <c r="AA29" s="1">
-        <v>0.0094240893452002834</v>
+        <v>0.0094237438067434637</v>
       </c>
       <c r="AB29" s="1">
-        <v>0.0085708062922522851</v>
+        <v>0.008570550341913924</v>
       </c>
       <c r="AC29" s="1">
-        <v>0.0089088741221740007</v>
+        <v>0.008908824401265834</v>
       </c>
       <c r="AD29" s="1">
-        <v>0.0134125905272564</v>
+        <v>0.01341200243676164</v>
       </c>
       <c r="AE29" s="1">
-        <v>-0.00041406791331916704</v>
+        <v>-0.00041407756417870804</v>
       </c>
       <c r="AF29" s="1">
-        <v>0.0025483606378370327</v>
+        <v>0.0025473907574137707</v>
       </c>
     </row>
     <row r="30">
@@ -7315,97 +7315,97 @@
         <v>60</v>
       </c>
       <c r="B30" s="1">
-        <v>0.01503934325817064</v>
+        <v>0.015040165580950006</v>
       </c>
       <c r="C30" s="1">
-        <v>2.6141751044661801e-05</v>
+        <v>2.6144706029497245e-05</v>
       </c>
       <c r="D30" s="1">
-        <v>-4.5037755042926681e-07</v>
+        <v>-4.5044237099095631e-07</v>
       </c>
       <c r="E30" s="1">
-        <v>0.0001499549302403266</v>
+        <v>0.00015002425862876048</v>
       </c>
       <c r="F30" s="1">
-        <v>0.00042162719398394083</v>
+        <v>0.00042171803809626965</v>
       </c>
       <c r="G30" s="1">
-        <v>8.7447931551082602e-05</v>
+        <v>8.7448195901297741e-05</v>
       </c>
       <c r="H30" s="1">
-        <v>-9.5847773255686443e-05</v>
+        <v>-9.5837210419994726e-05</v>
       </c>
       <c r="I30" s="1">
-        <v>7.0899346365670303e-05</v>
+        <v>7.0915562794835428e-05</v>
       </c>
       <c r="J30" s="1">
-        <v>0.00014199123407152703</v>
+        <v>0.0001419957463768386</v>
       </c>
       <c r="K30" s="1">
-        <v>-0.00023104565420874412</v>
+        <v>-0.00023106772669192932</v>
       </c>
       <c r="L30" s="1">
-        <v>-0.00028216260394437772</v>
+        <v>-0.0002822379105273438</v>
       </c>
       <c r="M30" s="1">
-        <v>1.1822318785110767e-05</v>
+        <v>1.1883689623908834e-05</v>
       </c>
       <c r="N30" s="1">
-        <v>8.935015113416476e-06</v>
+        <v>8.9837293119081627e-06</v>
       </c>
       <c r="O30" s="1">
-        <v>-0.00010329328279637878</v>
+        <v>-0.00010328002727435053</v>
       </c>
       <c r="P30" s="1">
-        <v>4.914540092129513e-05</v>
+        <v>4.916748255345739e-05</v>
       </c>
       <c r="Q30" s="1">
-        <v>8.4953870720705794e-05</v>
+        <v>8.4985396806276761e-05</v>
       </c>
       <c r="R30" s="1">
-        <v>0.00031207789997465346</v>
+        <v>0.00031209729978026198</v>
       </c>
       <c r="S30" s="1">
-        <v>1.7470663531584631e-06</v>
+        <v>1.7443319388007536e-06</v>
       </c>
       <c r="T30" s="1">
-        <v>-6.8160495177782255e-06</v>
+        <v>-6.8492705357745381e-06</v>
       </c>
       <c r="U30" s="1">
-        <v>0.00013193134986326407</v>
+        <v>0.00013193796421005159</v>
       </c>
       <c r="V30" s="1">
-        <v>-0.00016072277592358688</v>
+        <v>-0.00016068888804098163</v>
       </c>
       <c r="W30" s="1">
-        <v>-4.5405516495696327e-06</v>
+        <v>-4.5070648056820611e-06</v>
       </c>
       <c r="X30" s="1">
-        <v>-0.00013414137523227017</v>
+        <v>-0.00013404186026758953</v>
       </c>
       <c r="Y30" s="1">
-        <v>-5.5787116662466511e-05</v>
+        <v>-5.5776254740601778e-05</v>
       </c>
       <c r="Z30" s="1">
-        <v>3.8931382972244111e-05</v>
+        <v>3.8922183847342438e-05</v>
       </c>
       <c r="AA30" s="1">
-        <v>-0.0003627926087152978</v>
+        <v>-0.00036278004682541339</v>
       </c>
       <c r="AB30" s="1">
-        <v>-0.00052816464204864398</v>
+        <v>-0.00052819961778781421</v>
       </c>
       <c r="AC30" s="1">
-        <v>-0.00012832685653025591</v>
+        <v>-0.0001284022172339173</v>
       </c>
       <c r="AD30" s="1">
-        <v>-0.00041406791331916704</v>
+        <v>-0.00041407756417870804</v>
       </c>
       <c r="AE30" s="1">
-        <v>0.00012463569997818823</v>
+        <v>0.00012464306422049605</v>
       </c>
       <c r="AF30" s="1">
-        <v>-0.0018224554661008452</v>
+        <v>-0.0018227569587502637</v>
       </c>
     </row>
     <row r="31">
@@ -7413,97 +7413,97 @@
         <v>61</v>
       </c>
       <c r="B31" s="1">
-        <v>-2.8028944839863228</v>
+        <v>-2.8029163244373652</v>
       </c>
       <c r="C31" s="1">
-        <v>-0.010614376038956951</v>
+        <v>-0.010614498167765676</v>
       </c>
       <c r="D31" s="1">
-        <v>0.00011078841403356981</v>
+        <v>0.00011078767982932816</v>
       </c>
       <c r="E31" s="1">
-        <v>-0.013751893641947632</v>
+        <v>-0.013751819662359565</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.0051680041175217115</v>
+        <v>-0.0051608300928908911</v>
       </c>
       <c r="G31" s="1">
-        <v>-0.012767715221919274</v>
+        <v>-0.012768720242568088</v>
       </c>
       <c r="H31" s="1">
-        <v>-0.018095772569022839</v>
+        <v>-0.018093167866381488</v>
       </c>
       <c r="I31" s="1">
-        <v>-0.068998689710599803</v>
+        <v>-0.068996966864805831</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.061060832753046135</v>
+        <v>-0.061057112231170163</v>
       </c>
       <c r="K31" s="1">
-        <v>-0.059845235413058862</v>
+        <v>-0.059842135022758924</v>
       </c>
       <c r="L31" s="1">
-        <v>-0.078181719933197336</v>
+        <v>-0.078179773455942736</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.015282588862388254</v>
+        <v>-0.015285433752252293</v>
       </c>
       <c r="N31" s="1">
-        <v>-0.008620041528395652</v>
+        <v>-0.0086199135976611808</v>
       </c>
       <c r="O31" s="1">
-        <v>-0.017483004318354312</v>
+        <v>-0.01748337991926277</v>
       </c>
       <c r="P31" s="1">
-        <v>-0.03354000099045501</v>
+        <v>-0.033538578540351499</v>
       </c>
       <c r="Q31" s="1">
-        <v>-0.0079694921540220398</v>
+        <v>-0.0079701762010025747</v>
       </c>
       <c r="R31" s="1">
-        <v>-0.047038033738147161</v>
+        <v>-0.04703955051040784</v>
       </c>
       <c r="S31" s="1">
-        <v>0.0019753055981819958</v>
+        <v>0.0019757628031543111</v>
       </c>
       <c r="T31" s="1">
-        <v>0.0083184824836872104</v>
+        <v>0.0083168674174860097</v>
       </c>
       <c r="U31" s="1">
-        <v>-0.020190512709002375</v>
+        <v>-0.020190340773793385</v>
       </c>
       <c r="V31" s="1">
-        <v>0.0012979534655555951</v>
+        <v>0.0013004832590765604</v>
       </c>
       <c r="W31" s="1">
-        <v>-0.0040790662797016916</v>
+        <v>-0.0040788347355657367</v>
       </c>
       <c r="X31" s="1">
-        <v>-0.033925049769673879</v>
+        <v>-0.033922468878720274</v>
       </c>
       <c r="Y31" s="1">
-        <v>-0.0030107540991782273</v>
+        <v>-0.0030108073736972692</v>
       </c>
       <c r="Z31" s="1">
-        <v>0.001759812046446884</v>
+        <v>0.0017597151343675976</v>
       </c>
       <c r="AA31" s="1">
-        <v>-0.011939865908177916</v>
+        <v>-0.011949041492964663</v>
       </c>
       <c r="AB31" s="1">
-        <v>0.0082310665558321915</v>
+        <v>0.0082293751470244314</v>
       </c>
       <c r="AC31" s="1">
-        <v>0.011302393444868053</v>
+        <v>0.0112991217873336</v>
       </c>
       <c r="AD31" s="1">
-        <v>0.0025483606378370327</v>
+        <v>0.0025473907574137707</v>
       </c>
       <c r="AE31" s="1">
-        <v>-0.0018224554661008452</v>
+        <v>-0.0018227569587502637</v>
       </c>
       <c r="AF31" s="1">
-        <v>0.40063093072510769</v>
+        <v>0.40064367975340676</v>
       </c>
     </row>
   </sheetData>
